--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070"/>
+    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2375,9 +2375,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2395,9 +2395,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2411,6 +2417,14 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -2418,31 +2432,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2454,8 +2446,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2476,16 +2477,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2499,9 +2492,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF7F7F7F"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2524,7 +2517,7 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2533,7 +2526,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2554,7 +2554,169 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2566,175 +2728,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2763,39 +2763,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -2803,6 +2770,21 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2822,26 +2804,44 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2853,145 +2853,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -12039,14 +12039,14 @@
         <v>味方</v>
       </c>
       <c r="Q108">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R108" t="str">
         <f>INDEX(Define!N:N,MATCH(Q108,Define!M:M))</f>
-        <v>列</v>
+        <v>全体</v>
       </c>
       <c r="S108">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T108">
         <v>1</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="7070" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6620" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -317,8 +317,7 @@
     <t>べネディクション</t>
   </si>
   <si>
-    <t>自身以外のHpを/f[f,0,1]回復
-対象のCT-/f[f,1,1]</t>
+    <t>自身以外のHpを/f[f,0,1]回復</t>
   </si>
   <si>
     <t>アクトヒール</t>
@@ -2374,9 +2373,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
@@ -2396,6 +2395,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -2409,30 +2415,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2448,17 +2440,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2471,14 +2455,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2501,6 +2485,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2517,18 +2509,25 @@
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2554,7 +2553,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2566,19 +2637,79 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2596,145 +2727,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2765,41 +2764,18 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2828,20 +2804,43 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2853,16 +2852,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2871,127 +2870,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="28" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="25" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="25" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="23" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -22435,7 +22434,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I317"/>
+  <dimension ref="A1:I316"/>
   <sheetFormatPr defaultColWidth="8.72727272727273" defaultRowHeight="13"/>
   <cols>
     <col min="2" max="2" width="20" customWidth="1"/>
@@ -24041,7 +24040,7 @@
         <v>Hp回復</v>
       </c>
       <c r="E55">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="F55">
         <v>0</v>
@@ -24053,20 +24052,20 @@
         <v>100</v>
       </c>
     </row>
-    <row r="56" spans="1:8">
+    <row r="56" spans="1:9">
       <c r="A56">
-        <v>4050</v>
+        <v>4060</v>
       </c>
       <c r="B56" t="str">
         <f>INDEX(TextData!B:B,MATCH(A56,TextData!A:A))</f>
-        <v>べネディクション</v>
+        <v>ホーリーグレイス</v>
       </c>
       <c r="C56">
-        <v>4020</v>
+        <v>3020</v>
       </c>
       <c r="D56" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C56,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>ステート解除</v>
       </c>
       <c r="E56">
         <v>1</v>
@@ -24080,8 +24079,12 @@
       <c r="H56">
         <v>100</v>
       </c>
-    </row>
-    <row r="57" spans="1:9">
+      <c r="I56" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E56,[1]TextData!A:A))</f>
+        <v>戦闘不能</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
       <c r="A57">
         <v>4060</v>
       </c>
@@ -24090,14 +24093,14 @@
         <v>ホーリーグレイス</v>
       </c>
       <c r="C57">
-        <v>3020</v>
+        <v>2010</v>
       </c>
       <c r="D57" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C57,Define!P:P))</f>
-        <v>ステート解除</v>
+        <v>Hp回復</v>
       </c>
       <c r="E57">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F57">
         <v>0</v>
@@ -24108,18 +24111,14 @@
       <c r="H57">
         <v>100</v>
       </c>
-      <c r="I57" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E57,[1]TextData!A:A))</f>
-        <v>戦闘不能</v>
-      </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58">
-        <v>4060</v>
+        <v>4070</v>
       </c>
       <c r="B58" t="str">
         <f>INDEX(TextData!B:B,MATCH(A58,TextData!A:A))</f>
-        <v>ホーリーグレイス</v>
+        <v>キュアエール</v>
       </c>
       <c r="C58">
         <v>2010</v>
@@ -24129,7 +24128,7 @@
         <v>Hp回復</v>
       </c>
       <c r="E58">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="F58">
         <v>0</v>
@@ -24150,14 +24149,14 @@
         <v>キュアエール</v>
       </c>
       <c r="C59">
-        <v>2010</v>
+        <v>3030</v>
       </c>
       <c r="D59" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C59,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>Abnormalステート解除</v>
       </c>
       <c r="E59">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F59">
         <v>0</v>
@@ -24169,73 +24168,73 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:8">
+    <row r="60" spans="1:9">
       <c r="A60">
-        <v>4070</v>
+        <v>4080</v>
       </c>
       <c r="B60" t="str">
         <f>INDEX(TextData!B:B,MATCH(A60,TextData!A:A))</f>
-        <v>キュアエール</v>
+        <v>ラインバリア</v>
       </c>
       <c r="C60">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="D60" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C60,Define!P:P))</f>
-        <v>Abnormalステート解除</v>
+        <v>ステート付与</v>
       </c>
       <c r="E60">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G60">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H60">
         <v>100</v>
       </c>
-    </row>
-    <row r="61" spans="1:9">
+      <c r="I60" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E60,[1]TextData!A:A))</f>
+        <v>ダメージカット</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
       <c r="A61">
-        <v>4080</v>
+        <v>5010</v>
       </c>
       <c r="B61" t="str">
         <f>INDEX(TextData!B:B,MATCH(A61,TextData!A:A))</f>
-        <v>ラインバリア</v>
+        <v>ダークプリズン</v>
       </c>
       <c r="C61">
-        <v>3010</v>
+        <v>1010</v>
       </c>
       <c r="D61" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C61,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E61">
-        <v>1100</v>
+        <v>150</v>
       </c>
       <c r="F61">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G61">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H61">
         <v>100</v>
       </c>
-      <c r="I61" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E61,[1]TextData!A:A))</f>
-        <v>ダメージカット</v>
-      </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62">
-        <v>5010</v>
+        <v>5020</v>
       </c>
       <c r="B62" t="str">
         <f>INDEX(TextData!B:B,MATCH(A62,TextData!A:A))</f>
-        <v>ダークプリズン</v>
+        <v>ユーサネイジア</v>
       </c>
       <c r="C62">
         <v>1010</v>
@@ -24245,7 +24244,7 @@
         <v>Hpダメージ</v>
       </c>
       <c r="E62">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="F62">
         <v>0</v>
@@ -24259,27 +24258,27 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63">
-        <v>5020</v>
+        <v>5030</v>
       </c>
       <c r="B63" t="str">
         <f>INDEX(TextData!B:B,MATCH(A63,TextData!A:A))</f>
-        <v>ユーサネイジア</v>
+        <v>ドレインヒール</v>
       </c>
       <c r="C63">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="D63" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C63,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>Hp吸収ダメージ</v>
       </c>
       <c r="E63">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="F63">
         <v>0</v>
       </c>
       <c r="G63">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H63">
         <v>100</v>
@@ -24287,18 +24286,18 @@
     </row>
     <row r="64" spans="1:8">
       <c r="A64">
-        <v>5030</v>
+        <v>5040</v>
       </c>
       <c r="B64" t="str">
         <f>INDEX(TextData!B:B,MATCH(A64,TextData!A:A))</f>
-        <v>ドレインヒール</v>
+        <v>アビサルデスペア</v>
       </c>
       <c r="C64">
-        <v>1020</v>
+        <v>1010</v>
       </c>
       <c r="D64" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C64,Define!P:P))</f>
-        <v>Hp吸収ダメージ</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E64">
         <v>150</v>
@@ -24307,13 +24306,13 @@
         <v>0</v>
       </c>
       <c r="G64">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H64">
         <v>100</v>
       </c>
     </row>
-    <row r="65" spans="1:8">
+    <row r="65" spans="1:9">
       <c r="A65">
         <v>5040</v>
       </c>
@@ -24322,17 +24321,17 @@
         <v>アビサルデスペア</v>
       </c>
       <c r="C65">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="D65" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C65,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E65">
-        <v>150</v>
+        <v>2400</v>
       </c>
       <c r="F65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G65">
         <v>0</v>
@@ -24340,37 +24339,37 @@
       <c r="H65">
         <v>100</v>
       </c>
-    </row>
-    <row r="66" spans="1:9">
+      <c r="I65" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E65,[1]TextData!A:A))</f>
+        <v>不治</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
       <c r="A66">
-        <v>5040</v>
+        <v>5050</v>
       </c>
       <c r="B66" t="str">
         <f>INDEX(TextData!B:B,MATCH(A66,TextData!A:A))</f>
-        <v>アビサルデスペア</v>
+        <v>ディプラヴィティ</v>
       </c>
       <c r="C66">
-        <v>3010</v>
+        <v>1010</v>
       </c>
       <c r="D66" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C66,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E66">
-        <v>2400</v>
+        <v>150</v>
       </c>
       <c r="F66">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G66">
         <v>0</v>
       </c>
       <c r="H66">
         <v>100</v>
-      </c>
-      <c r="I66" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E66,[1]TextData!A:A))</f>
-        <v>不治</v>
       </c>
     </row>
     <row r="67" spans="1:8">
@@ -24382,14 +24381,14 @@
         <v>ディプラヴィティ</v>
       </c>
       <c r="C67">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="D67" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C67,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>Ctダメージ</v>
       </c>
       <c r="E67">
-        <v>150</v>
+        <v>2</v>
       </c>
       <c r="F67">
         <v>0</v>
@@ -24401,41 +24400,45 @@
         <v>100</v>
       </c>
     </row>
-    <row r="68" spans="1:8">
+    <row r="68" spans="1:9">
       <c r="A68">
-        <v>5050</v>
+        <v>5060</v>
       </c>
       <c r="B68" t="str">
         <f>INDEX(TextData!B:B,MATCH(A68,TextData!A:A))</f>
-        <v>ディプラヴィティ</v>
+        <v>ダークネス</v>
       </c>
       <c r="C68">
-        <v>4010</v>
+        <v>3010</v>
       </c>
       <c r="D68" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C68,Define!P:P))</f>
-        <v>Ctダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E68">
-        <v>2</v>
+        <v>1082</v>
       </c>
       <c r="F68">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G68">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H68">
         <v>100</v>
       </c>
+      <c r="I68" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E68,[1]TextData!A:A))</f>
+        <v>命中ダウン</v>
+      </c>
     </row>
     <row r="69" spans="1:9">
       <c r="A69">
-        <v>5060</v>
+        <v>5070</v>
       </c>
       <c r="B69" t="str">
         <f>INDEX(TextData!B:B,MATCH(A69,TextData!A:A))</f>
-        <v>ダークネス</v>
+        <v>シェイディークラウド</v>
       </c>
       <c r="C69">
         <v>3010</v>
@@ -24445,55 +24448,51 @@
         <v>ステート付与</v>
       </c>
       <c r="E69">
-        <v>1082</v>
+        <v>1041</v>
       </c>
       <c r="F69">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G69">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="H69">
         <v>100</v>
       </c>
       <c r="I69" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E69,[1]TextData!A:A))</f>
-        <v>命中ダウン</v>
-      </c>
-    </row>
-    <row r="70" spans="1:9">
+        <v>攻撃ダウン</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
       <c r="A70">
-        <v>5070</v>
+        <v>5080</v>
       </c>
       <c r="B70" t="str">
         <f>INDEX(TextData!B:B,MATCH(A70,TextData!A:A))</f>
-        <v>シェイディークラウド</v>
+        <v>ポイズンブロウ</v>
       </c>
       <c r="C70">
-        <v>3010</v>
+        <v>1010</v>
       </c>
       <c r="D70" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C70,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E70">
-        <v>1041</v>
+        <v>150</v>
       </c>
       <c r="F70">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G70">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H70">
         <v>100</v>
       </c>
-      <c r="I70" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E70,[1]TextData!A:A))</f>
-        <v>攻撃ダウン</v>
-      </c>
-    </row>
-    <row r="71" spans="1:8">
+    </row>
+    <row r="71" spans="1:9">
       <c r="A71">
         <v>5080</v>
       </c>
@@ -24502,32 +24501,36 @@
         <v>ポイズンブロウ</v>
       </c>
       <c r="C71">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="D71" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C71,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E71">
-        <v>150</v>
+        <v>2010</v>
       </c>
       <c r="F71">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G71">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H71">
         <v>100</v>
       </c>
+      <c r="I71" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E71,[1]TextData!A:A))</f>
+        <v>毒</v>
+      </c>
     </row>
     <row r="72" spans="1:9">
       <c r="A72">
-        <v>5080</v>
+        <v>10010</v>
       </c>
       <c r="B72" t="str">
         <f>INDEX(TextData!B:B,MATCH(A72,TextData!A:A))</f>
-        <v>ポイズンブロウ</v>
+        <v>アンデッド</v>
       </c>
       <c r="C72">
         <v>3010</v>
@@ -24537,10 +24540,10 @@
         <v>ステート付与</v>
       </c>
       <c r="E72">
-        <v>2010</v>
+        <v>2270</v>
       </c>
       <c r="F72">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G72">
         <v>10</v>
@@ -24550,16 +24553,16 @@
       </c>
       <c r="I72" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E72,[1]TextData!A:A))</f>
-        <v>毒</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="73" spans="1:9">
       <c r="A73">
-        <v>10010</v>
+        <v>10020</v>
       </c>
       <c r="B73" t="str">
         <f>INDEX(TextData!B:B,MATCH(A73,TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>エアリアル</v>
       </c>
       <c r="C73">
         <v>3010</v>
@@ -24569,29 +24572,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E73">
-        <v>2270</v>
+        <v>2190</v>
       </c>
       <c r="F73">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G73">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H73">
         <v>100</v>
       </c>
       <c r="I73" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E73,[1]TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="74" spans="1:9">
       <c r="A74">
-        <v>10020</v>
+        <v>10030</v>
       </c>
       <c r="B74" t="str">
         <f>INDEX(TextData!B:B,MATCH(A74,TextData!A:A))</f>
-        <v>エアリアル</v>
+        <v>悪魔</v>
       </c>
       <c r="C74">
         <v>3010</v>
@@ -24601,29 +24604,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E74">
-        <v>2190</v>
+        <v>1030</v>
       </c>
       <c r="F74">
         <v>999</v>
       </c>
       <c r="G74">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H74">
         <v>100</v>
       </c>
       <c r="I74" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E74,[1]TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>最大Mpアップ</v>
       </c>
     </row>
     <row r="75" spans="1:9">
       <c r="A75">
-        <v>10030</v>
+        <v>10040</v>
       </c>
       <c r="B75" t="str">
         <f>INDEX(TextData!B:B,MATCH(A75,TextData!A:A))</f>
-        <v>悪魔</v>
+        <v>クリーチャー</v>
       </c>
       <c r="C75">
         <v>3010</v>
@@ -24633,29 +24636,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E75">
-        <v>1030</v>
+        <v>1020</v>
       </c>
       <c r="F75">
         <v>999</v>
       </c>
       <c r="G75">
-        <v>3</v>
+        <v>20</v>
       </c>
       <c r="H75">
         <v>100</v>
       </c>
       <c r="I75" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E75,[1]TextData!A:A))</f>
-        <v>最大Mpアップ</v>
+        <v>最大Hpアップ</v>
       </c>
     </row>
     <row r="76" spans="1:9">
       <c r="A76">
-        <v>10040</v>
+        <v>10050</v>
       </c>
       <c r="B76" t="str">
         <f>INDEX(TextData!B:B,MATCH(A76,TextData!A:A))</f>
-        <v>クリーチャー</v>
+        <v>野生の記憶</v>
       </c>
       <c r="C76">
         <v>3010</v>
@@ -24665,29 +24668,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E76">
-        <v>1020</v>
+        <v>1040</v>
       </c>
       <c r="F76">
         <v>999</v>
       </c>
       <c r="G76">
-        <v>20</v>
+        <v>4</v>
       </c>
       <c r="H76">
         <v>100</v>
       </c>
       <c r="I76" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E76,[1]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="77" spans="1:9">
       <c r="A77">
-        <v>10050</v>
+        <v>10060</v>
       </c>
       <c r="B77" t="str">
         <f>INDEX(TextData!B:B,MATCH(A77,TextData!A:A))</f>
-        <v>野生の記憶</v>
+        <v>変異生物</v>
       </c>
       <c r="C77">
         <v>3010</v>
@@ -24697,29 +24700,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E77">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="F77">
         <v>999</v>
       </c>
       <c r="G77">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H77">
         <v>100</v>
       </c>
       <c r="I77" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E77,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
+        <v>防御アップ</v>
       </c>
     </row>
     <row r="78" spans="1:9">
       <c r="A78">
-        <v>10060</v>
+        <v>11010</v>
       </c>
       <c r="B78" t="str">
         <f>INDEX(TextData!B:B,MATCH(A78,TextData!A:A))</f>
-        <v>変異生物</v>
+        <v>ウルフソウル</v>
       </c>
       <c r="C78">
         <v>3010</v>
@@ -24729,29 +24732,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E78">
-        <v>1050</v>
+        <v>1040</v>
       </c>
       <c r="F78">
         <v>999</v>
       </c>
       <c r="G78">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H78">
         <v>100</v>
       </c>
       <c r="I78" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E78,[1]TextData!A:A))</f>
-        <v>防御アップ</v>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="79" spans="1:9">
       <c r="A79">
-        <v>11010</v>
+        <v>11020</v>
       </c>
       <c r="B79" t="str">
         <f>INDEX(TextData!B:B,MATCH(A79,TextData!A:A))</f>
-        <v>ウルフソウル</v>
+        <v>プリディカメント</v>
       </c>
       <c r="C79">
         <v>3010</v>
@@ -24767,7 +24770,7 @@
         <v>999</v>
       </c>
       <c r="G79">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H79">
         <v>100</v>
@@ -24779,11 +24782,11 @@
     </row>
     <row r="80" spans="1:9">
       <c r="A80">
-        <v>11020</v>
+        <v>11030</v>
       </c>
       <c r="B80" t="str">
         <f>INDEX(TextData!B:B,MATCH(A80,TextData!A:A))</f>
-        <v>プリディカメント</v>
+        <v>アサルトシフト</v>
       </c>
       <c r="C80">
         <v>3010</v>
@@ -24799,7 +24802,7 @@
         <v>999</v>
       </c>
       <c r="G80">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H80">
         <v>100</v>
@@ -24825,7 +24828,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E81">
-        <v>1040</v>
+        <v>1051</v>
       </c>
       <c r="F81">
         <v>999</v>
@@ -24838,48 +24841,44 @@
       </c>
       <c r="I81" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E81,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
-    </row>
-    <row r="82" spans="1:9">
+        <v>防御ダウン</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
       <c r="A82">
-        <v>11030</v>
+        <v>11040</v>
       </c>
       <c r="B82" t="str">
         <f>INDEX(TextData!B:B,MATCH(A82,TextData!A:A))</f>
-        <v>アサルトシフト</v>
+        <v>アクティブギフト</v>
       </c>
       <c r="C82">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="D82" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C82,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ct回復</v>
       </c>
       <c r="E82">
-        <v>1051</v>
+        <v>1</v>
       </c>
       <c r="F82">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G82">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H82">
         <v>100</v>
       </c>
-      <c r="I82" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E82,[1]TextData!A:A))</f>
-        <v>防御ダウン</v>
-      </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83">
-        <v>11040</v>
+        <v>11050</v>
       </c>
       <c r="B83" t="str">
         <f>INDEX(TextData!B:B,MATCH(A83,TextData!A:A))</f>
-        <v>アクティブギフト</v>
+        <v>イグナイテッド</v>
       </c>
       <c r="C83">
         <v>4020</v>
@@ -24889,10 +24888,10 @@
         <v>Ct回復</v>
       </c>
       <c r="E83">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F83">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G83">
         <v>0</v>
@@ -24903,11 +24902,11 @@
     </row>
     <row r="84" spans="1:8">
       <c r="A84">
-        <v>11050</v>
+        <v>11060</v>
       </c>
       <c r="B84" t="str">
         <f>INDEX(TextData!B:B,MATCH(A84,TextData!A:A))</f>
-        <v>イグナイテッド</v>
+        <v>ライジングファイア</v>
       </c>
       <c r="C84">
         <v>4020</v>
@@ -24917,10 +24916,10 @@
         <v>Ct回復</v>
       </c>
       <c r="E84">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F84">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G84">
         <v>0</v>
@@ -24929,41 +24928,45 @@
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="1:8">
+    <row r="85" spans="1:9">
       <c r="A85">
-        <v>11060</v>
+        <v>11070</v>
       </c>
       <c r="B85" t="str">
         <f>INDEX(TextData!B:B,MATCH(A85,TextData!A:A))</f>
-        <v>ライジングファイア</v>
+        <v>ルージュバック</v>
       </c>
       <c r="C85">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="D85" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C85,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E85">
-        <v>1</v>
+        <v>1044</v>
       </c>
       <c r="F85">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G85">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H85">
         <v>100</v>
       </c>
+      <c r="I85" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E85,[1]TextData!A:A))</f>
+        <v>攻撃アップ</v>
+      </c>
     </row>
     <row r="86" spans="1:9">
       <c r="A86">
-        <v>11070</v>
+        <v>11080</v>
       </c>
       <c r="B86" t="str">
         <f>INDEX(TextData!B:B,MATCH(A86,TextData!A:A))</f>
-        <v>ルージュバック</v>
+        <v>パワーエール</v>
       </c>
       <c r="C86">
         <v>3010</v>
@@ -24973,13 +24976,13 @@
         <v>ステート付与</v>
       </c>
       <c r="E86">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="F86">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G86">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H86">
         <v>100</v>
@@ -24991,11 +24994,11 @@
     </row>
     <row r="87" spans="1:9">
       <c r="A87">
-        <v>11080</v>
+        <v>11090</v>
       </c>
       <c r="B87" t="str">
         <f>INDEX(TextData!B:B,MATCH(A87,TextData!A:A))</f>
-        <v>パワーエール</v>
+        <v>スレイプニル</v>
       </c>
       <c r="C87">
         <v>3010</v>
@@ -25005,29 +25008,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E87">
-        <v>1040</v>
+        <v>2330</v>
       </c>
       <c r="F87">
         <v>1</v>
       </c>
       <c r="G87">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="H87">
         <v>100</v>
       </c>
       <c r="I87" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E87,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
+        <v>貫通</v>
       </c>
     </row>
     <row r="88" spans="1:9">
       <c r="A88">
-        <v>11090</v>
+        <v>12010</v>
       </c>
       <c r="B88" t="str">
         <f>INDEX(TextData!B:B,MATCH(A88,TextData!A:A))</f>
-        <v>スレイプニル</v>
+        <v>エクステンション</v>
       </c>
       <c r="C88">
         <v>3010</v>
@@ -25037,29 +25040,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E88">
-        <v>2330</v>
+        <v>2190</v>
       </c>
       <c r="F88">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G88">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H88">
         <v>100</v>
       </c>
       <c r="I88" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E88,[1]TextData!A:A))</f>
-        <v>貫通</v>
+        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="89" spans="1:9">
       <c r="A89">
-        <v>12010</v>
+        <v>12020</v>
       </c>
       <c r="B89" t="str">
         <f>INDEX(TextData!B:B,MATCH(A89,TextData!A:A))</f>
-        <v>エクステンション</v>
+        <v>ヘブンリーラック</v>
       </c>
       <c r="C89">
         <v>3010</v>
@@ -25069,29 +25072,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E89">
-        <v>2190</v>
+        <v>1090</v>
       </c>
       <c r="F89">
         <v>999</v>
       </c>
       <c r="G89">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H89">
         <v>100</v>
       </c>
       <c r="I89" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E89,[1]TextData!A:A))</f>
-        <v>対象範囲延長</v>
+        <v>回避アップ</v>
       </c>
     </row>
     <row r="90" spans="1:9">
       <c r="A90">
-        <v>12020</v>
+        <v>12030</v>
       </c>
       <c r="B90" t="str">
         <f>INDEX(TextData!B:B,MATCH(A90,TextData!A:A))</f>
-        <v>ヘブンリーラック</v>
+        <v>スウィフトカレント</v>
       </c>
       <c r="C90">
         <v>3010</v>
@@ -25101,29 +25104,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E90">
-        <v>1090</v>
+        <v>1060</v>
       </c>
       <c r="F90">
         <v>999</v>
       </c>
       <c r="G90">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="H90">
         <v>100</v>
       </c>
       <c r="I90" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E90,[1]TextData!A:A))</f>
-        <v>回避アップ</v>
+        <v>速度アップ</v>
       </c>
     </row>
     <row r="91" spans="1:9">
       <c r="A91">
-        <v>12030</v>
+        <v>12040</v>
       </c>
       <c r="B91" t="str">
         <f>INDEX(TextData!B:B,MATCH(A91,TextData!A:A))</f>
-        <v>スウィフトカレント</v>
+        <v>イヴェイドオール</v>
       </c>
       <c r="C91">
         <v>3010</v>
@@ -25133,7 +25136,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E91">
-        <v>1060</v>
+        <v>1092</v>
       </c>
       <c r="F91">
         <v>999</v>
@@ -25146,58 +25149,54 @@
       </c>
       <c r="I91" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E91,[1]TextData!A:A))</f>
-        <v>速度アップ</v>
-      </c>
-    </row>
-    <row r="92" spans="1:9">
+        <v>回避アップ</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
       <c r="A92">
-        <v>12040</v>
+        <v>12050</v>
       </c>
       <c r="B92" t="str">
         <f>INDEX(TextData!B:B,MATCH(A92,TextData!A:A))</f>
-        <v>イヴェイドオール</v>
+        <v>クイックムーブ</v>
       </c>
       <c r="C92">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="D92" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C92,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ap回復</v>
       </c>
       <c r="E92">
-        <v>1092</v>
+        <v>200</v>
       </c>
       <c r="F92">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G92">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H92">
         <v>100</v>
       </c>
-      <c r="I92" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E92,[1]TextData!A:A))</f>
-        <v>回避アップ</v>
-      </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93">
-        <v>12050</v>
+        <v>12060</v>
       </c>
       <c r="B93" t="str">
         <f>INDEX(TextData!B:B,MATCH(A93,TextData!A:A))</f>
-        <v>クイックムーブ</v>
+        <v>チェイスマジック</v>
       </c>
       <c r="C93">
-        <v>5020</v>
+        <v>1010</v>
       </c>
       <c r="D93" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C93,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E93">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="F93">
         <v>0</v>
@@ -25209,35 +25208,39 @@
         <v>100</v>
       </c>
     </row>
-    <row r="94" spans="1:8">
+    <row r="94" spans="1:9">
       <c r="A94">
-        <v>12060</v>
+        <v>12070</v>
       </c>
       <c r="B94" t="str">
         <f>INDEX(TextData!B:B,MATCH(A94,TextData!A:A))</f>
-        <v>チェイスマジック</v>
+        <v>ソーサリーコネクト</v>
       </c>
       <c r="C94">
-        <v>1010</v>
+        <v>3010</v>
       </c>
       <c r="D94" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C94,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E94">
-        <v>100</v>
+        <v>1040</v>
       </c>
       <c r="F94">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G94">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H94">
         <v>100</v>
       </c>
-    </row>
-    <row r="95" spans="1:9">
+      <c r="I94" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E94,[1]TextData!A:A))</f>
+        <v>攻撃アップ</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
       <c r="A95">
         <v>12070</v>
       </c>
@@ -25246,106 +25249,102 @@
         <v>ソーサリーコネクト</v>
       </c>
       <c r="C95">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D95" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C95,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E95">
-        <v>1040</v>
+        <v>12071</v>
       </c>
       <c r="F95">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G95">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H95">
         <v>100</v>
       </c>
-      <c r="I95" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E95,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
-    </row>
-    <row r="96" spans="1:8">
+    </row>
+    <row r="96" spans="1:9">
       <c r="A96">
-        <v>12070</v>
+        <v>12071</v>
       </c>
       <c r="B96" t="str">
         <f>INDEX(TextData!B:B,MATCH(A96,TextData!A:A))</f>
         <v>ソーサリーコネクト</v>
       </c>
       <c r="C96">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D96" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C96,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E96">
-        <v>12071</v>
+        <v>1041</v>
       </c>
       <c r="F96">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G96">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H96">
         <v>100</v>
       </c>
-    </row>
-    <row r="97" spans="1:9">
+      <c r="I96" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E96,[1]TextData!A:A))</f>
+        <v>攻撃ダウン</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
       <c r="A97">
-        <v>12071</v>
+        <v>12080</v>
       </c>
       <c r="B97" t="str">
         <f>INDEX(TextData!B:B,MATCH(A97,TextData!A:A))</f>
-        <v>ソーサリーコネクト</v>
+        <v>ウィンドライズ</v>
       </c>
       <c r="C97">
-        <v>3010</v>
+        <v>1010</v>
       </c>
       <c r="D97" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C97,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E97">
-        <v>1041</v>
+        <v>150</v>
       </c>
       <c r="F97">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G97">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H97">
         <v>100</v>
       </c>
-      <c r="I97" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E97,[1]TextData!A:A))</f>
-        <v>攻撃ダウン</v>
-      </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98">
-        <v>12080</v>
+        <v>12090</v>
       </c>
       <c r="B98" t="str">
         <f>INDEX(TextData!B:B,MATCH(A98,TextData!A:A))</f>
-        <v>ウィンドライズ</v>
+        <v>アウトオブオーダー</v>
       </c>
       <c r="C98">
-        <v>1010</v>
+        <v>5020</v>
       </c>
       <c r="D98" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C98,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>Ap回復</v>
       </c>
       <c r="E98">
-        <v>150</v>
+        <v>200</v>
       </c>
       <c r="F98">
         <v>0</v>
@@ -25357,41 +25356,45 @@
         <v>100</v>
       </c>
     </row>
-    <row r="99" spans="1:8">
+    <row r="99" spans="1:9">
       <c r="A99">
-        <v>12090</v>
+        <v>13010</v>
       </c>
       <c r="B99" t="str">
         <f>INDEX(TextData!B:B,MATCH(A99,TextData!A:A))</f>
-        <v>アウトオブオーダー</v>
+        <v>アーマーコード</v>
       </c>
       <c r="C99">
-        <v>5020</v>
+        <v>3010</v>
       </c>
       <c r="D99" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C99,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E99">
-        <v>200</v>
+        <v>1050</v>
       </c>
       <c r="F99">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G99">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H99">
         <v>100</v>
       </c>
+      <c r="I99" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E99,[1]TextData!A:A))</f>
+        <v>防御アップ</v>
+      </c>
     </row>
     <row r="100" spans="1:9">
       <c r="A100">
-        <v>13010</v>
+        <v>13020</v>
       </c>
       <c r="B100" t="str">
         <f>INDEX(TextData!B:B,MATCH(A100,TextData!A:A))</f>
-        <v>アーマーコード</v>
+        <v>クイックバリア</v>
       </c>
       <c r="C100">
         <v>3010</v>
@@ -25401,89 +25404,89 @@
         <v>ステート付与</v>
       </c>
       <c r="E100">
-        <v>1050</v>
+        <v>1100</v>
       </c>
       <c r="F100">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G100">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H100">
         <v>100</v>
       </c>
       <c r="I100" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E100,[1]TextData!A:A))</f>
-        <v>防御アップ</v>
-      </c>
-    </row>
-    <row r="101" spans="1:9">
+        <v>ダメージカット</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
       <c r="A101">
-        <v>13020</v>
+        <v>13030</v>
       </c>
       <c r="B101" t="str">
         <f>INDEX(TextData!B:B,MATCH(A101,TextData!A:A))</f>
-        <v>クイックバリア</v>
+        <v>クイックキュア</v>
       </c>
       <c r="C101">
-        <v>3010</v>
+        <v>3030</v>
       </c>
       <c r="D101" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C101,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Abnormalステート解除</v>
       </c>
       <c r="E101">
-        <v>1100</v>
+        <v>0</v>
       </c>
       <c r="F101">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G101">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H101">
         <v>100</v>
       </c>
-      <c r="I101" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E101,[1]TextData!A:A))</f>
-        <v>ダメージカット</v>
-      </c>
-    </row>
-    <row r="102" spans="1:8">
+    </row>
+    <row r="102" spans="1:9">
       <c r="A102">
-        <v>13030</v>
+        <v>13040</v>
       </c>
       <c r="B102" t="str">
         <f>INDEX(TextData!B:B,MATCH(A102,TextData!A:A))</f>
-        <v>クイックキュア</v>
+        <v>セルフシールド</v>
       </c>
       <c r="C102">
-        <v>3030</v>
+        <v>3010</v>
       </c>
       <c r="D102" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C102,Define!P:P))</f>
-        <v>Abnormalステート解除</v>
+        <v>ステート付与</v>
       </c>
       <c r="E102">
-        <v>0</v>
+        <v>1100</v>
       </c>
       <c r="F102">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G102">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H102">
         <v>100</v>
       </c>
+      <c r="I102" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E102,[1]TextData!A:A))</f>
+        <v>ダメージカット</v>
+      </c>
     </row>
     <row r="103" spans="1:9">
       <c r="A103">
-        <v>13040</v>
+        <v>13050</v>
       </c>
       <c r="B103" t="str">
         <f>INDEX(TextData!B:B,MATCH(A103,TextData!A:A))</f>
-        <v>セルフシールド</v>
+        <v>パッシブジャミング</v>
       </c>
       <c r="C103">
         <v>3010</v>
@@ -25493,29 +25496,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E103">
-        <v>1100</v>
+        <v>2090</v>
       </c>
       <c r="F103">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G103">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H103">
         <v>100</v>
       </c>
       <c r="I103" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E103,[1]TextData!A:A))</f>
-        <v>ダメージカット</v>
+        <v>パッシブ封じ</v>
       </c>
     </row>
     <row r="104" spans="1:9">
       <c r="A104">
-        <v>13050</v>
+        <v>13060</v>
       </c>
       <c r="B104" t="str">
         <f>INDEX(TextData!B:B,MATCH(A104,TextData!A:A))</f>
-        <v>パッシブジャミング</v>
+        <v>サプライカバー</v>
       </c>
       <c r="C104">
         <v>3010</v>
@@ -25525,10 +25528,10 @@
         <v>ステート付与</v>
       </c>
       <c r="E104">
-        <v>2090</v>
+        <v>2430</v>
       </c>
       <c r="F104">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G104">
         <v>0</v>
@@ -25538,29 +25541,29 @@
       </c>
       <c r="I104" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E104,[1]TextData!A:A))</f>
-        <v>パッシブ封じ</v>
-      </c>
-    </row>
-    <row r="105" spans="1:9">
+        <v>かばう</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
       <c r="A105">
-        <v>13060</v>
+        <v>13070</v>
       </c>
       <c r="B105" t="str">
         <f>INDEX(TextData!B:B,MATCH(A105,TextData!A:A))</f>
-        <v>サプライカバー</v>
+        <v>アシッドラッシュ</v>
       </c>
       <c r="C105">
-        <v>3010</v>
+        <v>5050</v>
       </c>
       <c r="D105" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C105,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>APダメージ</v>
       </c>
       <c r="E105">
-        <v>2430</v>
+        <v>200</v>
       </c>
       <c r="F105">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G105">
         <v>0</v>
@@ -25568,46 +25571,46 @@
       <c r="H105">
         <v>100</v>
       </c>
-      <c r="I105" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E105,[1]TextData!A:A))</f>
-        <v>かばう</v>
-      </c>
-    </row>
-    <row r="106" spans="1:8">
+    </row>
+    <row r="106" spans="1:9">
       <c r="A106">
-        <v>13070</v>
+        <v>13080</v>
       </c>
       <c r="B106" t="str">
         <f>INDEX(TextData!B:B,MATCH(A106,TextData!A:A))</f>
-        <v>アシッドラッシュ</v>
+        <v>ライフスティール</v>
       </c>
       <c r="C106">
-        <v>5050</v>
+        <v>3010</v>
       </c>
       <c r="D106" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C106,Define!P:P))</f>
-        <v>APダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E106">
-        <v>200</v>
+        <v>2060</v>
       </c>
       <c r="F106">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G106">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H106">
         <v>100</v>
       </c>
+      <c r="I106" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E106,[1]TextData!A:A))</f>
+        <v>ドレイン</v>
+      </c>
     </row>
     <row r="107" spans="1:9">
       <c r="A107">
-        <v>13080</v>
+        <v>13090</v>
       </c>
       <c r="B107" t="str">
         <f>INDEX(TextData!B:B,MATCH(A107,TextData!A:A))</f>
-        <v>ライフスティール</v>
+        <v>アイスセイバー</v>
       </c>
       <c r="C107">
         <v>3010</v>
@@ -25617,7 +25620,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E107">
-        <v>2060</v>
+        <v>2140</v>
       </c>
       <c r="F107">
         <v>1</v>
@@ -25630,16 +25633,16 @@
       </c>
       <c r="I107" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E107,[1]TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>凍結</v>
       </c>
     </row>
     <row r="108" spans="1:9">
       <c r="A108">
-        <v>13090</v>
+        <v>14010</v>
       </c>
       <c r="B108" t="str">
         <f>INDEX(TextData!B:B,MATCH(A108,TextData!A:A))</f>
-        <v>アイスセイバー</v>
+        <v>ディバインシールド</v>
       </c>
       <c r="C108">
         <v>3010</v>
@@ -25649,89 +25652,89 @@
         <v>ステート付与</v>
       </c>
       <c r="E108">
-        <v>2140</v>
+        <v>2180</v>
       </c>
       <c r="F108">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G108">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H108">
         <v>100</v>
       </c>
       <c r="I108" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E108,[1]TextData!A:A))</f>
-        <v>凍結</v>
-      </c>
-    </row>
-    <row r="109" spans="1:9">
+        <v>状態異常回避</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8">
       <c r="A109">
-        <v>14010</v>
+        <v>14020</v>
       </c>
       <c r="B109" t="str">
         <f>INDEX(TextData!B:B,MATCH(A109,TextData!A:A))</f>
-        <v>ディバインシールド</v>
+        <v>ライフディバイド</v>
       </c>
       <c r="C109">
-        <v>3010</v>
+        <v>2040</v>
       </c>
       <c r="D109" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C109,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hpを分け与える</v>
       </c>
       <c r="E109">
-        <v>2180</v>
+        <v>25</v>
       </c>
       <c r="F109">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G109">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H109">
         <v>100</v>
       </c>
-      <c r="I109" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E109,[1]TextData!A:A))</f>
-        <v>状態異常回避</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8">
+    </row>
+    <row r="110" spans="1:9">
       <c r="A110">
-        <v>14020</v>
+        <v>14030</v>
       </c>
       <c r="B110" t="str">
         <f>INDEX(TextData!B:B,MATCH(A110,TextData!A:A))</f>
-        <v>ライフディバイド</v>
+        <v>エイミングスコープ</v>
       </c>
       <c r="C110">
-        <v>2040</v>
+        <v>3010</v>
       </c>
       <c r="D110" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C110,Define!P:P))</f>
-        <v>Hpを分け与える</v>
+        <v>ステート付与</v>
       </c>
       <c r="E110">
-        <v>25</v>
+        <v>1081</v>
       </c>
       <c r="F110">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G110">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="H110">
         <v>100</v>
       </c>
+      <c r="I110" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E110,[1]TextData!A:A))</f>
+        <v>命中アップ</v>
+      </c>
     </row>
     <row r="111" spans="1:9">
       <c r="A111">
-        <v>14030</v>
+        <v>14040</v>
       </c>
       <c r="B111" t="str">
         <f>INDEX(TextData!B:B,MATCH(A111,TextData!A:A))</f>
-        <v>エイミングスコープ</v>
+        <v>リジェネレーション</v>
       </c>
       <c r="C111">
         <v>3010</v>
@@ -25741,7 +25744,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E111">
-        <v>1081</v>
+        <v>2040</v>
       </c>
       <c r="F111">
         <v>999</v>
@@ -25754,16 +25757,16 @@
       </c>
       <c r="I111" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E111,[1]TextData!A:A))</f>
-        <v>命中アップ</v>
+        <v>リジェネ</v>
       </c>
     </row>
     <row r="112" spans="1:9">
       <c r="A112">
-        <v>14040</v>
+        <v>14050</v>
       </c>
       <c r="B112" t="str">
         <f>INDEX(TextData!B:B,MATCH(A112,TextData!A:A))</f>
-        <v>リジェネレーション</v>
+        <v>ホープフルアイリス</v>
       </c>
       <c r="C112">
         <v>3010</v>
@@ -25773,74 +25776,70 @@
         <v>ステート付与</v>
       </c>
       <c r="E112">
-        <v>2040</v>
+        <v>1020</v>
       </c>
       <c r="F112">
         <v>999</v>
       </c>
       <c r="G112">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="H112">
         <v>100</v>
       </c>
       <c r="I112" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E112,[1]TextData!A:A))</f>
-        <v>リジェネ</v>
-      </c>
-    </row>
-    <row r="113" spans="1:9">
+        <v>最大Hpアップ</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8">
       <c r="A113">
-        <v>14050</v>
+        <v>14060</v>
       </c>
       <c r="B113" t="str">
         <f>INDEX(TextData!B:B,MATCH(A113,TextData!A:A))</f>
-        <v>ホープフルアイリス</v>
+        <v>パッシブサプライ</v>
       </c>
       <c r="C113">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="D113" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C113,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ct回復</v>
       </c>
       <c r="E113">
-        <v>1020</v>
+        <v>1</v>
       </c>
       <c r="F113">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G113">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H113">
         <v>100</v>
       </c>
-      <c r="I113" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E113,[1]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
-      </c>
-    </row>
-    <row r="114" spans="1:8">
+    </row>
+    <row r="114" spans="1:9">
       <c r="A114">
-        <v>14060</v>
+        <v>14070</v>
       </c>
       <c r="B114" t="str">
         <f>INDEX(TextData!B:B,MATCH(A114,TextData!A:A))</f>
-        <v>パッシブサプライ</v>
+        <v>ホーミングクルセイド</v>
       </c>
       <c r="C114">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="D114" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C114,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E114">
-        <v>1</v>
+        <v>2240</v>
       </c>
       <c r="F114">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G114">
         <v>0</v>
@@ -25848,27 +25847,31 @@
       <c r="H114">
         <v>100</v>
       </c>
-    </row>
-    <row r="115" spans="1:9">
+      <c r="I114" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E114,[1]TextData!A:A))</f>
+        <v>必中</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8">
       <c r="A115">
-        <v>14070</v>
+        <v>14080</v>
       </c>
       <c r="B115" t="str">
         <f>INDEX(TextData!B:B,MATCH(A115,TextData!A:A))</f>
-        <v>ホーミングクルセイド</v>
+        <v>クイックヒール</v>
       </c>
       <c r="C115">
-        <v>3010</v>
+        <v>2010</v>
       </c>
       <c r="D115" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C115,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp回復</v>
       </c>
       <c r="E115">
-        <v>2240</v>
+        <v>10</v>
       </c>
       <c r="F115">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G115">
         <v>0</v>
@@ -25876,46 +25879,46 @@
       <c r="H115">
         <v>100</v>
       </c>
-      <c r="I115" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E115,[1]TextData!A:A))</f>
-        <v>必中</v>
-      </c>
-    </row>
-    <row r="116" spans="1:8">
+    </row>
+    <row r="116" spans="1:9">
       <c r="A116">
-        <v>14080</v>
+        <v>14090</v>
       </c>
       <c r="B116" t="str">
         <f>INDEX(TextData!B:B,MATCH(A116,TextData!A:A))</f>
-        <v>クイックヒール</v>
+        <v>リレイズ</v>
       </c>
       <c r="C116">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="D116" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C116,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E116">
-        <v>10</v>
+        <v>2450</v>
       </c>
       <c r="F116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G116">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H116">
         <v>100</v>
       </c>
+      <c r="I116" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E116,[1]TextData!A:A))</f>
+        <v>不死</v>
+      </c>
     </row>
     <row r="117" spans="1:9">
       <c r="A117">
-        <v>14090</v>
+        <v>15010</v>
       </c>
       <c r="B117" t="str">
         <f>INDEX(TextData!B:B,MATCH(A117,TextData!A:A))</f>
-        <v>リレイズ</v>
+        <v>イーグルアイ</v>
       </c>
       <c r="C117">
         <v>3010</v>
@@ -25925,29 +25928,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E117">
-        <v>2450</v>
+        <v>1070</v>
       </c>
       <c r="F117">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G117">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H117">
         <v>100</v>
       </c>
       <c r="I117" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E117,[1]TextData!A:A))</f>
-        <v>不死</v>
+        <v>会心率アップ</v>
       </c>
     </row>
     <row r="118" spans="1:9">
       <c r="A118">
-        <v>15010</v>
+        <v>15020</v>
       </c>
       <c r="B118" t="str">
         <f>INDEX(TextData!B:B,MATCH(A118,TextData!A:A))</f>
-        <v>イーグルアイ</v>
+        <v>ネヴァーエンド</v>
       </c>
       <c r="C118">
         <v>3010</v>
@@ -25963,7 +25966,7 @@
         <v>999</v>
       </c>
       <c r="G118">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="H118">
         <v>100</v>
@@ -25973,73 +25976,73 @@
         <v>会心率アップ</v>
       </c>
     </row>
-    <row r="119" spans="1:9">
+    <row r="119" spans="1:8">
       <c r="A119">
-        <v>15020</v>
+        <v>15030</v>
       </c>
       <c r="B119" t="str">
         <f>INDEX(TextData!B:B,MATCH(A119,TextData!A:A))</f>
-        <v>ネヴァーエンド</v>
+        <v>グレイブアクト</v>
       </c>
       <c r="C119">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="D119" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C119,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ct回復</v>
       </c>
       <c r="E119">
-        <v>1070</v>
+        <v>2</v>
       </c>
       <c r="F119">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G119">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H119">
         <v>100</v>
       </c>
-      <c r="I119" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E119,[1]TextData!A:A))</f>
-        <v>会心率アップ</v>
-      </c>
-    </row>
-    <row r="120" spans="1:8">
+    </row>
+    <row r="120" spans="1:9">
       <c r="A120">
-        <v>15030</v>
+        <v>15040</v>
       </c>
       <c r="B120" t="str">
         <f>INDEX(TextData!B:B,MATCH(A120,TextData!A:A))</f>
-        <v>グレイブアクト</v>
+        <v>スカルグラッジ</v>
       </c>
       <c r="C120">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="D120" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C120,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E120">
-        <v>2</v>
+        <v>2220</v>
       </c>
       <c r="F120">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G120">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H120">
         <v>100</v>
       </c>
+      <c r="I120" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E120,[1]TextData!A:A))</f>
+        <v>即死付与</v>
+      </c>
     </row>
     <row r="121" spans="1:9">
       <c r="A121">
-        <v>15040</v>
+        <v>15050</v>
       </c>
       <c r="B121" t="str">
         <f>INDEX(TextData!B:B,MATCH(A121,TextData!A:A))</f>
-        <v>スカルグラッジ</v>
+        <v>ネガティブドレイン</v>
       </c>
       <c r="C121">
         <v>3010</v>
@@ -26049,29 +26052,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E121">
-        <v>2220</v>
+        <v>2060</v>
       </c>
       <c r="F121">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G121">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H121">
         <v>100</v>
       </c>
       <c r="I121" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E121,[1]TextData!A:A))</f>
-        <v>即死付与</v>
+        <v>ドレイン</v>
       </c>
     </row>
     <row r="122" spans="1:9">
       <c r="A122">
-        <v>15050</v>
+        <v>15060</v>
       </c>
       <c r="B122" t="str">
         <f>INDEX(TextData!B:B,MATCH(A122,TextData!A:A))</f>
-        <v>ネガティブドレイン</v>
+        <v>アンデッドペイン</v>
       </c>
       <c r="C122">
         <v>3010</v>
@@ -26081,29 +26084,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E122">
-        <v>2060</v>
+        <v>2270</v>
       </c>
       <c r="F122">
         <v>0</v>
       </c>
       <c r="G122">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="H122">
         <v>100</v>
       </c>
       <c r="I122" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E122,[1]TextData!A:A))</f>
-        <v>ドレイン</v>
+        <v>アンデッド</v>
       </c>
     </row>
     <row r="123" spans="1:9">
       <c r="A123">
-        <v>15060</v>
+        <v>15070</v>
       </c>
       <c r="B123" t="str">
         <f>INDEX(TextData!B:B,MATCH(A123,TextData!A:A))</f>
-        <v>アンデッドペイン</v>
+        <v>ジャックポッド</v>
       </c>
       <c r="C123">
         <v>3010</v>
@@ -26113,20 +26116,20 @@
         <v>ステート付与</v>
       </c>
       <c r="E123">
-        <v>2270</v>
+        <v>1070</v>
       </c>
       <c r="F123">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G123">
-        <v>7</v>
+        <v>50</v>
       </c>
       <c r="H123">
         <v>100</v>
       </c>
       <c r="I123" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E123,[1]TextData!A:A))</f>
-        <v>アンデッド</v>
+        <v>会心率アップ</v>
       </c>
     </row>
     <row r="124" spans="1:9">
@@ -26145,7 +26148,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E124">
-        <v>1070</v>
+        <v>1082</v>
       </c>
       <c r="F124">
         <v>1</v>
@@ -26158,76 +26161,76 @@
       </c>
       <c r="I124" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E124,[1]TextData!A:A))</f>
-        <v>会心率アップ</v>
-      </c>
-    </row>
-    <row r="125" spans="1:9">
+        <v>命中ダウン</v>
+      </c>
+    </row>
+    <row r="125" spans="1:8">
       <c r="A125">
-        <v>15070</v>
+        <v>15080</v>
       </c>
       <c r="B125" t="str">
         <f>INDEX(TextData!B:B,MATCH(A125,TextData!A:A))</f>
-        <v>ジャックポッド</v>
+        <v>ヒールハント</v>
       </c>
       <c r="C125">
-        <v>3010</v>
+        <v>1100</v>
       </c>
       <c r="D125" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C125,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp貫通ダメージ</v>
       </c>
       <c r="E125">
-        <v>1082</v>
+        <v>100</v>
       </c>
       <c r="F125">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G125">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="H125">
         <v>100</v>
       </c>
-      <c r="I125" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E125,[1]TextData!A:A))</f>
-        <v>命中ダウン</v>
-      </c>
-    </row>
-    <row r="126" spans="1:8">
+    </row>
+    <row r="126" spans="1:9">
       <c r="A126">
-        <v>15080</v>
+        <v>15090</v>
       </c>
       <c r="B126" t="str">
         <f>INDEX(TextData!B:B,MATCH(A126,TextData!A:A))</f>
-        <v>ヒールハント</v>
+        <v>クイックカース</v>
       </c>
       <c r="C126">
-        <v>1100</v>
+        <v>3010</v>
       </c>
       <c r="D126" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C126,Define!P:P))</f>
-        <v>Hp貫通ダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E126">
-        <v>100</v>
+        <v>1043</v>
       </c>
       <c r="F126">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G126">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H126">
         <v>100</v>
       </c>
+      <c r="I126" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E126,[1]TextData!A:A))</f>
+        <v>攻撃%ダウン</v>
+      </c>
     </row>
     <row r="127" spans="1:9">
       <c r="A127">
-        <v>15090</v>
+        <v>100110</v>
       </c>
       <c r="B127" t="str">
         <f>INDEX(TextData!B:B,MATCH(A127,TextData!A:A))</f>
-        <v>クイックカース</v>
+        <v>ソーイングアームド</v>
       </c>
       <c r="C127">
         <v>3010</v>
@@ -26237,23 +26240,23 @@
         <v>ステート付与</v>
       </c>
       <c r="E127">
-        <v>1043</v>
+        <v>2330</v>
       </c>
       <c r="F127">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G127">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H127">
         <v>100</v>
       </c>
       <c r="I127" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E127,[1]TextData!A:A))</f>
-        <v>攻撃%ダウン</v>
-      </c>
-    </row>
-    <row r="128" spans="1:9">
+        <v>貫通</v>
+      </c>
+    </row>
+    <row r="128" spans="1:8">
       <c r="A128">
         <v>100110</v>
       </c>
@@ -26262,46 +26265,42 @@
         <v>ソーイングアームド</v>
       </c>
       <c r="C128">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D128" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C128,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E128">
-        <v>2330</v>
+        <v>11</v>
       </c>
       <c r="F128">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G128">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H128">
         <v>100</v>
       </c>
-      <c r="I128" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E128,[1]TextData!A:A))</f>
-        <v>貫通</v>
-      </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129">
-        <v>100110</v>
+        <v>100120</v>
       </c>
       <c r="B129" t="str">
         <f>INDEX(TextData!B:B,MATCH(A129,TextData!A:A))</f>
-        <v>ソーイングアームド</v>
+        <v>エターナルロンド</v>
       </c>
       <c r="C129">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D129" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C129,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E129">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="F129">
         <v>0</v>
@@ -26322,14 +26321,14 @@
         <v>エターナルロンド</v>
       </c>
       <c r="C130">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D130" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C130,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E130">
-        <v>400</v>
+        <v>21</v>
       </c>
       <c r="F130">
         <v>0</v>
@@ -26341,35 +26340,39 @@
         <v>100</v>
       </c>
     </row>
-    <row r="131" spans="1:8">
+    <row r="131" spans="1:9">
       <c r="A131">
-        <v>100120</v>
+        <v>100210</v>
       </c>
       <c r="B131" t="str">
         <f>INDEX(TextData!B:B,MATCH(A131,TextData!A:A))</f>
-        <v>エターナルロンド</v>
+        <v>アブソリュートパリィ</v>
       </c>
       <c r="C131">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D131" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C131,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E131">
-        <v>21</v>
+        <v>1090</v>
       </c>
       <c r="F131">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G131">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H131">
         <v>100</v>
       </c>
-    </row>
-    <row r="132" spans="1:9">
+      <c r="I131" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E131,[1]TextData!A:A))</f>
+        <v>回避アップ</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8">
       <c r="A132">
         <v>100210</v>
       </c>
@@ -26378,46 +26381,42 @@
         <v>アブソリュートパリィ</v>
       </c>
       <c r="C132">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D132" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C132,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E132">
-        <v>1090</v>
+        <v>11</v>
       </c>
       <c r="F132">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G132">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H132">
         <v>100</v>
       </c>
-      <c r="I132" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E132,[1]TextData!A:A))</f>
-        <v>回避アップ</v>
-      </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133">
-        <v>100210</v>
+        <v>100220</v>
       </c>
       <c r="B133" t="str">
         <f>INDEX(TextData!B:B,MATCH(A133,TextData!A:A))</f>
-        <v>アブソリュートパリィ</v>
+        <v>レヴェリー</v>
       </c>
       <c r="C133">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D133" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C133,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E133">
-        <v>11</v>
+        <v>50</v>
       </c>
       <c r="F133">
         <v>0</v>
@@ -26438,14 +26437,14 @@
         <v>レヴェリー</v>
       </c>
       <c r="C134">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D134" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C134,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E134">
-        <v>50</v>
+        <v>21</v>
       </c>
       <c r="F134">
         <v>0</v>
@@ -26457,26 +26456,26 @@
         <v>100</v>
       </c>
     </row>
-    <row r="135" spans="1:8">
+    <row r="135" spans="1:9">
       <c r="A135">
-        <v>100220</v>
+        <v>100310</v>
       </c>
       <c r="B135" t="str">
         <f>INDEX(TextData!B:B,MATCH(A135,TextData!A:A))</f>
-        <v>レヴェリー</v>
+        <v>セイクリッドバリア</v>
       </c>
       <c r="C135">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D135" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C135,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E135">
-        <v>21</v>
+        <v>2050</v>
       </c>
       <c r="F135">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G135">
         <v>0</v>
@@ -26484,8 +26483,12 @@
       <c r="H135">
         <v>100</v>
       </c>
-    </row>
-    <row r="136" spans="1:9">
+      <c r="I135" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E135,[1]TextData!A:A))</f>
+        <v>攻撃無効</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8">
       <c r="A136">
         <v>100310</v>
       </c>
@@ -26494,17 +26497,17 @@
         <v>セイクリッドバリア</v>
       </c>
       <c r="C136">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D136" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C136,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E136">
-        <v>2050</v>
+        <v>11</v>
       </c>
       <c r="F136">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G136">
         <v>0</v>
@@ -26512,28 +26515,24 @@
       <c r="H136">
         <v>100</v>
       </c>
-      <c r="I136" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E136,[1]TextData!A:A))</f>
-        <v>攻撃無効</v>
-      </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137">
-        <v>100310</v>
+        <v>100320</v>
       </c>
       <c r="B137" t="str">
         <f>INDEX(TextData!B:B,MATCH(A137,TextData!A:A))</f>
-        <v>セイクリッドバリア</v>
+        <v>リベンジニードル</v>
       </c>
       <c r="C137">
-        <v>7010</v>
+        <v>1090</v>
       </c>
       <c r="D137" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C137,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>受けたダメージ総計ダメージ</v>
       </c>
       <c r="E137">
-        <v>11</v>
+        <v>100</v>
       </c>
       <c r="F137">
         <v>0</v>
@@ -26554,14 +26553,14 @@
         <v>リベンジニードル</v>
       </c>
       <c r="C138">
-        <v>1090</v>
+        <v>7010</v>
       </c>
       <c r="D138" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C138,Define!P:P))</f>
-        <v>受けたダメージ総計ダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E138">
-        <v>100</v>
+        <v>21</v>
       </c>
       <c r="F138">
         <v>0</v>
@@ -26573,23 +26572,23 @@
         <v>100</v>
       </c>
     </row>
-    <row r="139" spans="1:8">
+    <row r="139" spans="1:9">
       <c r="A139">
-        <v>100320</v>
+        <v>100410</v>
       </c>
       <c r="B139" t="str">
         <f>INDEX(TextData!B:B,MATCH(A139,TextData!A:A))</f>
-        <v>リベンジニードル</v>
+        <v>アバンデンス</v>
       </c>
       <c r="C139">
-        <v>7010</v>
+        <v>3020</v>
       </c>
       <c r="D139" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C139,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート解除</v>
       </c>
       <c r="E139">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="F139">
         <v>0</v>
@@ -26600,8 +26599,12 @@
       <c r="H139">
         <v>100</v>
       </c>
-    </row>
-    <row r="140" spans="1:9">
+      <c r="I139" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E139,[1]TextData!A:A))</f>
+        <v>戦闘不能</v>
+      </c>
+    </row>
+    <row r="140" spans="1:8">
       <c r="A140">
         <v>100410</v>
       </c>
@@ -26610,14 +26613,14 @@
         <v>アバンデンス</v>
       </c>
       <c r="C140">
-        <v>3020</v>
+        <v>2010</v>
       </c>
       <c r="D140" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C140,Define!P:P))</f>
-        <v>ステート解除</v>
+        <v>Hp回復</v>
       </c>
       <c r="E140">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="F140">
         <v>0</v>
@@ -26627,10 +26630,6 @@
       </c>
       <c r="H140">
         <v>100</v>
-      </c>
-      <c r="I140" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E140,[1]TextData!A:A))</f>
-        <v>戦闘不能</v>
       </c>
     </row>
     <row r="141" spans="1:8">
@@ -26642,14 +26641,14 @@
         <v>アバンデンス</v>
       </c>
       <c r="C141">
-        <v>2010</v>
+        <v>7010</v>
       </c>
       <c r="D141" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C141,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E141">
-        <v>25</v>
+        <v>11</v>
       </c>
       <c r="F141">
         <v>0</v>
@@ -26661,35 +26660,39 @@
         <v>100</v>
       </c>
     </row>
-    <row r="142" spans="1:8">
+    <row r="142" spans="1:9">
       <c r="A142">
-        <v>100410</v>
+        <v>100420</v>
       </c>
       <c r="B142" t="str">
         <f>INDEX(TextData!B:B,MATCH(A142,TextData!A:A))</f>
-        <v>アバンデンス</v>
+        <v>ハーヴェスト</v>
       </c>
       <c r="C142">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D142" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C142,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E142">
-        <v>11</v>
+        <v>2040</v>
       </c>
       <c r="F142">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G142">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H142">
         <v>100</v>
       </c>
-    </row>
-    <row r="143" spans="1:9">
+      <c r="I142" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E142,[1]TextData!A:A))</f>
+        <v>リジェネ</v>
+      </c>
+    </row>
+    <row r="143" spans="1:8">
       <c r="A143">
         <v>100420</v>
       </c>
@@ -26698,58 +26701,58 @@
         <v>ハーヴェスト</v>
       </c>
       <c r="C143">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D143" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C143,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E143">
-        <v>2040</v>
+        <v>21</v>
       </c>
       <c r="F143">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G143">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H143">
         <v>100</v>
       </c>
-      <c r="I143" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E143,[1]TextData!A:A))</f>
-        <v>リジェネ</v>
-      </c>
-    </row>
-    <row r="144" spans="1:8">
+    </row>
+    <row r="144" spans="1:9">
       <c r="A144">
-        <v>100420</v>
+        <v>100510</v>
       </c>
       <c r="B144" t="str">
         <f>INDEX(TextData!B:B,MATCH(A144,TextData!A:A))</f>
-        <v>ハーヴェスト</v>
+        <v>カースドブレイク</v>
       </c>
       <c r="C144">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D144" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C144,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E144">
-        <v>21</v>
+        <v>2470</v>
       </c>
       <c r="F144">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G144">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H144">
         <v>100</v>
       </c>
-    </row>
-    <row r="145" spans="1:9">
+      <c r="I144" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E144,[1]TextData!A:A))</f>
+        <v>呪詛</v>
+      </c>
+    </row>
+    <row r="145" spans="1:8">
       <c r="A145">
         <v>100510</v>
       </c>
@@ -26758,58 +26761,58 @@
         <v>カースドブレイク</v>
       </c>
       <c r="C145">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D145" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C145,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E145">
-        <v>2470</v>
+        <v>11</v>
       </c>
       <c r="F145">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G145">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H145">
         <v>100</v>
       </c>
-      <c r="I145" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E145,[1]TextData!A:A))</f>
-        <v>呪詛</v>
-      </c>
-    </row>
-    <row r="146" spans="1:8">
+    </row>
+    <row r="146" spans="1:9">
       <c r="A146">
-        <v>100510</v>
+        <v>100520</v>
       </c>
       <c r="B146" t="str">
         <f>INDEX(TextData!B:B,MATCH(A146,TextData!A:A))</f>
-        <v>カースドブレイク</v>
+        <v>ムーンライトレイ</v>
       </c>
       <c r="C146">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D146" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C146,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E146">
-        <v>11</v>
+        <v>2010</v>
       </c>
       <c r="F146">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G146">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H146">
         <v>100</v>
       </c>
-    </row>
-    <row r="147" spans="1:9">
+      <c r="I146" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E146,[1]TextData!A:A))</f>
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="147" spans="1:8">
       <c r="A147">
         <v>100520</v>
       </c>
@@ -26818,46 +26821,42 @@
         <v>ムーンライトレイ</v>
       </c>
       <c r="C147">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D147" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C147,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E147">
-        <v>2010</v>
+        <v>21</v>
       </c>
       <c r="F147">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G147">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H147">
         <v>100</v>
       </c>
-      <c r="I147" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E147,[1]TextData!A:A))</f>
-        <v>毒</v>
-      </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148">
-        <v>100520</v>
+        <v>100610</v>
       </c>
       <c r="B148" t="str">
         <f>INDEX(TextData!B:B,MATCH(A148,TextData!A:A))</f>
-        <v>ムーンライトレイ</v>
+        <v>サンフレイム</v>
       </c>
       <c r="C148">
-        <v>7010</v>
+        <v>4020</v>
       </c>
       <c r="D148" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C148,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Ct回復</v>
       </c>
       <c r="E148">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F148">
         <v>0</v>
@@ -26878,14 +26877,14 @@
         <v>サンフレイム</v>
       </c>
       <c r="C149">
-        <v>4020</v>
+        <v>7010</v>
       </c>
       <c r="D149" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C149,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E149">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="F149">
         <v>0</v>
@@ -26899,21 +26898,21 @@
     </row>
     <row r="150" spans="1:8">
       <c r="A150">
-        <v>100610</v>
+        <v>100620</v>
       </c>
       <c r="B150" t="str">
         <f>INDEX(TextData!B:B,MATCH(A150,TextData!A:A))</f>
-        <v>サンフレイム</v>
+        <v>フレイムタン</v>
       </c>
       <c r="C150">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D150" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C150,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E150">
-        <v>11</v>
+        <v>200</v>
       </c>
       <c r="F150">
         <v>0</v>
@@ -26934,14 +26933,14 @@
         <v>フレイムタン</v>
       </c>
       <c r="C151">
-        <v>1010</v>
+        <v>4010</v>
       </c>
       <c r="D151" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C151,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>Ctダメージ</v>
       </c>
       <c r="E151">
-        <v>200</v>
+        <v>2</v>
       </c>
       <c r="F151">
         <v>0</v>
@@ -26962,14 +26961,14 @@
         <v>フレイムタン</v>
       </c>
       <c r="C152">
-        <v>4010</v>
+        <v>7010</v>
       </c>
       <c r="D152" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C152,Define!P:P))</f>
-        <v>Ctダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E152">
-        <v>2</v>
+        <v>21</v>
       </c>
       <c r="F152">
         <v>0</v>
@@ -26981,26 +26980,26 @@
         <v>100</v>
       </c>
     </row>
-    <row r="153" spans="1:8">
+    <row r="153" spans="1:9">
       <c r="A153">
-        <v>100620</v>
+        <v>100710</v>
       </c>
       <c r="B153" t="str">
         <f>INDEX(TextData!B:B,MATCH(A153,TextData!A:A))</f>
-        <v>フレイムタン</v>
+        <v>ライズザフラッグ</v>
       </c>
       <c r="C153">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D153" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C153,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E153">
-        <v>21</v>
+        <v>2420</v>
       </c>
       <c r="F153">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G153">
         <v>0</v>
@@ -27008,8 +27007,12 @@
       <c r="H153">
         <v>100</v>
       </c>
-    </row>
-    <row r="154" spans="1:9">
+      <c r="I153" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E153,[1]TextData!A:A))</f>
+        <v>フォロー</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8">
       <c r="A154">
         <v>100710</v>
       </c>
@@ -27018,17 +27021,17 @@
         <v>ライズザフラッグ</v>
       </c>
       <c r="C154">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D154" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C154,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E154">
-        <v>2420</v>
+        <v>11</v>
       </c>
       <c r="F154">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G154">
         <v>0</v>
@@ -27036,37 +27039,37 @@
       <c r="H154">
         <v>100</v>
       </c>
-      <c r="I154" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E154,[1]TextData!A:A))</f>
-        <v>フォロー</v>
-      </c>
-    </row>
-    <row r="155" spans="1:8">
+    </row>
+    <row r="155" spans="1:9">
       <c r="A155">
-        <v>100710</v>
+        <v>100720</v>
       </c>
       <c r="B155" t="str">
         <f>INDEX(TextData!B:B,MATCH(A155,TextData!A:A))</f>
-        <v>ライズザフラッグ</v>
+        <v>オーバーリミット</v>
       </c>
       <c r="C155">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D155" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C155,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E155">
-        <v>11</v>
+        <v>1040</v>
       </c>
       <c r="F155">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G155">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H155">
         <v>100</v>
+      </c>
+      <c r="I155" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E155,[1]TextData!A:A))</f>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="156" spans="1:9">
@@ -27085,7 +27088,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E156">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="F156">
         <v>999</v>
@@ -27098,10 +27101,10 @@
       </c>
       <c r="I156" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E156,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
-    </row>
-    <row r="157" spans="1:9">
+        <v>防御アップ</v>
+      </c>
+    </row>
+    <row r="157" spans="1:8">
       <c r="A157">
         <v>100720</v>
       </c>
@@ -27110,55 +27113,55 @@
         <v>オーバーリミット</v>
       </c>
       <c r="C157">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D157" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C157,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E157">
-        <v>1050</v>
+        <v>21</v>
       </c>
       <c r="F157">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G157">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H157">
         <v>100</v>
       </c>
-      <c r="I157" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E157,[1]TextData!A:A))</f>
-        <v>防御アップ</v>
-      </c>
-    </row>
-    <row r="158" spans="1:8">
+    </row>
+    <row r="158" spans="1:9">
       <c r="A158">
-        <v>100720</v>
+        <v>100810</v>
       </c>
       <c r="B158" t="str">
         <f>INDEX(TextData!B:B,MATCH(A158,TextData!A:A))</f>
-        <v>オーバーリミット</v>
+        <v>テンパランス</v>
       </c>
       <c r="C158">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D158" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C158,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E158">
-        <v>21</v>
+        <v>1040</v>
       </c>
       <c r="F158">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G158">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H158">
         <v>100</v>
+      </c>
+      <c r="I158" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E158,[1]TextData!A:A))</f>
+        <v>攻撃アップ</v>
       </c>
     </row>
     <row r="159" spans="1:9">
@@ -27177,7 +27180,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E159">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="F159">
         <v>999</v>
@@ -27190,10 +27193,10 @@
       </c>
       <c r="I159" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E159,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
-    </row>
-    <row r="160" spans="1:9">
+        <v>防御アップ</v>
+      </c>
+    </row>
+    <row r="160" spans="1:8">
       <c r="A160">
         <v>100810</v>
       </c>
@@ -27202,46 +27205,42 @@
         <v>テンパランス</v>
       </c>
       <c r="C160">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D160" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C160,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E160">
-        <v>1050</v>
+        <v>11</v>
       </c>
       <c r="F160">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G160">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H160">
         <v>100</v>
       </c>
-      <c r="I160" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E160,[1]TextData!A:A))</f>
-        <v>防御アップ</v>
-      </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161">
-        <v>100810</v>
+        <v>100820</v>
       </c>
       <c r="B161" t="str">
         <f>INDEX(TextData!B:B,MATCH(A161,TextData!A:A))</f>
-        <v>テンパランス</v>
+        <v>シエルクルセイダー</v>
       </c>
       <c r="C161">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D161" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C161,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E161">
-        <v>11</v>
+        <v>300</v>
       </c>
       <c r="F161">
         <v>0</v>
@@ -27262,14 +27261,14 @@
         <v>シエルクルセイダー</v>
       </c>
       <c r="C162">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D162" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C162,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E162">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="F162">
         <v>0</v>
@@ -27283,21 +27282,21 @@
     </row>
     <row r="163" spans="1:8">
       <c r="A163">
-        <v>100820</v>
+        <v>100910</v>
       </c>
       <c r="B163" t="str">
         <f>INDEX(TextData!B:B,MATCH(A163,TextData!A:A))</f>
-        <v>シエルクルセイダー</v>
+        <v>バーニングカウンター</v>
       </c>
       <c r="C163">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D163" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C163,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E163">
-        <v>21</v>
+        <v>350</v>
       </c>
       <c r="F163">
         <v>0</v>
@@ -27318,14 +27317,14 @@
         <v>バーニングカウンター</v>
       </c>
       <c r="C164">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D164" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C164,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E164">
-        <v>350</v>
+        <v>100911</v>
       </c>
       <c r="F164">
         <v>0</v>
@@ -27339,7 +27338,7 @@
     </row>
     <row r="165" spans="1:8">
       <c r="A165">
-        <v>100910</v>
+        <v>100911</v>
       </c>
       <c r="B165" t="str">
         <f>INDEX(TextData!B:B,MATCH(A165,TextData!A:A))</f>
@@ -27353,7 +27352,7 @@
         <v>行動後スキル</v>
       </c>
       <c r="E165">
-        <v>100911</v>
+        <v>11</v>
       </c>
       <c r="F165">
         <v>0</v>
@@ -27367,21 +27366,21 @@
     </row>
     <row r="166" spans="1:8">
       <c r="A166">
-        <v>100911</v>
+        <v>100920</v>
       </c>
       <c r="B166" t="str">
         <f>INDEX(TextData!B:B,MATCH(A166,TextData!A:A))</f>
-        <v>バーニングカウンター</v>
+        <v>プロミネンス</v>
       </c>
       <c r="C166">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D166" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C166,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E166">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="F166">
         <v>0</v>
@@ -27402,14 +27401,14 @@
         <v>プロミネンス</v>
       </c>
       <c r="C167">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D167" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C167,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E167">
-        <v>400</v>
+        <v>100921</v>
       </c>
       <c r="F167">
         <v>0</v>
@@ -27421,35 +27420,39 @@
         <v>100</v>
       </c>
     </row>
-    <row r="168" spans="1:8">
+    <row r="168" spans="1:9">
       <c r="A168">
-        <v>100920</v>
+        <v>100921</v>
       </c>
       <c r="B168" t="str">
         <f>INDEX(TextData!B:B,MATCH(A168,TextData!A:A))</f>
         <v>プロミネンス</v>
       </c>
       <c r="C168">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D168" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C168,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E168">
-        <v>100921</v>
+        <v>1070</v>
       </c>
       <c r="F168">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G168">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="H168">
         <v>100</v>
       </c>
-    </row>
-    <row r="169" spans="1:9">
+      <c r="I168" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E168,[1]TextData!A:A))</f>
+        <v>会心率アップ</v>
+      </c>
+    </row>
+    <row r="169" spans="1:8">
       <c r="A169">
         <v>100921</v>
       </c>
@@ -27458,46 +27461,42 @@
         <v>プロミネンス</v>
       </c>
       <c r="C169">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D169" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C169,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E169">
-        <v>1070</v>
+        <v>21</v>
       </c>
       <c r="F169">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G169">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H169">
         <v>100</v>
       </c>
-      <c r="I169" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E169,[1]TextData!A:A))</f>
-        <v>会心率アップ</v>
-      </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170">
-        <v>100921</v>
+        <v>101010</v>
       </c>
       <c r="B170" t="str">
         <f>INDEX(TextData!B:B,MATCH(A170,TextData!A:A))</f>
-        <v>プロミネンス</v>
+        <v>エウロス</v>
       </c>
       <c r="C170">
-        <v>7010</v>
+        <v>12010</v>
       </c>
       <c r="D170" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C170,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>最後に受けたAbnormalを相手に移す</v>
       </c>
       <c r="E170">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="F170">
         <v>0</v>
@@ -27518,11 +27517,11 @@
         <v>エウロス</v>
       </c>
       <c r="C171">
-        <v>12010</v>
+        <v>13010</v>
       </c>
       <c r="D171" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C171,Define!P:P))</f>
-        <v>最後に受けたAbnormalを相手に移す</v>
+        <v>対象のバフを奪い取る</v>
       </c>
       <c r="E171">
         <v>0</v>
@@ -27546,14 +27545,14 @@
         <v>エウロス</v>
       </c>
       <c r="C172">
-        <v>13010</v>
+        <v>7010</v>
       </c>
       <c r="D172" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C172,Define!P:P))</f>
-        <v>対象のバフを奪い取る</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E172">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F172">
         <v>0</v>
@@ -27567,21 +27566,21 @@
     </row>
     <row r="173" spans="1:8">
       <c r="A173">
-        <v>101010</v>
+        <v>101020</v>
       </c>
       <c r="B173" t="str">
         <f>INDEX(TextData!B:B,MATCH(A173,TextData!A:A))</f>
-        <v>エウロス</v>
+        <v>ボレアス</v>
       </c>
       <c r="C173">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D173" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C173,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E173">
-        <v>11</v>
+        <v>300</v>
       </c>
       <c r="F173">
         <v>0</v>
@@ -27602,14 +27601,14 @@
         <v>ボレアス</v>
       </c>
       <c r="C174">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D174" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C174,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E174">
-        <v>300</v>
+        <v>21</v>
       </c>
       <c r="F174">
         <v>0</v>
@@ -27621,35 +27620,39 @@
         <v>100</v>
       </c>
     </row>
-    <row r="175" spans="1:8">
+    <row r="175" spans="1:9">
       <c r="A175">
-        <v>101020</v>
+        <v>101110</v>
       </c>
       <c r="B175" t="str">
         <f>INDEX(TextData!B:B,MATCH(A175,TextData!A:A))</f>
-        <v>ボレアス</v>
+        <v>アバランシュ</v>
       </c>
       <c r="C175">
-        <v>7010</v>
+        <v>3070</v>
       </c>
       <c r="D175" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C175,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステートの効果を変更</v>
       </c>
       <c r="E175">
-        <v>21</v>
+        <v>2140</v>
       </c>
       <c r="F175">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G175">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="H175">
         <v>100</v>
       </c>
-    </row>
-    <row r="176" spans="1:9">
+      <c r="I175" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E175,[1]TextData!A:A))</f>
+        <v>凍結</v>
+      </c>
+    </row>
+    <row r="176" spans="1:8">
       <c r="A176">
         <v>101110</v>
       </c>
@@ -27658,52 +27661,48 @@
         <v>アバランシュ</v>
       </c>
       <c r="C176">
-        <v>3070</v>
+        <v>7010</v>
       </c>
       <c r="D176" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C176,Define!P:P))</f>
-        <v>ステートの効果を変更</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E176">
-        <v>2140</v>
+        <v>11</v>
       </c>
       <c r="F176">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G176">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="H176">
         <v>100</v>
       </c>
-      <c r="I176" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E176,[1]TextData!A:A))</f>
-        <v>凍結</v>
-      </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177">
-        <v>101110</v>
+        <v>101120</v>
       </c>
       <c r="B177" t="str">
         <f>INDEX(TextData!B:B,MATCH(A177,TextData!A:A))</f>
-        <v>アバランシュ</v>
+        <v>ブリザードコフィン</v>
       </c>
       <c r="C177">
-        <v>7010</v>
+        <v>1040</v>
       </c>
       <c r="D177" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C177,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>特定ステートダメージ</v>
       </c>
       <c r="E177">
-        <v>11</v>
+        <v>400</v>
       </c>
       <c r="F177">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="G177">
-        <v>0</v>
+        <v>2140</v>
       </c>
       <c r="H177">
         <v>100</v>
@@ -27718,54 +27717,58 @@
         <v>ブリザードコフィン</v>
       </c>
       <c r="C178">
-        <v>1040</v>
+        <v>7010</v>
       </c>
       <c r="D178" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C178,Define!P:P))</f>
-        <v>特定ステートダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E178">
-        <v>400</v>
+        <v>21</v>
       </c>
       <c r="F178">
-        <v>200</v>
+        <v>0</v>
       </c>
       <c r="G178">
-        <v>2140</v>
+        <v>0</v>
       </c>
       <c r="H178">
         <v>100</v>
       </c>
     </row>
-    <row r="179" spans="1:8">
+    <row r="179" ht="11" customHeight="1" spans="1:9">
       <c r="A179">
-        <v>101120</v>
+        <v>200210</v>
       </c>
       <c r="B179" t="str">
         <f>INDEX(TextData!B:B,MATCH(A179,TextData!A:A))</f>
-        <v>ブリザードコフィン</v>
+        <v>マイトレインフォース</v>
       </c>
       <c r="C179">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D179" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C179,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E179">
-        <v>21</v>
+        <v>1040</v>
       </c>
       <c r="F179">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G179">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H179">
         <v>100</v>
       </c>
-    </row>
-    <row r="180" ht="11" customHeight="1" spans="1:9">
+      <c r="I179" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E179,[1]TextData!A:A))</f>
+        <v>攻撃アップ</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8">
       <c r="A180">
         <v>200210</v>
       </c>
@@ -27774,46 +27777,42 @@
         <v>マイトレインフォース</v>
       </c>
       <c r="C180">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D180" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C180,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E180">
-        <v>1040</v>
+        <v>11</v>
       </c>
       <c r="F180">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G180">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H180">
         <v>100</v>
       </c>
-      <c r="I180" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E180,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181">
-        <v>200210</v>
+        <v>200220</v>
       </c>
       <c r="B181" t="str">
         <f>INDEX(TextData!B:B,MATCH(A181,TextData!A:A))</f>
-        <v>マイトレインフォース</v>
+        <v>カタストロフィ</v>
       </c>
       <c r="C181">
-        <v>7010</v>
+        <v>1010</v>
       </c>
       <c r="D181" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C181,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E181">
-        <v>11</v>
+        <v>500</v>
       </c>
       <c r="F181">
         <v>0</v>
@@ -27834,14 +27833,14 @@
         <v>カタストロフィ</v>
       </c>
       <c r="C182">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D182" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C182,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E182">
-        <v>500</v>
+        <v>21</v>
       </c>
       <c r="F182">
         <v>0</v>
@@ -27853,41 +27852,45 @@
         <v>100</v>
       </c>
     </row>
-    <row r="183" spans="1:8">
+    <row r="183" spans="1:9">
       <c r="A183">
-        <v>200220</v>
+        <v>200230</v>
       </c>
       <c r="B183" t="str">
         <f>INDEX(TextData!B:B,MATCH(A183,TextData!A:A))</f>
-        <v>カタストロフィ</v>
+        <v>悪魔(ベリト)</v>
       </c>
       <c r="C183">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D183" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C183,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E183">
-        <v>21</v>
+        <v>1040</v>
       </c>
       <c r="F183">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G183">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H183">
         <v>100</v>
       </c>
+      <c r="I183" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E183,[1]TextData!A:A))</f>
+        <v>攻撃アップ</v>
+      </c>
     </row>
     <row r="184" spans="1:9">
       <c r="A184">
-        <v>200230</v>
+        <v>200310</v>
       </c>
       <c r="B184" t="str">
         <f>INDEX(TextData!B:B,MATCH(A184,TextData!A:A))</f>
-        <v>悪魔(ベリト)</v>
+        <v>プルガシオン</v>
       </c>
       <c r="C184">
         <v>3010</v>
@@ -27897,23 +27900,23 @@
         <v>ステート付与</v>
       </c>
       <c r="E184">
-        <v>1040</v>
+        <v>2040</v>
       </c>
       <c r="F184">
-        <v>999</v>
+        <v>3</v>
       </c>
       <c r="G184">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="H184">
         <v>100</v>
       </c>
       <c r="I184" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E184,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
-      </c>
-    </row>
-    <row r="185" spans="1:9">
+        <v>リジェネ</v>
+      </c>
+    </row>
+    <row r="185" spans="1:8">
       <c r="A185">
         <v>200310</v>
       </c>
@@ -27922,58 +27925,58 @@
         <v>プルガシオン</v>
       </c>
       <c r="C185">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D185" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C185,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E185">
-        <v>2040</v>
+        <v>11</v>
       </c>
       <c r="F185">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G185">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H185">
         <v>100</v>
       </c>
-      <c r="I185" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E185,[1]TextData!A:A))</f>
-        <v>リジェネ</v>
-      </c>
-    </row>
-    <row r="186" spans="1:8">
+    </row>
+    <row r="186" spans="1:9">
       <c r="A186">
-        <v>200310</v>
+        <v>200320</v>
       </c>
       <c r="B186" t="str">
         <f>INDEX(TextData!B:B,MATCH(A186,TextData!A:A))</f>
-        <v>プルガシオン</v>
+        <v>プリエステス</v>
       </c>
       <c r="C186">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D186" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C186,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E186">
-        <v>11</v>
+        <v>2030</v>
       </c>
       <c r="F186">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G186">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="H186">
         <v>100</v>
       </c>
-    </row>
-    <row r="187" spans="1:9">
+      <c r="I186" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E186,[1]TextData!A:A))</f>
+        <v>カウンタ</v>
+      </c>
+    </row>
+    <row r="187" spans="1:8">
       <c r="A187">
         <v>200320</v>
       </c>
@@ -27982,55 +27985,55 @@
         <v>プリエステス</v>
       </c>
       <c r="C187">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D187" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C187,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E187">
-        <v>2030</v>
+        <v>21</v>
       </c>
       <c r="F187">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G187">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="H187">
         <v>100</v>
       </c>
-      <c r="I187" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E187,[1]TextData!A:A))</f>
-        <v>カウンタ</v>
-      </c>
-    </row>
-    <row r="188" spans="1:8">
+    </row>
+    <row r="188" spans="1:9">
       <c r="A188">
-        <v>200320</v>
+        <v>200330</v>
       </c>
       <c r="B188" t="str">
         <f>INDEX(TextData!B:B,MATCH(A188,TextData!A:A))</f>
-        <v>プリエステス</v>
+        <v>悪魔(パイモン)</v>
       </c>
       <c r="C188">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D188" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C188,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E188">
-        <v>21</v>
+        <v>2340</v>
       </c>
       <c r="F188">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G188">
         <v>0</v>
       </c>
       <c r="H188">
         <v>100</v>
+      </c>
+      <c r="I188" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E188,[1]TextData!A:A))</f>
+        <v>対象列化</v>
       </c>
     </row>
     <row r="189" spans="1:9">
@@ -28049,7 +28052,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E189">
-        <v>2340</v>
+        <v>2190</v>
       </c>
       <c r="F189">
         <v>999</v>
@@ -28062,39 +28065,35 @@
       </c>
       <c r="I189" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E189,[1]TextData!A:A))</f>
-        <v>対象列化</v>
-      </c>
-    </row>
-    <row r="190" spans="1:9">
+        <v>対象範囲延長</v>
+      </c>
+    </row>
+    <row r="190" spans="1:8">
       <c r="A190">
-        <v>200330</v>
+        <v>200410</v>
       </c>
       <c r="B190" t="str">
         <f>INDEX(TextData!B:B,MATCH(A190,TextData!A:A))</f>
-        <v>悪魔(パイモン)</v>
+        <v>コウソクテンショウ</v>
       </c>
       <c r="C190">
-        <v>3010</v>
+        <v>1010</v>
       </c>
       <c r="D190" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C190,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hpダメージ</v>
       </c>
       <c r="E190">
-        <v>2190</v>
+        <v>300</v>
       </c>
       <c r="F190">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G190">
         <v>0</v>
       </c>
       <c r="H190">
         <v>100</v>
-      </c>
-      <c r="I190" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E190,[1]TextData!A:A))</f>
-        <v>対象範囲延長</v>
       </c>
     </row>
     <row r="191" spans="1:8">
@@ -28106,14 +28105,14 @@
         <v>コウソクテンショウ</v>
       </c>
       <c r="C191">
-        <v>1010</v>
+        <v>7010</v>
       </c>
       <c r="D191" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C191,Define!P:P))</f>
-        <v>Hpダメージ</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E191">
-        <v>300</v>
+        <v>200411</v>
       </c>
       <c r="F191">
         <v>0</v>
@@ -28125,35 +28124,39 @@
         <v>100</v>
       </c>
     </row>
-    <row r="192" spans="1:8">
+    <row r="192" spans="1:9">
       <c r="A192">
-        <v>200410</v>
+        <v>200411</v>
       </c>
       <c r="B192" t="str">
         <f>INDEX(TextData!B:B,MATCH(A192,TextData!A:A))</f>
         <v>コウソクテンショウ</v>
       </c>
       <c r="C192">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D192" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C192,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E192">
-        <v>200411</v>
+        <v>2060</v>
       </c>
       <c r="F192">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G192">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H192">
         <v>100</v>
       </c>
-    </row>
-    <row r="193" spans="1:9">
+      <c r="I192" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E192,[1]TextData!A:A))</f>
+        <v>ドレイン</v>
+      </c>
+    </row>
+    <row r="193" spans="1:8">
       <c r="A193">
         <v>200411</v>
       </c>
@@ -28162,46 +28165,42 @@
         <v>コウソクテンショウ</v>
       </c>
       <c r="C193">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D193" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C193,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E193">
-        <v>2060</v>
+        <v>11</v>
       </c>
       <c r="F193">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G193">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H193">
         <v>100</v>
       </c>
-      <c r="I193" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E193,[1]TextData!A:A))</f>
-        <v>ドレイン</v>
-      </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194">
-        <v>200411</v>
+        <v>200420</v>
       </c>
       <c r="B194" t="str">
         <f>INDEX(TextData!B:B,MATCH(A194,TextData!A:A))</f>
-        <v>コウソクテンショウ</v>
+        <v>アンチバフ</v>
       </c>
       <c r="C194">
-        <v>7010</v>
+        <v>3050</v>
       </c>
       <c r="D194" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C194,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>バフステート解除</v>
       </c>
       <c r="E194">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F194">
         <v>0</v>
@@ -28222,14 +28221,14 @@
         <v>アンチバフ</v>
       </c>
       <c r="C195">
-        <v>3050</v>
+        <v>7010</v>
       </c>
       <c r="D195" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C195,Define!P:P))</f>
-        <v>バフステート解除</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E195">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F195">
         <v>0</v>
@@ -28243,61 +28242,65 @@
     </row>
     <row r="196" spans="1:8">
       <c r="A196">
-        <v>200420</v>
+        <v>200430</v>
       </c>
       <c r="B196" t="str">
         <f>INDEX(TextData!B:B,MATCH(A196,TextData!A:A))</f>
-        <v>アンチバフ</v>
+        <v>悪魔(アンドラス)</v>
       </c>
       <c r="C196">
-        <v>7010</v>
+        <v>6100</v>
       </c>
       <c r="D196" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C196,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>指定魔法の攻撃回数を増やす(強化限定)</v>
       </c>
       <c r="E196">
-        <v>21</v>
+        <v>2010</v>
       </c>
       <c r="F196">
         <v>0</v>
       </c>
       <c r="G196">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H196">
         <v>100</v>
       </c>
     </row>
-    <row r="197" spans="1:8">
+    <row r="197" spans="1:9">
       <c r="A197">
-        <v>200430</v>
+        <v>200510</v>
       </c>
       <c r="B197" t="str">
         <f>INDEX(TextData!B:B,MATCH(A197,TextData!A:A))</f>
-        <v>悪魔(アンドラス)</v>
+        <v>カウントダウン</v>
       </c>
       <c r="C197">
-        <v>6100</v>
+        <v>3010</v>
       </c>
       <c r="D197" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C197,Define!P:P))</f>
-        <v>指定魔法の攻撃回数を増やす(強化限定)</v>
+        <v>ステート付与</v>
       </c>
       <c r="E197">
-        <v>2010</v>
+        <v>2050</v>
       </c>
       <c r="F197">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G197">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H197">
         <v>100</v>
       </c>
-    </row>
-    <row r="198" spans="1:9">
+      <c r="I197" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E197,[1]TextData!A:A))</f>
+        <v>攻撃無効</v>
+      </c>
+    </row>
+    <row r="198" spans="1:8">
       <c r="A198">
         <v>200510</v>
       </c>
@@ -28306,17 +28309,17 @@
         <v>カウントダウン</v>
       </c>
       <c r="C198">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D198" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C198,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E198">
-        <v>2050</v>
+        <v>11</v>
       </c>
       <c r="F198">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G198">
         <v>0</v>
@@ -28324,28 +28327,24 @@
       <c r="H198">
         <v>100</v>
       </c>
-      <c r="I198" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E198,[1]TextData!A:A))</f>
-        <v>攻撃無効</v>
-      </c>
-    </row>
-    <row r="199" spans="1:8">
+    </row>
+    <row r="199" spans="1:9">
       <c r="A199">
-        <v>200510</v>
+        <v>200520</v>
       </c>
       <c r="B199" t="str">
         <f>INDEX(TextData!B:B,MATCH(A199,TextData!A:A))</f>
-        <v>カウントダウン</v>
+        <v>グラウンドゼロ</v>
       </c>
       <c r="C199">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D199" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C199,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E199">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="F199">
         <v>0</v>
@@ -28356,8 +28355,12 @@
       <c r="H199">
         <v>100</v>
       </c>
-    </row>
-    <row r="200" spans="1:9">
+      <c r="I199" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E199,[1]TextData!A:A))</f>
+        <v>戦闘不能</v>
+      </c>
+    </row>
+    <row r="200" spans="1:8">
       <c r="A200">
         <v>200520</v>
       </c>
@@ -28366,14 +28369,14 @@
         <v>グラウンドゼロ</v>
       </c>
       <c r="C200">
-        <v>3010</v>
+        <v>11010</v>
       </c>
       <c r="D200" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C200,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>命中判定しない</v>
       </c>
       <c r="E200">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F200">
         <v>0</v>
@@ -28383,10 +28386,6 @@
       </c>
       <c r="H200">
         <v>100</v>
-      </c>
-      <c r="I200" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E200,[1]TextData!A:A))</f>
-        <v>戦闘不能</v>
       </c>
     </row>
     <row r="201" spans="1:8">
@@ -28398,14 +28397,14 @@
         <v>グラウンドゼロ</v>
       </c>
       <c r="C201">
-        <v>11010</v>
+        <v>7010</v>
       </c>
       <c r="D201" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C201,Define!P:P))</f>
-        <v>命中判定しない</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E201">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F201">
         <v>0</v>
@@ -28417,41 +28416,45 @@
         <v>100</v>
       </c>
     </row>
-    <row r="202" spans="1:8">
+    <row r="202" spans="1:9">
       <c r="A202">
-        <v>200520</v>
+        <v>200530</v>
       </c>
       <c r="B202" t="str">
         <f>INDEX(TextData!B:B,MATCH(A202,TextData!A:A))</f>
-        <v>グラウンドゼロ</v>
+        <v>悪魔(ビフロンス)</v>
       </c>
       <c r="C202">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D202" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C202,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E202">
-        <v>21</v>
+        <v>2410</v>
       </c>
       <c r="F202">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G202">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H202">
         <v>100</v>
       </c>
+      <c r="I202" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E202,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
     </row>
     <row r="203" spans="1:9">
       <c r="A203">
-        <v>200530</v>
+        <v>201010</v>
       </c>
       <c r="B203" t="str">
         <f>INDEX(TextData!B:B,MATCH(A203,TextData!A:A))</f>
-        <v>悪魔(ビフロンス)</v>
+        <v>カオスペイン</v>
       </c>
       <c r="C203">
         <v>3010</v>
@@ -28461,10 +28464,10 @@
         <v>ステート付与</v>
       </c>
       <c r="E203">
-        <v>2410</v>
+        <v>2010</v>
       </c>
       <c r="F203">
-        <v>999</v>
+        <v>2</v>
       </c>
       <c r="G203">
         <v>25</v>
@@ -28474,10 +28477,10 @@
       </c>
       <c r="I203" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E203,[1]TextData!A:A))</f>
-        <v>シールド</v>
-      </c>
-    </row>
-    <row r="204" spans="1:9">
+        <v>毒</v>
+      </c>
+    </row>
+    <row r="204" spans="1:8">
       <c r="A204">
         <v>201010</v>
       </c>
@@ -28486,46 +28489,42 @@
         <v>カオスペイン</v>
       </c>
       <c r="C204">
-        <v>3010</v>
+        <v>7010</v>
       </c>
       <c r="D204" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C204,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E204">
-        <v>2010</v>
+        <v>11</v>
       </c>
       <c r="F204">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G204">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H204">
         <v>100</v>
       </c>
-      <c r="I204" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E204,[1]TextData!A:A))</f>
-        <v>毒</v>
-      </c>
     </row>
     <row r="205" spans="1:8">
       <c r="A205">
-        <v>201010</v>
+        <v>201020</v>
       </c>
       <c r="B205" t="str">
         <f>INDEX(TextData!B:B,MATCH(A205,TextData!A:A))</f>
-        <v>カオスペイン</v>
+        <v>フォールンワン</v>
       </c>
       <c r="C205">
-        <v>7010</v>
+        <v>2030</v>
       </c>
       <c r="D205" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C205,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>対象のHpを1にする</v>
       </c>
       <c r="E205">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="F205">
         <v>0</v>
@@ -28546,11 +28545,11 @@
         <v>フォールンワン</v>
       </c>
       <c r="C206">
-        <v>2030</v>
+        <v>11010</v>
       </c>
       <c r="D206" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C206,Define!P:P))</f>
-        <v>対象のHpを1にする</v>
+        <v>命中判定しない</v>
       </c>
       <c r="E206">
         <v>0</v>
@@ -28574,14 +28573,14 @@
         <v>フォールンワン</v>
       </c>
       <c r="C207">
-        <v>11010</v>
+        <v>7010</v>
       </c>
       <c r="D207" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C207,Define!P:P))</f>
-        <v>命中判定しない</v>
+        <v>行動後スキル</v>
       </c>
       <c r="E207">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F207">
         <v>0</v>
@@ -28593,26 +28592,26 @@
         <v>100</v>
       </c>
     </row>
-    <row r="208" spans="1:8">
+    <row r="208" spans="1:9">
       <c r="A208">
-        <v>201020</v>
+        <v>201030</v>
       </c>
       <c r="B208" t="str">
         <f>INDEX(TextData!B:B,MATCH(A208,TextData!A:A))</f>
-        <v>フォールンワン</v>
+        <v>アンリマユ</v>
       </c>
       <c r="C208">
-        <v>7010</v>
+        <v>3010</v>
       </c>
       <c r="D208" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C208,Define!P:P))</f>
-        <v>行動後スキル</v>
+        <v>ステート付与</v>
       </c>
       <c r="E208">
-        <v>21</v>
+        <v>2050</v>
       </c>
       <c r="F208">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G208">
         <v>0</v>
@@ -28620,14 +28619,18 @@
       <c r="H208">
         <v>100</v>
       </c>
+      <c r="I208" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E208,[1]TextData!A:A))</f>
+        <v>攻撃無効</v>
+      </c>
     </row>
     <row r="209" spans="1:9">
       <c r="A209">
-        <v>201030</v>
+        <v>300010</v>
       </c>
       <c r="B209" t="str">
         <f>INDEX(TextData!B:B,MATCH(A209,TextData!A:A))</f>
-        <v>アンリマユ</v>
+        <v>ライフブースト</v>
       </c>
       <c r="C209">
         <v>3010</v>
@@ -28637,89 +28640,89 @@
         <v>ステート付与</v>
       </c>
       <c r="E209">
-        <v>2050</v>
+        <v>1020</v>
       </c>
       <c r="F209">
-        <v>2</v>
+        <v>999</v>
       </c>
       <c r="G209">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H209">
         <v>100</v>
       </c>
       <c r="I209" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E209,[1]TextData!A:A))</f>
-        <v>攻撃無効</v>
-      </c>
-    </row>
-    <row r="210" spans="1:9">
+        <v>最大Hpアップ</v>
+      </c>
+    </row>
+    <row r="210" spans="1:8">
       <c r="A210">
-        <v>300010</v>
+        <v>300020</v>
       </c>
       <c r="B210" t="str">
         <f>INDEX(TextData!B:B,MATCH(A210,TextData!A:A))</f>
-        <v>ライフブースト</v>
+        <v>スピリットチャージ</v>
       </c>
       <c r="C210">
-        <v>3010</v>
+        <v>4040</v>
       </c>
       <c r="D210" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C210,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>指定魔法のCｔ回復</v>
       </c>
       <c r="E210">
-        <v>1020</v>
+        <v>1</v>
       </c>
       <c r="F210">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G210">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H210">
         <v>100</v>
       </c>
-      <c r="I210" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E210,[1]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
-      </c>
-    </row>
-    <row r="211" spans="1:8">
+    </row>
+    <row r="211" spans="1:9">
       <c r="A211">
-        <v>300020</v>
+        <v>300030</v>
       </c>
       <c r="B211" t="str">
         <f>INDEX(TextData!B:B,MATCH(A211,TextData!A:A))</f>
-        <v>スピリットチャージ</v>
+        <v>フォースライズ</v>
       </c>
       <c r="C211">
-        <v>4040</v>
+        <v>3010</v>
       </c>
       <c r="D211" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C211,Define!P:P))</f>
-        <v>指定魔法のCｔ回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E211">
-        <v>1</v>
+        <v>1040</v>
       </c>
       <c r="F211">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G211">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H211">
         <v>100</v>
       </c>
+      <c r="I211" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E211,[1]TextData!A:A))</f>
+        <v>攻撃アップ</v>
+      </c>
     </row>
     <row r="212" spans="1:9">
       <c r="A212">
-        <v>300030</v>
+        <v>300040</v>
       </c>
       <c r="B212" t="str">
         <f>INDEX(TextData!B:B,MATCH(A212,TextData!A:A))</f>
-        <v>フォースライズ</v>
+        <v>ディフェンスオーラ</v>
       </c>
       <c r="C212">
         <v>3010</v>
@@ -28729,7 +28732,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E212">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="F212">
         <v>999</v>
@@ -28742,16 +28745,16 @@
       </c>
       <c r="I212" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E212,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
+        <v>防御アップ</v>
       </c>
     </row>
     <row r="213" spans="1:9">
       <c r="A213">
-        <v>300040</v>
+        <v>300050</v>
       </c>
       <c r="B213" t="str">
         <f>INDEX(TextData!B:B,MATCH(A213,TextData!A:A))</f>
-        <v>ディフェンスオーラ</v>
+        <v>ラピッドムーブ</v>
       </c>
       <c r="C213">
         <v>3010</v>
@@ -28761,29 +28764,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E213">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="F213">
         <v>999</v>
       </c>
       <c r="G213">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H213">
         <v>100</v>
       </c>
       <c r="I213" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E213,[1]TextData!A:A))</f>
-        <v>防御アップ</v>
+        <v>速度アップ</v>
       </c>
     </row>
     <row r="214" spans="1:9">
       <c r="A214">
-        <v>300050</v>
+        <v>300130</v>
       </c>
       <c r="B214" t="str">
         <f>INDEX(TextData!B:B,MATCH(A214,TextData!A:A))</f>
-        <v>ラピッドムーブ</v>
+        <v>アタックブレイク</v>
       </c>
       <c r="C214">
         <v>3010</v>
@@ -28793,29 +28796,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E214">
-        <v>1060</v>
+        <v>1041</v>
       </c>
       <c r="F214">
         <v>999</v>
       </c>
       <c r="G214">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H214">
         <v>100</v>
       </c>
       <c r="I214" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E214,[1]TextData!A:A))</f>
-        <v>速度アップ</v>
+        <v>攻撃ダウン</v>
       </c>
     </row>
     <row r="215" spans="1:9">
       <c r="A215">
-        <v>300130</v>
+        <v>300140</v>
       </c>
       <c r="B215" t="str">
         <f>INDEX(TextData!B:B,MATCH(A215,TextData!A:A))</f>
-        <v>アタックブレイク</v>
+        <v>シールドバニッシュ</v>
       </c>
       <c r="C215">
         <v>3010</v>
@@ -28825,7 +28828,7 @@
         <v>ステート付与</v>
       </c>
       <c r="E215">
-        <v>1041</v>
+        <v>1051</v>
       </c>
       <c r="F215">
         <v>999</v>
@@ -28838,76 +28841,76 @@
       </c>
       <c r="I215" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E215,[1]TextData!A:A))</f>
-        <v>攻撃ダウン</v>
-      </c>
-    </row>
-    <row r="216" spans="1:9">
+        <v>防御ダウン</v>
+      </c>
+    </row>
+    <row r="216" spans="1:8">
       <c r="A216">
-        <v>300140</v>
+        <v>300210</v>
       </c>
       <c r="B216" t="str">
         <f>INDEX(TextData!B:B,MATCH(A216,TextData!A:A))</f>
-        <v>シールドバニッシュ</v>
+        <v>エーテルリチャージ</v>
       </c>
       <c r="C216">
-        <v>3010</v>
+        <v>4020</v>
       </c>
       <c r="D216" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C216,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ct回復</v>
       </c>
       <c r="E216">
-        <v>1051</v>
+        <v>1</v>
       </c>
       <c r="F216">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G216">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H216">
         <v>100</v>
       </c>
-      <c r="I216" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E216,[1]TextData!A:A))</f>
-        <v>防御ダウン</v>
-      </c>
-    </row>
-    <row r="217" spans="1:8">
+    </row>
+    <row r="217" spans="1:9">
       <c r="A217">
-        <v>300210</v>
+        <v>300220</v>
       </c>
       <c r="B217" t="str">
         <f>INDEX(TextData!B:B,MATCH(A217,TextData!A:A))</f>
-        <v>エーテルリチャージ</v>
+        <v>リカバリーエンハンス</v>
       </c>
       <c r="C217">
-        <v>4020</v>
+        <v>3010</v>
       </c>
       <c r="D217" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C217,Define!P:P))</f>
-        <v>Ct回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E217">
-        <v>1</v>
+        <v>2460</v>
       </c>
       <c r="F217">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G217">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="H217">
         <v>100</v>
       </c>
+      <c r="I217" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E217,[1]TextData!A:A))</f>
+        <v>Hp回復効果アップ</v>
+      </c>
     </row>
     <row r="218" spans="1:9">
       <c r="A218">
-        <v>300220</v>
+        <v>300230</v>
       </c>
       <c r="B218" t="str">
         <f>INDEX(TextData!B:B,MATCH(A218,TextData!A:A))</f>
-        <v>リカバリーエンハンス</v>
+        <v>ヴェンジェンス</v>
       </c>
       <c r="C218">
         <v>3010</v>
@@ -28917,89 +28920,89 @@
         <v>ステート付与</v>
       </c>
       <c r="E218">
-        <v>2460</v>
+        <v>2030</v>
       </c>
       <c r="F218">
         <v>999</v>
       </c>
       <c r="G218">
-        <v>5</v>
+        <v>30</v>
       </c>
       <c r="H218">
         <v>100</v>
       </c>
       <c r="I218" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E218,[1]TextData!A:A))</f>
-        <v>Hp回復効果アップ</v>
-      </c>
-    </row>
-    <row r="219" spans="1:9">
+        <v>カウンタ</v>
+      </c>
+    </row>
+    <row r="219" spans="1:8">
       <c r="A219">
-        <v>300230</v>
+        <v>301010</v>
       </c>
       <c r="B219" t="str">
         <f>INDEX(TextData!B:B,MATCH(A219,TextData!A:A))</f>
-        <v>ヴェンジェンス</v>
+        <v>ディケイドリセット</v>
       </c>
       <c r="C219">
-        <v>3010</v>
+        <v>5012</v>
       </c>
       <c r="D219" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C219,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>ActionResult扱いでAP指定</v>
       </c>
       <c r="E219">
-        <v>2030</v>
+        <v>0</v>
       </c>
       <c r="F219">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G219">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H219">
         <v>100</v>
       </c>
-      <c r="I219" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E219,[1]TextData!A:A))</f>
-        <v>カウンタ</v>
-      </c>
-    </row>
-    <row r="220" spans="1:8">
+    </row>
+    <row r="220" spans="1:9">
       <c r="A220">
-        <v>301010</v>
+        <v>301020</v>
       </c>
       <c r="B220" t="str">
         <f>INDEX(TextData!B:B,MATCH(A220,TextData!A:A))</f>
-        <v>ディケイドリセット</v>
+        <v>ウォーリアーブラッド</v>
       </c>
       <c r="C220">
-        <v>5012</v>
+        <v>3010</v>
       </c>
       <c r="D220" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C220,Define!P:P))</f>
-        <v>ActionResult扱いでAP指定</v>
+        <v>ステート付与</v>
       </c>
       <c r="E220">
-        <v>0</v>
+        <v>1040</v>
       </c>
       <c r="F220">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G220">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="H220">
         <v>100</v>
       </c>
+      <c r="I220" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E220,[1]TextData!A:A))</f>
+        <v>攻撃アップ</v>
+      </c>
     </row>
     <row r="221" spans="1:9">
       <c r="A221">
-        <v>301020</v>
+        <v>301030</v>
       </c>
       <c r="B221" t="str">
         <f>INDEX(TextData!B:B,MATCH(A221,TextData!A:A))</f>
-        <v>ウォーリアーブラッド</v>
+        <v>トライアングルガード</v>
       </c>
       <c r="C221">
         <v>3010</v>
@@ -29009,29 +29012,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E221">
-        <v>1040</v>
+        <v>1100</v>
       </c>
       <c r="F221">
-        <v>999</v>
+        <v>1</v>
       </c>
       <c r="G221">
-        <v>8</v>
+        <v>30</v>
       </c>
       <c r="H221">
         <v>100</v>
       </c>
       <c r="I221" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E221,[1]TextData!A:A))</f>
-        <v>攻撃アップ</v>
+        <v>ダメージカット</v>
       </c>
     </row>
     <row r="222" spans="1:9">
       <c r="A222">
-        <v>301030</v>
+        <v>301040</v>
       </c>
       <c r="B222" t="str">
         <f>INDEX(TextData!B:B,MATCH(A222,TextData!A:A))</f>
-        <v>トライアングルガード</v>
+        <v>セーフティバリア</v>
       </c>
       <c r="C222">
         <v>3010</v>
@@ -29041,29 +29044,29 @@
         <v>ステート付与</v>
       </c>
       <c r="E222">
-        <v>1100</v>
+        <v>2050</v>
       </c>
       <c r="F222">
         <v>1</v>
       </c>
       <c r="G222">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="H222">
         <v>100</v>
       </c>
       <c r="I222" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E222,[1]TextData!A:A))</f>
-        <v>ダメージカット</v>
+        <v>攻撃無効</v>
       </c>
     </row>
     <row r="223" spans="1:9">
       <c r="A223">
-        <v>301040</v>
+        <v>301050</v>
       </c>
       <c r="B223" t="str">
         <f>INDEX(TextData!B:B,MATCH(A223,TextData!A:A))</f>
-        <v>セーフティバリア</v>
+        <v>ヒロインズハイ</v>
       </c>
       <c r="C223">
         <v>3010</v>
@@ -29073,55 +29076,55 @@
         <v>ステート付与</v>
       </c>
       <c r="E223">
-        <v>2050</v>
+        <v>1020</v>
       </c>
       <c r="F223">
-        <v>1</v>
+        <v>999</v>
       </c>
       <c r="G223">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="H223">
         <v>100</v>
       </c>
       <c r="I223" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E223,[1]TextData!A:A))</f>
-        <v>攻撃無効</v>
+        <v>最大Hpアップ</v>
       </c>
     </row>
     <row r="224" spans="1:9">
       <c r="A224">
-        <v>301050</v>
+        <v>301060</v>
       </c>
       <c r="B224" t="str">
         <f>INDEX(TextData!B:B,MATCH(A224,TextData!A:A))</f>
-        <v>ヒロインズハイ</v>
+        <v>セカンドステージ</v>
       </c>
       <c r="C224">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="D224" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C224,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>ステート解除</v>
       </c>
       <c r="E224">
-        <v>1020</v>
+        <v>1</v>
       </c>
       <c r="F224">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G224">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="H224">
         <v>100</v>
       </c>
       <c r="I224" t="str">
         <f>INDEX([1]TextData!B:B,MATCH(E224,[1]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
-      </c>
-    </row>
-    <row r="225" spans="1:9">
+        <v>戦闘不能</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8">
       <c r="A225">
         <v>301060</v>
       </c>
@@ -29130,14 +29133,14 @@
         <v>セカンドステージ</v>
       </c>
       <c r="C225">
-        <v>3020</v>
+        <v>2030</v>
       </c>
       <c r="D225" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C225,Define!P:P))</f>
-        <v>ステート解除</v>
+        <v>対象のHpを1にする</v>
       </c>
       <c r="E225">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F225">
         <v>0</v>
@@ -29147,10 +29150,6 @@
       </c>
       <c r="H225">
         <v>100</v>
-      </c>
-      <c r="I225" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E225,[1]TextData!A:A))</f>
-        <v>戦闘不能</v>
       </c>
     </row>
     <row r="226" spans="1:8">
@@ -29162,14 +29161,14 @@
         <v>セカンドステージ</v>
       </c>
       <c r="C226">
-        <v>2030</v>
+        <v>2010</v>
       </c>
       <c r="D226" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C226,Define!P:P))</f>
-        <v>対象のHpを1にする</v>
+        <v>Hp回復</v>
       </c>
       <c r="E226">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="F226">
         <v>0</v>
@@ -29181,149 +29180,149 @@
         <v>100</v>
       </c>
     </row>
-    <row r="227" spans="1:8">
+    <row r="227" spans="1:9">
       <c r="A227">
-        <v>301060</v>
+        <v>301070</v>
       </c>
       <c r="B227" t="str">
         <f>INDEX(TextData!B:B,MATCH(A227,TextData!A:A))</f>
-        <v>セカンドステージ</v>
+        <v>ハイヒットポイント</v>
       </c>
       <c r="C227">
-        <v>2010</v>
+        <v>3010</v>
       </c>
       <c r="D227" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C227,Define!P:P))</f>
-        <v>Hp回復</v>
+        <v>ステート付与</v>
       </c>
       <c r="E227">
-        <v>20</v>
+        <v>1020</v>
       </c>
       <c r="F227">
-        <v>0</v>
+        <v>999</v>
       </c>
       <c r="G227">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H227">
         <v>100</v>
       </c>
-    </row>
-    <row r="228" spans="1:9">
+      <c r="I227" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E227,[1]TextData!A:A))</f>
+        <v>最大Hpアップ</v>
+      </c>
+    </row>
+    <row r="228" spans="1:8">
       <c r="A228">
-        <v>301070</v>
+        <v>301080</v>
       </c>
       <c r="B228" t="str">
         <f>INDEX(TextData!B:B,MATCH(A228,TextData!A:A))</f>
-        <v>ハイヒットポイント</v>
+        <v>セプタブラスト</v>
       </c>
       <c r="C228">
-        <v>3010</v>
+        <v>1030</v>
       </c>
       <c r="D228" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C228,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Hp固定ダメージ</v>
       </c>
       <c r="E228">
-        <v>1020</v>
+        <v>50</v>
       </c>
       <c r="F228">
-        <v>999</v>
+        <v>0</v>
       </c>
       <c r="G228">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H228">
         <v>100</v>
       </c>
-      <c r="I228" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E228,[1]TextData!A:A))</f>
-        <v>最大Hpアップ</v>
-      </c>
-    </row>
-    <row r="229" spans="1:8">
+    </row>
+    <row r="229" spans="1:9">
       <c r="A229">
-        <v>301080</v>
+        <v>301090</v>
       </c>
       <c r="B229" t="str">
         <f>INDEX(TextData!B:B,MATCH(A229,TextData!A:A))</f>
-        <v>セプタブラスト</v>
+        <v>イニシャルブロッカー</v>
       </c>
       <c r="C229">
-        <v>1030</v>
+        <v>3010</v>
       </c>
       <c r="D229" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C229,Define!P:P))</f>
-        <v>Hp固定ダメージ</v>
+        <v>ステート付与</v>
       </c>
       <c r="E229">
-        <v>50</v>
+        <v>2410</v>
       </c>
       <c r="F229">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G229">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="H229">
         <v>100</v>
       </c>
-    </row>
-    <row r="230" spans="1:9">
+      <c r="I229" t="str">
+        <f>INDEX([1]TextData!B:B,MATCH(E229,[1]TextData!A:A))</f>
+        <v>シールド</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8">
       <c r="A230">
-        <v>301090</v>
+        <v>301100</v>
       </c>
       <c r="B230" t="str">
         <f>INDEX(TextData!B:B,MATCH(A230,TextData!A:A))</f>
-        <v>イニシャルブロッカー</v>
+        <v>ファーストテイク</v>
       </c>
       <c r="C230">
-        <v>3010</v>
+        <v>5020</v>
       </c>
       <c r="D230" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C230,Define!P:P))</f>
-        <v>ステート付与</v>
+        <v>Ap回復</v>
       </c>
       <c r="E230">
-        <v>2410</v>
+        <v>200</v>
       </c>
       <c r="F230">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G230">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="H230">
         <v>100</v>
       </c>
-      <c r="I230" t="str">
-        <f>INDEX([1]TextData!B:B,MATCH(E230,[1]TextData!A:A))</f>
-        <v>シールド</v>
-      </c>
     </row>
     <row r="231" spans="1:8">
       <c r="A231">
-        <v>301100</v>
+        <v>401010</v>
       </c>
       <c r="B231" t="str">
         <f>INDEX(TextData!B:B,MATCH(A231,TextData!A:A))</f>
-        <v>ファーストテイク</v>
+        <v>ファイアボール+</v>
       </c>
       <c r="C231">
-        <v>5020</v>
+        <v>6010</v>
       </c>
       <c r="D231" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C231,Define!P:P))</f>
-        <v>Ap回復</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E231">
-        <v>200</v>
+        <v>1010</v>
       </c>
       <c r="F231">
         <v>0</v>
       </c>
       <c r="G231">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="H231">
         <v>100</v>
@@ -29331,11 +29330,11 @@
     </row>
     <row r="232" spans="1:8">
       <c r="A232">
-        <v>401010</v>
+        <v>401020</v>
       </c>
       <c r="B232" t="str">
         <f>INDEX(TextData!B:B,MATCH(A232,TextData!A:A))</f>
-        <v>ファイアボール+</v>
+        <v>バーンストーム+</v>
       </c>
       <c r="C232">
         <v>6010</v>
@@ -29345,7 +29344,7 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E232">
-        <v>1010</v>
+        <v>1020</v>
       </c>
       <c r="F232">
         <v>0</v>
@@ -29359,11 +29358,11 @@
     </row>
     <row r="233" spans="1:8">
       <c r="A233">
-        <v>401020</v>
+        <v>401030</v>
       </c>
       <c r="B233" t="str">
         <f>INDEX(TextData!B:B,MATCH(A233,TextData!A:A))</f>
-        <v>バーンストーム+</v>
+        <v>ヒートスタンプ+</v>
       </c>
       <c r="C233">
         <v>6010</v>
@@ -29373,13 +29372,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E233">
-        <v>1020</v>
+        <v>1030</v>
       </c>
       <c r="F233">
         <v>0</v>
       </c>
       <c r="G233">
-        <v>250</v>
+        <v>2</v>
       </c>
       <c r="H233">
         <v>100</v>
@@ -29387,11 +29386,11 @@
     </row>
     <row r="234" spans="1:8">
       <c r="A234">
-        <v>401030</v>
+        <v>401040</v>
       </c>
       <c r="B234" t="str">
         <f>INDEX(TextData!B:B,MATCH(A234,TextData!A:A))</f>
-        <v>ヒートスタンプ+</v>
+        <v>ソードアダプト+</v>
       </c>
       <c r="C234">
         <v>6010</v>
@@ -29401,13 +29400,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E234">
-        <v>1030</v>
+        <v>1040</v>
       </c>
       <c r="F234">
         <v>0</v>
       </c>
       <c r="G234">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="H234">
         <v>100</v>
@@ -29415,11 +29414,11 @@
     </row>
     <row r="235" spans="1:8">
       <c r="A235">
-        <v>401040</v>
+        <v>401050</v>
       </c>
       <c r="B235" t="str">
         <f>INDEX(TextData!B:B,MATCH(A235,TextData!A:A))</f>
-        <v>ソードアダプト+</v>
+        <v>フレイムレイン+</v>
       </c>
       <c r="C235">
         <v>6010</v>
@@ -29429,13 +29428,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E235">
-        <v>1040</v>
+        <v>1050</v>
       </c>
       <c r="F235">
         <v>0</v>
       </c>
       <c r="G235">
-        <v>15</v>
+        <v>60</v>
       </c>
       <c r="H235">
         <v>100</v>
@@ -29443,11 +29442,11 @@
     </row>
     <row r="236" spans="1:8">
       <c r="A236">
-        <v>401050</v>
+        <v>401060</v>
       </c>
       <c r="B236" t="str">
         <f>INDEX(TextData!B:B,MATCH(A236,TextData!A:A))</f>
-        <v>フレイムレイン+</v>
+        <v>イクスティンクション+</v>
       </c>
       <c r="C236">
         <v>6010</v>
@@ -29457,13 +29456,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E236">
-        <v>1050</v>
+        <v>1060</v>
       </c>
       <c r="F236">
         <v>0</v>
       </c>
       <c r="G236">
-        <v>60</v>
+        <v>400</v>
       </c>
       <c r="H236">
         <v>100</v>
@@ -29471,27 +29470,27 @@
     </row>
     <row r="237" spans="1:8">
       <c r="A237">
-        <v>401060</v>
+        <v>401070</v>
       </c>
       <c r="B237" t="str">
         <f>INDEX(TextData!B:B,MATCH(A237,TextData!A:A))</f>
-        <v>イクスティンクション+</v>
+        <v>バーニングソウル+</v>
       </c>
       <c r="C237">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D237" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C237,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E237">
-        <v>1060</v>
+        <v>1070</v>
       </c>
       <c r="F237">
         <v>0</v>
       </c>
       <c r="G237">
-        <v>400</v>
+        <v>2</v>
       </c>
       <c r="H237">
         <v>100</v>
@@ -29499,27 +29498,27 @@
     </row>
     <row r="238" spans="1:8">
       <c r="A238">
-        <v>401070</v>
+        <v>401080</v>
       </c>
       <c r="B238" t="str">
         <f>INDEX(TextData!B:B,MATCH(A238,TextData!A:A))</f>
-        <v>バーニングソウル+</v>
+        <v>レイジングバウンサー+</v>
       </c>
       <c r="C238">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D238" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C238,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E238">
-        <v>1070</v>
+        <v>1080</v>
       </c>
       <c r="F238">
         <v>0</v>
       </c>
       <c r="G238">
-        <v>2</v>
+        <v>45</v>
       </c>
       <c r="H238">
         <v>100</v>
@@ -29527,27 +29526,27 @@
     </row>
     <row r="239" spans="1:8">
       <c r="A239">
-        <v>401080</v>
+        <v>402010</v>
       </c>
       <c r="B239" t="str">
         <f>INDEX(TextData!B:B,MATCH(A239,TextData!A:A))</f>
-        <v>レイジングバウンサー+</v>
+        <v>ディスチャージ+</v>
       </c>
       <c r="C239">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D239" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C239,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E239">
-        <v>1080</v>
+        <v>2010</v>
       </c>
       <c r="F239">
         <v>0</v>
       </c>
       <c r="G239">
-        <v>45</v>
+        <v>250</v>
       </c>
       <c r="H239">
         <v>100</v>
@@ -29555,27 +29554,27 @@
     </row>
     <row r="240" spans="1:8">
       <c r="A240">
-        <v>402010</v>
+        <v>402020</v>
       </c>
       <c r="B240" t="str">
         <f>INDEX(TextData!B:B,MATCH(A240,TextData!A:A))</f>
-        <v>ディスチャージ+</v>
+        <v>イベイドコード+</v>
       </c>
       <c r="C240">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D240" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C240,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E240">
-        <v>2010</v>
+        <v>2020</v>
       </c>
       <c r="F240">
         <v>0</v>
       </c>
       <c r="G240">
-        <v>250</v>
+        <v>25</v>
       </c>
       <c r="H240">
         <v>100</v>
@@ -29583,27 +29582,27 @@
     </row>
     <row r="241" spans="1:8">
       <c r="A241">
-        <v>402020</v>
+        <v>402030</v>
       </c>
       <c r="B241" t="str">
         <f>INDEX(TextData!B:B,MATCH(A241,TextData!A:A))</f>
-        <v>イベイドコード+</v>
+        <v>ショックインパルス+</v>
       </c>
       <c r="C241">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D241" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C241,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E241">
-        <v>2020</v>
+        <v>2030</v>
       </c>
       <c r="F241">
         <v>0</v>
       </c>
       <c r="G241">
-        <v>25</v>
+        <v>2</v>
       </c>
       <c r="H241">
         <v>100</v>
@@ -29611,27 +29610,27 @@
     </row>
     <row r="242" spans="1:8">
       <c r="A242">
-        <v>402030</v>
+        <v>402040</v>
       </c>
       <c r="B242" t="str">
         <f>INDEX(TextData!B:B,MATCH(A242,TextData!A:A))</f>
-        <v>ショックインパルス+</v>
+        <v>トラストチェイン+</v>
       </c>
       <c r="C242">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D242" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C242,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E242">
-        <v>2030</v>
+        <v>2040</v>
       </c>
       <c r="F242">
         <v>0</v>
       </c>
       <c r="G242">
-        <v>2</v>
+        <v>400</v>
       </c>
       <c r="H242">
         <v>100</v>
@@ -29639,27 +29638,27 @@
     </row>
     <row r="243" spans="1:8">
       <c r="A243">
-        <v>402040</v>
+        <v>402050</v>
       </c>
       <c r="B243" t="str">
         <f>INDEX(TextData!B:B,MATCH(A243,TextData!A:A))</f>
-        <v>トラストチェイン+</v>
+        <v>スペルバニシング+</v>
       </c>
       <c r="C243">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D243" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C243,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E243">
-        <v>2040</v>
+        <v>2050</v>
       </c>
       <c r="F243">
         <v>0</v>
       </c>
       <c r="G243">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="H243">
         <v>100</v>
@@ -29667,27 +29666,27 @@
     </row>
     <row r="244" spans="1:8">
       <c r="A244">
-        <v>402050</v>
+        <v>402060</v>
       </c>
       <c r="B244" t="str">
         <f>INDEX(TextData!B:B,MATCH(A244,TextData!A:A))</f>
-        <v>スペルバニシング+</v>
+        <v>アーテニーストライク+</v>
       </c>
       <c r="C244">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D244" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C244,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E244">
-        <v>2050</v>
+        <v>2060</v>
       </c>
       <c r="F244">
         <v>0</v>
       </c>
       <c r="G244">
-        <v>1</v>
+        <v>250</v>
       </c>
       <c r="H244">
         <v>100</v>
@@ -29695,27 +29694,27 @@
     </row>
     <row r="245" spans="1:8">
       <c r="A245">
-        <v>402060</v>
+        <v>402070</v>
       </c>
       <c r="B245" t="str">
         <f>INDEX(TextData!B:B,MATCH(A245,TextData!A:A))</f>
-        <v>アーテニーストライク+</v>
+        <v>コンセントレイト+</v>
       </c>
       <c r="C245">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D245" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C245,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E245">
-        <v>2060</v>
+        <v>2070</v>
       </c>
       <c r="F245">
         <v>0</v>
       </c>
       <c r="G245">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="H245">
         <v>100</v>
@@ -29723,27 +29722,27 @@
     </row>
     <row r="246" spans="1:8">
       <c r="A246">
-        <v>402070</v>
+        <v>402080</v>
       </c>
       <c r="B246" t="str">
         <f>INDEX(TextData!B:B,MATCH(A246,TextData!A:A))</f>
-        <v>コンセントレイト+</v>
+        <v>ディレイマジック+</v>
       </c>
       <c r="C246">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D246" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C246,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E246">
-        <v>2070</v>
+        <v>2080</v>
       </c>
       <c r="F246">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G246">
-        <v>40</v>
+        <v>2</v>
       </c>
       <c r="H246">
         <v>100</v>
@@ -29751,11 +29750,11 @@
     </row>
     <row r="247" spans="1:8">
       <c r="A247">
-        <v>402080</v>
+        <v>403010</v>
       </c>
       <c r="B247" t="str">
         <f>INDEX(TextData!B:B,MATCH(A247,TextData!A:A))</f>
-        <v>ディレイマジック+</v>
+        <v>アイスブレイド+</v>
       </c>
       <c r="C247">
         <v>6010</v>
@@ -29765,13 +29764,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E247">
-        <v>2080</v>
+        <v>3010</v>
       </c>
       <c r="F247">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G247">
-        <v>2</v>
+        <v>250</v>
       </c>
       <c r="H247">
         <v>100</v>
@@ -29779,27 +29778,27 @@
     </row>
     <row r="248" spans="1:8">
       <c r="A248">
-        <v>403010</v>
+        <v>403020</v>
       </c>
       <c r="B248" t="str">
         <f>INDEX(TextData!B:B,MATCH(A248,TextData!A:A))</f>
-        <v>アイスブレイド+</v>
+        <v>カウンターオーラ+</v>
       </c>
       <c r="C248">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D248" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C248,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E248">
-        <v>3010</v>
+        <v>3020</v>
       </c>
       <c r="F248">
         <v>0</v>
       </c>
       <c r="G248">
-        <v>250</v>
+        <v>40</v>
       </c>
       <c r="H248">
         <v>100</v>
@@ -29807,11 +29806,11 @@
     </row>
     <row r="249" spans="1:8">
       <c r="A249">
-        <v>403020</v>
+        <v>403030</v>
       </c>
       <c r="B249" t="str">
         <f>INDEX(TextData!B:B,MATCH(A249,TextData!A:A))</f>
-        <v>カウンターオーラ+</v>
+        <v>ラインプロテクト+</v>
       </c>
       <c r="C249">
         <v>6030</v>
@@ -29821,13 +29820,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E249">
-        <v>3020</v>
+        <v>3030</v>
       </c>
       <c r="F249">
         <v>0</v>
       </c>
       <c r="G249">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="H249">
         <v>100</v>
@@ -29835,11 +29834,11 @@
     </row>
     <row r="250" spans="1:8">
       <c r="A250">
-        <v>403030</v>
+        <v>403040</v>
       </c>
       <c r="B250" t="str">
         <f>INDEX(TextData!B:B,MATCH(A250,TextData!A:A))</f>
-        <v>ラインプロテクト+</v>
+        <v>エスコートソール+</v>
       </c>
       <c r="C250">
         <v>6030</v>
@@ -29849,13 +29848,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E250">
-        <v>3030</v>
+        <v>3040</v>
       </c>
       <c r="F250">
         <v>0</v>
       </c>
       <c r="G250">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="H250">
         <v>100</v>
@@ -29863,11 +29862,11 @@
     </row>
     <row r="251" spans="1:8">
       <c r="A251">
-        <v>403040</v>
+        <v>403050</v>
       </c>
       <c r="B251" t="str">
         <f>INDEX(TextData!B:B,MATCH(A251,TextData!A:A))</f>
-        <v>エスコートソール+</v>
+        <v>ディープフリーズ+</v>
       </c>
       <c r="C251">
         <v>6030</v>
@@ -29877,7 +29876,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E251">
-        <v>3040</v>
+        <v>3050</v>
       </c>
       <c r="F251">
         <v>0</v>
@@ -29891,11 +29890,11 @@
     </row>
     <row r="252" spans="1:8">
       <c r="A252">
-        <v>403050</v>
+        <v>403060</v>
       </c>
       <c r="B252" t="str">
         <f>INDEX(TextData!B:B,MATCH(A252,TextData!A:A))</f>
-        <v>ディープフリーズ+</v>
+        <v>バブルブロウ+</v>
       </c>
       <c r="C252">
         <v>6030</v>
@@ -29905,13 +29904,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E252">
-        <v>3050</v>
+        <v>3060</v>
       </c>
       <c r="F252">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G252">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="H252">
         <v>100</v>
@@ -29919,27 +29918,27 @@
     </row>
     <row r="253" spans="1:8">
       <c r="A253">
-        <v>403060</v>
+        <v>403070</v>
       </c>
       <c r="B253" t="str">
         <f>INDEX(TextData!B:B,MATCH(A253,TextData!A:A))</f>
-        <v>バブルブロウ+</v>
+        <v>アクアミラージュ+</v>
       </c>
       <c r="C253">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="D253" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C253,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E253">
-        <v>3060</v>
+        <v>3070</v>
       </c>
       <c r="F253">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G253">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H253">
         <v>100</v>
@@ -29947,27 +29946,27 @@
     </row>
     <row r="254" spans="1:8">
       <c r="A254">
-        <v>403070</v>
+        <v>403080</v>
       </c>
       <c r="B254" t="str">
         <f>INDEX(TextData!B:B,MATCH(A254,TextData!A:A))</f>
-        <v>アクアミラージュ+</v>
+        <v>フロストシールド+</v>
       </c>
       <c r="C254">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="D254" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C254,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E254">
-        <v>3070</v>
+        <v>3080</v>
       </c>
       <c r="F254">
         <v>0</v>
       </c>
       <c r="G254">
-        <v>2</v>
+        <v>30</v>
       </c>
       <c r="H254">
         <v>100</v>
@@ -29975,27 +29974,27 @@
     </row>
     <row r="255" spans="1:8">
       <c r="A255">
-        <v>403080</v>
+        <v>404010</v>
       </c>
       <c r="B255" t="str">
         <f>INDEX(TextData!B:B,MATCH(A255,TextData!A:A))</f>
-        <v>フロストシールド+</v>
+        <v>セイントレーザー+</v>
       </c>
       <c r="C255">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D255" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C255,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E255">
-        <v>3080</v>
+        <v>4010</v>
       </c>
       <c r="F255">
         <v>0</v>
       </c>
       <c r="G255">
-        <v>30</v>
+        <v>250</v>
       </c>
       <c r="H255">
         <v>100</v>
@@ -30003,11 +30002,11 @@
     </row>
     <row r="256" spans="1:8">
       <c r="A256">
-        <v>404010</v>
+        <v>404020</v>
       </c>
       <c r="B256" t="str">
         <f>INDEX(TextData!B:B,MATCH(A256,TextData!A:A))</f>
-        <v>セイントレーザー+</v>
+        <v>ペネトレイト+</v>
       </c>
       <c r="C256">
         <v>6010</v>
@@ -30017,7 +30016,7 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E256">
-        <v>4010</v>
+        <v>4020</v>
       </c>
       <c r="F256">
         <v>0</v>
@@ -30031,27 +30030,27 @@
     </row>
     <row r="257" spans="1:8">
       <c r="A257">
-        <v>404020</v>
+        <v>404030</v>
       </c>
       <c r="B257" t="str">
         <f>INDEX(TextData!B:B,MATCH(A257,TextData!A:A))</f>
-        <v>ペネトレイト+</v>
+        <v>ヒーリング+</v>
       </c>
       <c r="C257">
-        <v>6010</v>
+        <v>6210</v>
       </c>
       <c r="D257" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C257,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法の対象を変更（強化限定）</v>
       </c>
       <c r="E257">
-        <v>4020</v>
+        <v>4030</v>
       </c>
       <c r="F257">
         <v>0</v>
       </c>
       <c r="G257">
-        <v>250</v>
+        <v>31</v>
       </c>
       <c r="H257">
         <v>100</v>
@@ -30059,27 +30058,27 @@
     </row>
     <row r="258" spans="1:8">
       <c r="A258">
-        <v>404030</v>
+        <v>404040</v>
       </c>
       <c r="B258" t="str">
         <f>INDEX(TextData!B:B,MATCH(A258,TextData!A:A))</f>
-        <v>ヒーリング+</v>
+        <v>リザイアフォトン+</v>
       </c>
       <c r="C258">
-        <v>6210</v>
+        <v>6030</v>
       </c>
       <c r="D258" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C258,Define!P:P))</f>
-        <v>指定魔法の対象を変更（強化限定）</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E258">
-        <v>4030</v>
+        <v>4040</v>
       </c>
       <c r="F258">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G258">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="H258">
         <v>100</v>
@@ -30087,27 +30086,27 @@
     </row>
     <row r="259" spans="1:8">
       <c r="A259">
-        <v>404040</v>
+        <v>404050</v>
       </c>
       <c r="B259" t="str">
         <f>INDEX(TextData!B:B,MATCH(A259,TextData!A:A))</f>
-        <v>リザイアフォトン+</v>
+        <v>べネディクション+</v>
       </c>
       <c r="C259">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D259" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C259,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E259">
-        <v>4040</v>
+        <v>4050</v>
       </c>
       <c r="F259">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G259">
-        <v>30</v>
+        <v>2</v>
       </c>
       <c r="H259">
         <v>100</v>
@@ -30115,27 +30114,27 @@
     </row>
     <row r="260" spans="1:8">
       <c r="A260">
-        <v>404050</v>
+        <v>404060</v>
       </c>
       <c r="B260" t="str">
         <f>INDEX(TextData!B:B,MATCH(A260,TextData!A:A))</f>
-        <v>べネディクション+</v>
+        <v>ホーリーグレイス+</v>
       </c>
       <c r="C260">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D260" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C260,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E260">
-        <v>4050</v>
+        <v>4060</v>
       </c>
       <c r="F260">
         <v>0</v>
       </c>
       <c r="G260">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H260">
         <v>100</v>
@@ -30143,27 +30142,27 @@
     </row>
     <row r="261" spans="1:8">
       <c r="A261">
-        <v>404060</v>
+        <v>404070</v>
       </c>
       <c r="B261" t="str">
         <f>INDEX(TextData!B:B,MATCH(A261,TextData!A:A))</f>
-        <v>ホーリーグレイス+</v>
+        <v>キュアエール+</v>
       </c>
       <c r="C261">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D261" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C261,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E261">
-        <v>4060</v>
+        <v>4070</v>
       </c>
       <c r="F261">
         <v>0</v>
       </c>
       <c r="G261">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="H261">
         <v>100</v>
@@ -30171,27 +30170,27 @@
     </row>
     <row r="262" spans="1:8">
       <c r="A262">
-        <v>404070</v>
+        <v>404080</v>
       </c>
       <c r="B262" t="str">
         <f>INDEX(TextData!B:B,MATCH(A262,TextData!A:A))</f>
-        <v>キュアエール+</v>
+        <v>ラインバリア+</v>
       </c>
       <c r="C262">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D262" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C262,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E262">
-        <v>4070</v>
+        <v>4080</v>
       </c>
       <c r="F262">
         <v>0</v>
       </c>
       <c r="G262">
-        <v>25</v>
+        <v>3</v>
       </c>
       <c r="H262">
         <v>100</v>
@@ -30199,27 +30198,27 @@
     </row>
     <row r="263" spans="1:8">
       <c r="A263">
-        <v>404080</v>
+        <v>405010</v>
       </c>
       <c r="B263" t="str">
         <f>INDEX(TextData!B:B,MATCH(A263,TextData!A:A))</f>
-        <v>ラインバリア+</v>
+        <v>ダークプリズン+</v>
       </c>
       <c r="C263">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D263" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C263,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E263">
-        <v>4080</v>
+        <v>5010</v>
       </c>
       <c r="F263">
         <v>0</v>
       </c>
       <c r="G263">
-        <v>3</v>
+        <v>250</v>
       </c>
       <c r="H263">
         <v>100</v>
@@ -30227,11 +30226,11 @@
     </row>
     <row r="264" spans="1:8">
       <c r="A264">
-        <v>405010</v>
+        <v>405020</v>
       </c>
       <c r="B264" t="str">
         <f>INDEX(TextData!B:B,MATCH(A264,TextData!A:A))</f>
-        <v>ダークプリズン+</v>
+        <v>ユーサネイジア+</v>
       </c>
       <c r="C264">
         <v>6010</v>
@@ -30241,13 +30240,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E264">
-        <v>5010</v>
+        <v>5020</v>
       </c>
       <c r="F264">
         <v>0</v>
       </c>
       <c r="G264">
-        <v>250</v>
+        <v>200</v>
       </c>
       <c r="H264">
         <v>100</v>
@@ -30255,27 +30254,27 @@
     </row>
     <row r="265" spans="1:8">
       <c r="A265">
-        <v>405020</v>
+        <v>405030</v>
       </c>
       <c r="B265" t="str">
         <f>INDEX(TextData!B:B,MATCH(A265,TextData!A:A))</f>
-        <v>ユーサネイジア+</v>
+        <v>ドレインヒール+</v>
       </c>
       <c r="C265">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D265" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C265,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E265">
-        <v>5020</v>
+        <v>5030</v>
       </c>
       <c r="F265">
         <v>0</v>
       </c>
       <c r="G265">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="H265">
         <v>100</v>
@@ -30283,27 +30282,27 @@
     </row>
     <row r="266" spans="1:8">
       <c r="A266">
-        <v>405030</v>
+        <v>405040</v>
       </c>
       <c r="B266" t="str">
         <f>INDEX(TextData!B:B,MATCH(A266,TextData!A:A))</f>
-        <v>ドレインヒール+</v>
+        <v>アビサルデスペア+</v>
       </c>
       <c r="C266">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="D266" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C266,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E266">
-        <v>5030</v>
+        <v>5040</v>
       </c>
       <c r="F266">
         <v>0</v>
       </c>
       <c r="G266">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="H266">
         <v>100</v>
@@ -30311,27 +30310,27 @@
     </row>
     <row r="267" spans="1:8">
       <c r="A267">
-        <v>405040</v>
+        <v>405050</v>
       </c>
       <c r="B267" t="str">
         <f>INDEX(TextData!B:B,MATCH(A267,TextData!A:A))</f>
-        <v>アビサルデスペア+</v>
+        <v>ディプラヴィティ+</v>
       </c>
       <c r="C267">
-        <v>6020</v>
+        <v>6030</v>
       </c>
       <c r="D267" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C267,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E267">
-        <v>5040</v>
+        <v>5050</v>
       </c>
       <c r="F267">
         <v>0</v>
       </c>
       <c r="G267">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H267">
         <v>100</v>
@@ -30339,11 +30338,11 @@
     </row>
     <row r="268" spans="1:8">
       <c r="A268">
-        <v>405050</v>
+        <v>405060</v>
       </c>
       <c r="B268" t="str">
         <f>INDEX(TextData!B:B,MATCH(A268,TextData!A:A))</f>
-        <v>ディプラヴィティ+</v>
+        <v>ダークネス+</v>
       </c>
       <c r="C268">
         <v>6030</v>
@@ -30353,13 +30352,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E268">
-        <v>5050</v>
+        <v>5060</v>
       </c>
       <c r="F268">
         <v>0</v>
       </c>
       <c r="G268">
-        <v>3</v>
+        <v>50</v>
       </c>
       <c r="H268">
         <v>100</v>
@@ -30367,11 +30366,11 @@
     </row>
     <row r="269" spans="1:8">
       <c r="A269">
-        <v>405060</v>
+        <v>405070</v>
       </c>
       <c r="B269" t="str">
         <f>INDEX(TextData!B:B,MATCH(A269,TextData!A:A))</f>
-        <v>ダークネス+</v>
+        <v>シェイディークラウド+</v>
       </c>
       <c r="C269">
         <v>6030</v>
@@ -30381,13 +30380,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E269">
-        <v>5060</v>
+        <v>5070</v>
       </c>
       <c r="F269">
         <v>0</v>
       </c>
       <c r="G269">
-        <v>50</v>
+        <v>12</v>
       </c>
       <c r="H269">
         <v>100</v>
@@ -30395,11 +30394,11 @@
     </row>
     <row r="270" spans="1:8">
       <c r="A270">
-        <v>405070</v>
+        <v>405080</v>
       </c>
       <c r="B270" t="str">
         <f>INDEX(TextData!B:B,MATCH(A270,TextData!A:A))</f>
-        <v>シェイディークラウド+</v>
+        <v>ポイズンブロウ+</v>
       </c>
       <c r="C270">
         <v>6030</v>
@@ -30409,13 +30408,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E270">
-        <v>5070</v>
+        <v>5080</v>
       </c>
       <c r="F270">
         <v>0</v>
       </c>
       <c r="G270">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H270">
         <v>100</v>
@@ -30423,11 +30422,11 @@
     </row>
     <row r="271" spans="1:8">
       <c r="A271">
-        <v>405080</v>
+        <v>411010</v>
       </c>
       <c r="B271" t="str">
         <f>INDEX(TextData!B:B,MATCH(A271,TextData!A:A))</f>
-        <v>ポイズンブロウ+</v>
+        <v>ウルフソウル+</v>
       </c>
       <c r="C271">
         <v>6030</v>
@@ -30437,13 +30436,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E271">
-        <v>5080</v>
+        <v>11010</v>
       </c>
       <c r="F271">
         <v>0</v>
       </c>
       <c r="G271">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H271">
         <v>100</v>
@@ -30451,11 +30450,11 @@
     </row>
     <row r="272" spans="1:8">
       <c r="A272">
-        <v>411010</v>
+        <v>411020</v>
       </c>
       <c r="B272" t="str">
         <f>INDEX(TextData!B:B,MATCH(A272,TextData!A:A))</f>
-        <v>ウルフソウル+</v>
+        <v>プリディカメント+</v>
       </c>
       <c r="C272">
         <v>6030</v>
@@ -30465,13 +30464,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E272">
-        <v>11010</v>
+        <v>11020</v>
       </c>
       <c r="F272">
         <v>0</v>
       </c>
       <c r="G272">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="H272">
         <v>100</v>
@@ -30479,11 +30478,11 @@
     </row>
     <row r="273" spans="1:8">
       <c r="A273">
-        <v>411020</v>
+        <v>411030</v>
       </c>
       <c r="B273" t="str">
         <f>INDEX(TextData!B:B,MATCH(A273,TextData!A:A))</f>
-        <v>プリディカメント+</v>
+        <v>アサルトシフト+</v>
       </c>
       <c r="C273">
         <v>6030</v>
@@ -30493,13 +30492,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E273">
-        <v>11020</v>
+        <v>11030</v>
       </c>
       <c r="F273">
         <v>0</v>
       </c>
       <c r="G273">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="H273">
         <v>100</v>
@@ -30524,7 +30523,7 @@
         <v>11030</v>
       </c>
       <c r="F274">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G274">
         <v>8</v>
@@ -30535,27 +30534,27 @@
     </row>
     <row r="275" spans="1:8">
       <c r="A275">
-        <v>411030</v>
+        <v>411040</v>
       </c>
       <c r="B275" t="str">
         <f>INDEX(TextData!B:B,MATCH(A275,TextData!A:A))</f>
-        <v>アサルトシフト+</v>
+        <v>アクティブギフト+</v>
       </c>
       <c r="C275">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D275" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C275,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E275">
-        <v>11030</v>
+        <v>11040</v>
       </c>
       <c r="F275">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G275">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H275">
         <v>100</v>
@@ -30563,11 +30562,11 @@
     </row>
     <row r="276" spans="1:8">
       <c r="A276">
-        <v>411040</v>
+        <v>411050</v>
       </c>
       <c r="B276" t="str">
         <f>INDEX(TextData!B:B,MATCH(A276,TextData!A:A))</f>
-        <v>アクティブギフト+</v>
+        <v>イグナイテッド+</v>
       </c>
       <c r="C276">
         <v>6010</v>
@@ -30577,13 +30576,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E276">
-        <v>11040</v>
+        <v>11050</v>
       </c>
       <c r="F276">
         <v>0</v>
       </c>
       <c r="G276">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H276">
         <v>100</v>
@@ -30591,11 +30590,11 @@
     </row>
     <row r="277" spans="1:8">
       <c r="A277">
-        <v>411050</v>
+        <v>411060</v>
       </c>
       <c r="B277" t="str">
         <f>INDEX(TextData!B:B,MATCH(A277,TextData!A:A))</f>
-        <v>イグナイテッド+</v>
+        <v>ライジングファイア+</v>
       </c>
       <c r="C277">
         <v>6010</v>
@@ -30605,13 +30604,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E277">
-        <v>11050</v>
+        <v>11060</v>
       </c>
       <c r="F277">
         <v>0</v>
       </c>
       <c r="G277">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H277">
         <v>100</v>
@@ -30619,27 +30618,27 @@
     </row>
     <row r="278" spans="1:8">
       <c r="A278">
-        <v>411060</v>
+        <v>411070</v>
       </c>
       <c r="B278" t="str">
         <f>INDEX(TextData!B:B,MATCH(A278,TextData!A:A))</f>
-        <v>ライジングファイア+</v>
+        <v>ルージュバック+</v>
       </c>
       <c r="C278">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D278" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C278,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E278">
-        <v>11060</v>
+        <v>11070</v>
       </c>
       <c r="F278">
         <v>0</v>
       </c>
       <c r="G278">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H278">
         <v>100</v>
@@ -30647,11 +30646,11 @@
     </row>
     <row r="279" spans="1:8">
       <c r="A279">
-        <v>411070</v>
+        <v>411080</v>
       </c>
       <c r="B279" t="str">
         <f>INDEX(TextData!B:B,MATCH(A279,TextData!A:A))</f>
-        <v>ルージュバック+</v>
+        <v>パワーエール+</v>
       </c>
       <c r="C279">
         <v>6030</v>
@@ -30661,13 +30660,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E279">
-        <v>11070</v>
+        <v>11080</v>
       </c>
       <c r="F279">
         <v>0</v>
       </c>
       <c r="G279">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H279">
         <v>100</v>
@@ -30675,11 +30674,11 @@
     </row>
     <row r="280" spans="1:8">
       <c r="A280">
-        <v>411080</v>
+        <v>411090</v>
       </c>
       <c r="B280" t="str">
         <f>INDEX(TextData!B:B,MATCH(A280,TextData!A:A))</f>
-        <v>パワーエール+</v>
+        <v>スレイプニル+</v>
       </c>
       <c r="C280">
         <v>6030</v>
@@ -30689,13 +30688,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E280">
-        <v>11080</v>
+        <v>11090</v>
       </c>
       <c r="F280">
         <v>0</v>
       </c>
       <c r="G280">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="H280">
         <v>100</v>
@@ -30703,27 +30702,27 @@
     </row>
     <row r="281" spans="1:8">
       <c r="A281">
-        <v>411090</v>
+        <v>412010</v>
       </c>
       <c r="B281" t="str">
         <f>INDEX(TextData!B:B,MATCH(A281,TextData!A:A))</f>
-        <v>スレイプニル+</v>
+        <v>エクステンション+</v>
       </c>
       <c r="C281">
-        <v>6030</v>
+        <v>6210</v>
       </c>
       <c r="D281" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C281,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法の対象を変更（強化限定）</v>
       </c>
       <c r="E281">
-        <v>11090</v>
+        <v>12010</v>
       </c>
       <c r="F281">
         <v>0</v>
       </c>
       <c r="G281">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H281">
         <v>100</v>
@@ -30731,27 +30730,27 @@
     </row>
     <row r="282" spans="1:8">
       <c r="A282">
-        <v>412010</v>
+        <v>412020</v>
       </c>
       <c r="B282" t="str">
         <f>INDEX(TextData!B:B,MATCH(A282,TextData!A:A))</f>
-        <v>エクステンション+</v>
+        <v>ヘブンリーラック+</v>
       </c>
       <c r="C282">
-        <v>6210</v>
+        <v>6030</v>
       </c>
       <c r="D282" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C282,Define!P:P))</f>
-        <v>指定魔法の対象を変更（強化限定）</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E282">
-        <v>12010</v>
+        <v>12020</v>
       </c>
       <c r="F282">
         <v>0</v>
       </c>
       <c r="G282">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="H282">
         <v>100</v>
@@ -30759,11 +30758,11 @@
     </row>
     <row r="283" spans="1:8">
       <c r="A283">
-        <v>412020</v>
+        <v>412030</v>
       </c>
       <c r="B283" t="str">
         <f>INDEX(TextData!B:B,MATCH(A283,TextData!A:A))</f>
-        <v>ヘブンリーラック+</v>
+        <v>スウィフトカレント+</v>
       </c>
       <c r="C283">
         <v>6030</v>
@@ -30773,13 +30772,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E283">
-        <v>12020</v>
+        <v>12030</v>
       </c>
       <c r="F283">
         <v>0</v>
       </c>
       <c r="G283">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="H283">
         <v>100</v>
@@ -30787,11 +30786,11 @@
     </row>
     <row r="284" spans="1:8">
       <c r="A284">
-        <v>412030</v>
+        <v>412040</v>
       </c>
       <c r="B284" t="str">
         <f>INDEX(TextData!B:B,MATCH(A284,TextData!A:A))</f>
-        <v>スウィフトカレント+</v>
+        <v>イヴェイドオール+</v>
       </c>
       <c r="C284">
         <v>6030</v>
@@ -30801,7 +30800,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E284">
-        <v>12030</v>
+        <v>12040</v>
       </c>
       <c r="F284">
         <v>0</v>
@@ -30815,27 +30814,27 @@
     </row>
     <row r="285" spans="1:8">
       <c r="A285">
-        <v>412040</v>
+        <v>412050</v>
       </c>
       <c r="B285" t="str">
         <f>INDEX(TextData!B:B,MATCH(A285,TextData!A:A))</f>
-        <v>イヴェイドオール+</v>
+        <v>クイックムーブ+</v>
       </c>
       <c r="C285">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D285" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C285,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E285">
-        <v>12040</v>
+        <v>12050</v>
       </c>
       <c r="F285">
         <v>0</v>
       </c>
       <c r="G285">
-        <v>10</v>
+        <v>400</v>
       </c>
       <c r="H285">
         <v>100</v>
@@ -30843,11 +30842,11 @@
     </row>
     <row r="286" spans="1:8">
       <c r="A286">
-        <v>412050</v>
+        <v>412060</v>
       </c>
       <c r="B286" t="str">
         <f>INDEX(TextData!B:B,MATCH(A286,TextData!A:A))</f>
-        <v>クイックムーブ+</v>
+        <v>チェイスマジック+</v>
       </c>
       <c r="C286">
         <v>6010</v>
@@ -30857,13 +30856,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E286">
-        <v>12050</v>
+        <v>12060</v>
       </c>
       <c r="F286">
         <v>0</v>
       </c>
       <c r="G286">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="H286">
         <v>100</v>
@@ -30871,27 +30870,27 @@
     </row>
     <row r="287" spans="1:8">
       <c r="A287">
-        <v>412060</v>
+        <v>412070</v>
       </c>
       <c r="B287" t="str">
         <f>INDEX(TextData!B:B,MATCH(A287,TextData!A:A))</f>
-        <v>チェイスマジック+</v>
+        <v>ソーサリーコネクト+</v>
       </c>
       <c r="C287">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D287" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C287,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E287">
-        <v>12060</v>
+        <v>12070</v>
       </c>
       <c r="F287">
         <v>0</v>
       </c>
       <c r="G287">
-        <v>300</v>
+        <v>16</v>
       </c>
       <c r="H287">
         <v>100</v>
@@ -30899,27 +30898,27 @@
     </row>
     <row r="288" spans="1:8">
       <c r="A288">
-        <v>412070</v>
+        <v>412080</v>
       </c>
       <c r="B288" t="str">
         <f>INDEX(TextData!B:B,MATCH(A288,TextData!A:A))</f>
-        <v>ソーサリーコネクト+</v>
+        <v>ウィンドライズ+</v>
       </c>
       <c r="C288">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D288" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C288,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E288">
-        <v>12070</v>
+        <v>12080</v>
       </c>
       <c r="F288">
         <v>0</v>
       </c>
       <c r="G288">
-        <v>16</v>
+        <v>300</v>
       </c>
       <c r="H288">
         <v>100</v>
@@ -30927,11 +30926,11 @@
     </row>
     <row r="289" spans="1:8">
       <c r="A289">
-        <v>412080</v>
+        <v>412090</v>
       </c>
       <c r="B289" t="str">
         <f>INDEX(TextData!B:B,MATCH(A289,TextData!A:A))</f>
-        <v>ウィンドライズ+</v>
+        <v>アウトオブオーダー+</v>
       </c>
       <c r="C289">
         <v>6010</v>
@@ -30941,13 +30940,13 @@
         <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E289">
-        <v>12080</v>
+        <v>12090</v>
       </c>
       <c r="F289">
         <v>0</v>
       </c>
       <c r="G289">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="H289">
         <v>100</v>
@@ -30955,27 +30954,27 @@
     </row>
     <row r="290" spans="1:8">
       <c r="A290">
-        <v>412090</v>
+        <v>413010</v>
       </c>
       <c r="B290" t="str">
         <f>INDEX(TextData!B:B,MATCH(A290,TextData!A:A))</f>
-        <v>アウトオブオーダー+</v>
+        <v>アーマーコード+</v>
       </c>
       <c r="C290">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D290" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C290,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E290">
-        <v>12090</v>
+        <v>13010</v>
       </c>
       <c r="F290">
         <v>0</v>
       </c>
       <c r="G290">
-        <v>400</v>
+        <v>8</v>
       </c>
       <c r="H290">
         <v>100</v>
@@ -30983,11 +30982,11 @@
     </row>
     <row r="291" spans="1:8">
       <c r="A291">
-        <v>413010</v>
+        <v>413020</v>
       </c>
       <c r="B291" t="str">
         <f>INDEX(TextData!B:B,MATCH(A291,TextData!A:A))</f>
-        <v>アーマーコード+</v>
+        <v>クイックバリア+</v>
       </c>
       <c r="C291">
         <v>6030</v>
@@ -30997,13 +30996,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E291">
-        <v>13010</v>
+        <v>13020</v>
       </c>
       <c r="F291">
         <v>0</v>
       </c>
       <c r="G291">
-        <v>8</v>
+        <v>50</v>
       </c>
       <c r="H291">
         <v>100</v>
@@ -31011,27 +31010,27 @@
     </row>
     <row r="292" spans="1:8">
       <c r="A292">
-        <v>413020</v>
+        <v>413030</v>
       </c>
       <c r="B292" t="str">
         <f>INDEX(TextData!B:B,MATCH(A292,TextData!A:A))</f>
-        <v>クイックバリア+</v>
+        <v>クイックキュア+</v>
       </c>
       <c r="C292">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D292" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C292,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E292">
-        <v>13020</v>
+        <v>14090</v>
       </c>
       <c r="F292">
         <v>0</v>
       </c>
       <c r="G292">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H292">
         <v>100</v>
@@ -31039,27 +31038,27 @@
     </row>
     <row r="293" spans="1:8">
       <c r="A293">
-        <v>413030</v>
+        <v>413040</v>
       </c>
       <c r="B293" t="str">
         <f>INDEX(TextData!B:B,MATCH(A293,TextData!A:A))</f>
-        <v>クイックキュア+</v>
+        <v>セルフシールド+</v>
       </c>
       <c r="C293">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D293" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C293,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E293">
-        <v>14090</v>
+        <v>13040</v>
       </c>
       <c r="F293">
         <v>0</v>
       </c>
       <c r="G293">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="H293">
         <v>100</v>
@@ -31067,27 +31066,27 @@
     </row>
     <row r="294" spans="1:8">
       <c r="A294">
-        <v>413040</v>
+        <v>413050</v>
       </c>
       <c r="B294" t="str">
         <f>INDEX(TextData!B:B,MATCH(A294,TextData!A:A))</f>
-        <v>セルフシールド+</v>
+        <v>パッシブジャミング+</v>
       </c>
       <c r="C294">
-        <v>6030</v>
+        <v>6080</v>
       </c>
       <c r="D294" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C294,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E294">
-        <v>13040</v>
+        <v>14090</v>
       </c>
       <c r="F294">
         <v>0</v>
       </c>
       <c r="G294">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="H294">
         <v>100</v>
@@ -31095,11 +31094,11 @@
     </row>
     <row r="295" spans="1:8">
       <c r="A295">
-        <v>413050</v>
+        <v>413060</v>
       </c>
       <c r="B295" t="str">
         <f>INDEX(TextData!B:B,MATCH(A295,TextData!A:A))</f>
-        <v>パッシブジャミング+</v>
+        <v>サプライカバー+</v>
       </c>
       <c r="C295">
         <v>6080</v>
@@ -31123,27 +31122,27 @@
     </row>
     <row r="296" spans="1:8">
       <c r="A296">
-        <v>413060</v>
+        <v>413070</v>
       </c>
       <c r="B296" t="str">
         <f>INDEX(TextData!B:B,MATCH(A296,TextData!A:A))</f>
-        <v>サプライカバー+</v>
+        <v>アシッドラッシュ+</v>
       </c>
       <c r="C296">
-        <v>6080</v>
+        <v>6010</v>
       </c>
       <c r="D296" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C296,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E296">
-        <v>14090</v>
+        <v>13070</v>
       </c>
       <c r="F296">
         <v>0</v>
       </c>
       <c r="G296">
-        <v>1</v>
+        <v>400</v>
       </c>
       <c r="H296">
         <v>100</v>
@@ -31151,27 +31150,27 @@
     </row>
     <row r="297" spans="1:8">
       <c r="A297">
-        <v>413070</v>
+        <v>413080</v>
       </c>
       <c r="B297" t="str">
         <f>INDEX(TextData!B:B,MATCH(A297,TextData!A:A))</f>
-        <v>アシッドラッシュ+</v>
+        <v>ライフスティール+</v>
       </c>
       <c r="C297">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D297" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C297,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E297">
-        <v>13070</v>
+        <v>13080</v>
       </c>
       <c r="F297">
         <v>0</v>
       </c>
       <c r="G297">
-        <v>400</v>
+        <v>50</v>
       </c>
       <c r="H297">
         <v>100</v>
@@ -31179,11 +31178,11 @@
     </row>
     <row r="298" spans="1:8">
       <c r="A298">
-        <v>413080</v>
+        <v>413090</v>
       </c>
       <c r="B298" t="str">
         <f>INDEX(TextData!B:B,MATCH(A298,TextData!A:A))</f>
-        <v>ライフスティール+</v>
+        <v>アイスセイバー+</v>
       </c>
       <c r="C298">
         <v>6030</v>
@@ -31193,7 +31192,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E298">
-        <v>13080</v>
+        <v>13090</v>
       </c>
       <c r="F298">
         <v>0</v>
@@ -31207,27 +31206,27 @@
     </row>
     <row r="299" spans="1:8">
       <c r="A299">
-        <v>413090</v>
+        <v>414010</v>
       </c>
       <c r="B299" t="str">
         <f>INDEX(TextData!B:B,MATCH(A299,TextData!A:A))</f>
-        <v>アイスセイバー+</v>
+        <v>ディバインシールド+</v>
       </c>
       <c r="C299">
-        <v>6030</v>
+        <v>6020</v>
       </c>
       <c r="D299" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C299,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E299">
-        <v>13090</v>
+        <v>14010</v>
       </c>
       <c r="F299">
         <v>0</v>
       </c>
       <c r="G299">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H299">
         <v>100</v>
@@ -31235,27 +31234,27 @@
     </row>
     <row r="300" spans="1:8">
       <c r="A300">
-        <v>414010</v>
+        <v>414020</v>
       </c>
       <c r="B300" t="str">
         <f>INDEX(TextData!B:B,MATCH(A300,TextData!A:A))</f>
-        <v>ディバインシールド+</v>
+        <v>ライフディバイド+</v>
       </c>
       <c r="C300">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="D300" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C300,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E300">
-        <v>14010</v>
+        <v>14020</v>
       </c>
       <c r="F300">
         <v>0</v>
       </c>
       <c r="G300">
-        <v>2</v>
+        <v>50</v>
       </c>
       <c r="H300">
         <v>100</v>
@@ -31263,27 +31262,27 @@
     </row>
     <row r="301" spans="1:8">
       <c r="A301">
-        <v>414020</v>
+        <v>414030</v>
       </c>
       <c r="B301" t="str">
         <f>INDEX(TextData!B:B,MATCH(A301,TextData!A:A))</f>
-        <v>ライフディバイド+</v>
+        <v>エイミングスコープ+</v>
       </c>
       <c r="C301">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D301" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C301,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E301">
-        <v>14020</v>
+        <v>14030</v>
       </c>
       <c r="F301">
         <v>0</v>
       </c>
       <c r="G301">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H301">
         <v>100</v>
@@ -31291,11 +31290,11 @@
     </row>
     <row r="302" spans="1:8">
       <c r="A302">
-        <v>414030</v>
+        <v>414040</v>
       </c>
       <c r="B302" t="str">
         <f>INDEX(TextData!B:B,MATCH(A302,TextData!A:A))</f>
-        <v>エイミングスコープ+</v>
+        <v>リジェネレーション+</v>
       </c>
       <c r="C302">
         <v>6030</v>
@@ -31305,7 +31304,7 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E302">
-        <v>14030</v>
+        <v>14040</v>
       </c>
       <c r="F302">
         <v>0</v>
@@ -31319,11 +31318,11 @@
     </row>
     <row r="303" spans="1:8">
       <c r="A303">
-        <v>414040</v>
+        <v>414050</v>
       </c>
       <c r="B303" t="str">
         <f>INDEX(TextData!B:B,MATCH(A303,TextData!A:A))</f>
-        <v>リジェネレーション+</v>
+        <v>ホープフルアイリス+</v>
       </c>
       <c r="C303">
         <v>6030</v>
@@ -31333,13 +31332,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E303">
-        <v>14040</v>
+        <v>14050</v>
       </c>
       <c r="F303">
         <v>0</v>
       </c>
       <c r="G303">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="H303">
         <v>100</v>
@@ -31347,27 +31346,27 @@
     </row>
     <row r="304" spans="1:8">
       <c r="A304">
-        <v>414050</v>
+        <v>414060</v>
       </c>
       <c r="B304" t="str">
         <f>INDEX(TextData!B:B,MATCH(A304,TextData!A:A))</f>
-        <v>ホープフルアイリス+</v>
+        <v>パッシブサプライ+</v>
       </c>
       <c r="C304">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D304" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C304,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E304">
-        <v>14050</v>
+        <v>14060</v>
       </c>
       <c r="F304">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G304">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H304">
         <v>100</v>
@@ -31375,27 +31374,27 @@
     </row>
     <row r="305" spans="1:8">
       <c r="A305">
-        <v>414060</v>
+        <v>414070</v>
       </c>
       <c r="B305" t="str">
         <f>INDEX(TextData!B:B,MATCH(A305,TextData!A:A))</f>
-        <v>パッシブサプライ+</v>
+        <v>ホーミングクルセイド+</v>
       </c>
       <c r="C305">
-        <v>6010</v>
+        <v>6020</v>
       </c>
       <c r="D305" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C305,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam2を増やす</v>
       </c>
       <c r="E305">
-        <v>14060</v>
+        <v>14070</v>
       </c>
       <c r="F305">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G305">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H305">
         <v>100</v>
@@ -31403,27 +31402,27 @@
     </row>
     <row r="306" spans="1:8">
       <c r="A306">
-        <v>414070</v>
+        <v>414080</v>
       </c>
       <c r="B306" t="str">
         <f>INDEX(TextData!B:B,MATCH(A306,TextData!A:A))</f>
-        <v>ホーミングクルセイド+</v>
+        <v>クイックヒール+</v>
       </c>
       <c r="C306">
-        <v>6020</v>
+        <v>6010</v>
       </c>
       <c r="D306" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C306,Define!P:P))</f>
-        <v>指定のFeatureのParam2を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E306">
-        <v>14070</v>
+        <v>14080</v>
       </c>
       <c r="F306">
         <v>0</v>
       </c>
       <c r="G306">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="H306">
         <v>100</v>
@@ -31431,27 +31430,27 @@
     </row>
     <row r="307" spans="1:8">
       <c r="A307">
-        <v>414080</v>
+        <v>414090</v>
       </c>
       <c r="B307" t="str">
         <f>INDEX(TextData!B:B,MATCH(A307,TextData!A:A))</f>
-        <v>クイックヒール+</v>
+        <v>リレイズ+</v>
       </c>
       <c r="C307">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D307" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C307,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E307">
-        <v>14080</v>
+        <v>14090</v>
       </c>
       <c r="F307">
         <v>0</v>
       </c>
       <c r="G307">
-        <v>15</v>
+        <v>4</v>
       </c>
       <c r="H307">
         <v>100</v>
@@ -31459,27 +31458,27 @@
     </row>
     <row r="308" spans="1:8">
       <c r="A308">
-        <v>414090</v>
+        <v>415010</v>
       </c>
       <c r="B308" t="str">
         <f>INDEX(TextData!B:B,MATCH(A308,TextData!A:A))</f>
-        <v>リレイズ+</v>
+        <v>イーグルアイ+</v>
       </c>
       <c r="C308">
-        <v>6080</v>
+        <v>6030</v>
       </c>
       <c r="D308" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C308,Define!P:P))</f>
-        <v>指定魔法のCTリセット値を変更する</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E308">
-        <v>14090</v>
+        <v>15010</v>
       </c>
       <c r="F308">
         <v>0</v>
       </c>
       <c r="G308">
-        <v>4</v>
+        <v>25</v>
       </c>
       <c r="H308">
         <v>100</v>
@@ -31487,11 +31486,11 @@
     </row>
     <row r="309" spans="1:8">
       <c r="A309">
-        <v>415010</v>
+        <v>415020</v>
       </c>
       <c r="B309" t="str">
         <f>INDEX(TextData!B:B,MATCH(A309,TextData!A:A))</f>
-        <v>イーグルアイ+</v>
+        <v>ネヴァーエンド+</v>
       </c>
       <c r="C309">
         <v>6030</v>
@@ -31501,13 +31500,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E309">
-        <v>15010</v>
+        <v>15020</v>
       </c>
       <c r="F309">
         <v>0</v>
       </c>
       <c r="G309">
-        <v>25</v>
+        <v>50</v>
       </c>
       <c r="H309">
         <v>100</v>
@@ -31515,27 +31514,27 @@
     </row>
     <row r="310" spans="1:8">
       <c r="A310">
-        <v>415020</v>
+        <v>415030</v>
       </c>
       <c r="B310" t="str">
         <f>INDEX(TextData!B:B,MATCH(A310,TextData!A:A))</f>
-        <v>ネヴァーエンド+</v>
+        <v>グレイブアクト+</v>
       </c>
       <c r="C310">
-        <v>6030</v>
+        <v>6010</v>
       </c>
       <c r="D310" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C310,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
+        <v>指定のFeatureのParam1を増やす</v>
       </c>
       <c r="E310">
-        <v>15020</v>
+        <v>15030</v>
       </c>
       <c r="F310">
         <v>0</v>
       </c>
       <c r="G310">
-        <v>50</v>
+        <v>2</v>
       </c>
       <c r="H310">
         <v>100</v>
@@ -31543,27 +31542,27 @@
     </row>
     <row r="311" spans="1:8">
       <c r="A311">
-        <v>415030</v>
+        <v>415040</v>
       </c>
       <c r="B311" t="str">
         <f>INDEX(TextData!B:B,MATCH(A311,TextData!A:A))</f>
-        <v>グレイブアクト+</v>
+        <v>スカルグラッジ+</v>
       </c>
       <c r="C311">
-        <v>6010</v>
+        <v>6030</v>
       </c>
       <c r="D311" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C311,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E311">
-        <v>15030</v>
+        <v>15040</v>
       </c>
       <c r="F311">
         <v>0</v>
       </c>
       <c r="G311">
-        <v>2</v>
+        <v>10</v>
       </c>
       <c r="H311">
         <v>100</v>
@@ -31571,11 +31570,11 @@
     </row>
     <row r="312" spans="1:8">
       <c r="A312">
-        <v>415040</v>
+        <v>415050</v>
       </c>
       <c r="B312" t="str">
         <f>INDEX(TextData!B:B,MATCH(A312,TextData!A:A))</f>
-        <v>スカルグラッジ+</v>
+        <v>ネガティブドレイン+</v>
       </c>
       <c r="C312">
         <v>6030</v>
@@ -31585,13 +31584,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E312">
-        <v>15040</v>
+        <v>15050</v>
       </c>
       <c r="F312">
         <v>0</v>
       </c>
       <c r="G312">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="H312">
         <v>100</v>
@@ -31599,11 +31598,11 @@
     </row>
     <row r="313" spans="1:8">
       <c r="A313">
-        <v>415050</v>
+        <v>415060</v>
       </c>
       <c r="B313" t="str">
         <f>INDEX(TextData!B:B,MATCH(A313,TextData!A:A))</f>
-        <v>ネガティブドレイン+</v>
+        <v>アンデッドペイン+</v>
       </c>
       <c r="C313">
         <v>6030</v>
@@ -31613,13 +31612,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E313">
-        <v>15050</v>
+        <v>15060</v>
       </c>
       <c r="F313">
         <v>0</v>
       </c>
       <c r="G313">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="H313">
         <v>100</v>
@@ -31627,11 +31626,11 @@
     </row>
     <row r="314" spans="1:8">
       <c r="A314">
-        <v>415060</v>
+        <v>415070</v>
       </c>
       <c r="B314" t="str">
         <f>INDEX(TextData!B:B,MATCH(A314,TextData!A:A))</f>
-        <v>アンデッドペイン+</v>
+        <v>ジャックポッド+</v>
       </c>
       <c r="C314">
         <v>6030</v>
@@ -31641,13 +31640,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E314">
-        <v>15060</v>
+        <v>15070</v>
       </c>
       <c r="F314">
         <v>0</v>
       </c>
       <c r="G314">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="H314">
         <v>100</v>
@@ -31655,11 +31654,11 @@
     </row>
     <row r="315" spans="1:8">
       <c r="A315">
-        <v>415070</v>
+        <v>415080</v>
       </c>
       <c r="B315" t="str">
         <f>INDEX(TextData!B:B,MATCH(A315,TextData!A:A))</f>
-        <v>ジャックポッド+</v>
+        <v>ヒールハント+</v>
       </c>
       <c r="C315">
         <v>6030</v>
@@ -31669,13 +31668,13 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E315">
-        <v>15070</v>
+        <v>15080</v>
       </c>
       <c r="F315">
         <v>0</v>
       </c>
       <c r="G315">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="H315">
         <v>100</v>
@@ -31683,11 +31682,11 @@
     </row>
     <row r="316" spans="1:8">
       <c r="A316">
-        <v>415080</v>
+        <v>415090</v>
       </c>
       <c r="B316" t="str">
         <f>INDEX(TextData!B:B,MATCH(A316,TextData!A:A))</f>
-        <v>ヒールハント+</v>
+        <v>クイックカース+</v>
       </c>
       <c r="C316">
         <v>6030</v>
@@ -31697,43 +31696,15 @@
         <v>指定のFeatureのParam3を増やす</v>
       </c>
       <c r="E316">
-        <v>15080</v>
+        <v>15090</v>
       </c>
       <c r="F316">
         <v>0</v>
       </c>
       <c r="G316">
-        <v>50</v>
+        <v>35</v>
       </c>
       <c r="H316">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="317" spans="1:8">
-      <c r="A317">
-        <v>415090</v>
-      </c>
-      <c r="B317" t="str">
-        <f>INDEX(TextData!B:B,MATCH(A317,TextData!A:A))</f>
-        <v>クイックカース+</v>
-      </c>
-      <c r="C317">
-        <v>6030</v>
-      </c>
-      <c r="D317" t="str">
-        <f>INDEX(Define!Q:Q,MATCH(C317,Define!P:P))</f>
-        <v>指定のFeatureのParam3を増やす</v>
-      </c>
-      <c r="E317">
-        <v>15090</v>
-      </c>
-      <c r="F317">
-        <v>0</v>
-      </c>
-      <c r="G317">
-        <v>35</v>
-      </c>
-      <c r="H317">
         <v>100</v>
       </c>
     </row>
@@ -35902,7 +35873,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="37" ht="26" spans="1:4">
+    <row r="37" spans="1:4">
       <c r="A37">
         <v>4050</v>
       </c>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6620" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6620"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="828" uniqueCount="720">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="829" uniqueCount="721">
   <si>
     <t>Id</t>
   </si>
@@ -1855,28 +1855,31 @@
     <t>自身のMpが〇以下</t>
   </si>
   <si>
+    <t>かばう専用。割り込みの最優先</t>
+  </si>
+  <si>
+    <t>ステータスアップ</t>
+  </si>
+  <si>
+    <t>自身のHpを1にする</t>
+  </si>
+  <si>
+    <t>自身のMpが〇以上</t>
+  </si>
+  <si>
     <t>ターン開始前</t>
   </si>
   <si>
-    <t>ステータスアップ</t>
-  </si>
-  <si>
-    <t>自身のHpを1にする</t>
-  </si>
-  <si>
-    <t>自身のMpが〇以上</t>
+    <t>魔法入手</t>
+  </si>
+  <si>
+    <t>対象のHpを1にする</t>
+  </si>
+  <si>
+    <t>Mp〇未満の味方</t>
   </si>
   <si>
     <t>ターン開始後</t>
-  </si>
-  <si>
-    <t>魔法入手</t>
-  </si>
-  <si>
-    <t>対象のHpを1にする</t>
-  </si>
-  <si>
-    <t>Mp〇未満の味方</t>
   </si>
   <si>
     <t>最大HpとMpアップ</t>
@@ -2373,10 +2376,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2395,6 +2398,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color rgb="FF3F3F76"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -2409,17 +2419,9 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2432,7 +2434,7 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2448,7 +2450,14 @@
     <font>
       <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2461,8 +2470,17 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2501,31 +2519,16 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <sz val="13"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2553,19 +2556,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2577,31 +2592,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2625,13 +2622,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2649,31 +2658,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2685,19 +2712,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2709,31 +2724,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2762,24 +2765,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -2804,17 +2789,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
+      <left/>
+      <right/>
       <top style="thin">
-        <color rgb="FF3F3F3F"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2834,13 +2815,35 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left/>
       <right/>
-      <top style="thin">
+      <top/>
+      <bottom style="medium">
         <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2852,145 +2855,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="18" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="21" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -14513,14 +14516,14 @@
         <v>相手</v>
       </c>
       <c r="Q141">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R141" t="str">
         <f>INDEX(Define!N:N,MATCH(Q141,Define!M:M))</f>
-        <v>列</v>
+        <v>全体</v>
       </c>
       <c r="S141">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="T141">
         <v>1</v>
@@ -32662,7 +32665,7 @@
         <v>味方が攻撃を受ける。Param2で対象指定</v>
       </c>
       <c r="E34">
-        <v>3</v>
+        <v>41</v>
       </c>
       <c r="F34">
         <v>0</v>
@@ -38878,7 +38881,7 @@
         <v>548</v>
       </c>
       <c r="Y14">
-        <v>51</v>
+        <v>41</v>
       </c>
       <c r="Z14" t="s">
         <v>549</v>
@@ -38904,7 +38907,7 @@
         <v>552</v>
       </c>
       <c r="Y15">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="Z15" t="s">
         <v>553</v>
@@ -38929,11 +38932,17 @@
       <c r="V16" t="s">
         <v>556</v>
       </c>
+      <c r="Y16">
+        <v>52</v>
+      </c>
+      <c r="Z16" t="s">
+        <v>557</v>
+      </c>
       <c r="AB16">
         <v>404</v>
       </c>
       <c r="AC16" t="s">
-        <v>557</v>
+        <v>558</v>
       </c>
     </row>
     <row r="17" spans="16:29">
@@ -38941,19 +38950,19 @@
         <v>2040</v>
       </c>
       <c r="Q17" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="U17">
         <v>3040</v>
       </c>
       <c r="V17" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="AB17">
         <v>501</v>
       </c>
       <c r="AC17" t="s">
-        <v>560</v>
+        <v>561</v>
       </c>
     </row>
     <row r="18" spans="16:29">
@@ -38961,19 +38970,19 @@
         <v>2110</v>
       </c>
       <c r="Q18" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="U18">
         <v>3050</v>
       </c>
       <c r="V18" t="s">
-        <v>562</v>
+        <v>563</v>
       </c>
       <c r="AB18">
         <v>502</v>
       </c>
       <c r="AC18" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
     </row>
     <row r="19" spans="16:29">
@@ -38981,19 +38990,19 @@
         <v>2120</v>
       </c>
       <c r="Q19" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="U19">
         <v>3060</v>
       </c>
       <c r="V19" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="AB19">
         <v>503</v>
       </c>
       <c r="AC19" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
     </row>
     <row r="20" spans="16:29">
@@ -39001,19 +39010,19 @@
         <v>2130</v>
       </c>
       <c r="Q20" t="s">
-        <v>567</v>
+        <v>568</v>
       </c>
       <c r="U20">
         <v>4010</v>
       </c>
       <c r="V20" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="AB20">
         <v>504</v>
       </c>
       <c r="AC20" t="s">
-        <v>569</v>
+        <v>570</v>
       </c>
     </row>
     <row r="21" spans="16:29">
@@ -39021,19 +39030,19 @@
         <v>3010</v>
       </c>
       <c r="Q21" t="s">
-        <v>570</v>
+        <v>571</v>
       </c>
       <c r="U21">
         <v>4020</v>
       </c>
       <c r="V21" t="s">
-        <v>571</v>
+        <v>572</v>
       </c>
       <c r="AB21">
         <v>505</v>
       </c>
       <c r="AC21" t="s">
-        <v>572</v>
+        <v>573</v>
       </c>
     </row>
     <row r="22" spans="16:29">
@@ -39041,19 +39050,19 @@
         <v>3020</v>
       </c>
       <c r="Q22" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="U22">
         <v>5010</v>
       </c>
       <c r="V22" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="AB22">
         <v>506</v>
       </c>
       <c r="AC22" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
     </row>
     <row r="23" spans="16:29">
@@ -39061,19 +39070,19 @@
         <v>3030</v>
       </c>
       <c r="Q23" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="U23">
         <v>5020</v>
       </c>
       <c r="V23" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="AB23">
         <v>507</v>
       </c>
       <c r="AC23" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" spans="16:29">
@@ -39081,13 +39090,13 @@
         <v>3040</v>
       </c>
       <c r="Q24" t="s">
-        <v>579</v>
+        <v>580</v>
       </c>
       <c r="U24">
         <v>5030</v>
       </c>
       <c r="V24" t="s">
-        <v>580</v>
+        <v>581</v>
       </c>
       <c r="AB24">
         <v>508</v>
@@ -39101,13 +39110,13 @@
         <v>3050</v>
       </c>
       <c r="Q25" t="s">
-        <v>581</v>
+        <v>582</v>
       </c>
       <c r="U25">
         <v>5040</v>
       </c>
       <c r="V25" t="s">
-        <v>582</v>
+        <v>583</v>
       </c>
       <c r="AB25">
         <v>509</v>
@@ -39121,13 +39130,13 @@
         <v>3060</v>
       </c>
       <c r="Q26" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="U26">
         <v>5050</v>
       </c>
       <c r="V26" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
     </row>
     <row r="27" spans="16:22">
@@ -39135,13 +39144,13 @@
         <v>3070</v>
       </c>
       <c r="Q27" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="U27">
         <v>5060</v>
       </c>
       <c r="V27" t="s">
-        <v>586</v>
+        <v>587</v>
       </c>
     </row>
     <row r="28" spans="16:22">
@@ -39149,13 +39158,13 @@
         <v>4010</v>
       </c>
       <c r="Q28" t="s">
-        <v>587</v>
+        <v>588</v>
       </c>
       <c r="U28">
         <v>5070</v>
       </c>
       <c r="V28" t="s">
-        <v>588</v>
+        <v>589</v>
       </c>
     </row>
     <row r="29" spans="16:22">
@@ -39163,13 +39172,13 @@
         <v>4020</v>
       </c>
       <c r="Q29" t="s">
-        <v>589</v>
+        <v>590</v>
       </c>
       <c r="U29">
         <v>5080</v>
       </c>
       <c r="V29" t="s">
-        <v>590</v>
+        <v>591</v>
       </c>
     </row>
     <row r="30" spans="16:22">
@@ -39177,13 +39186,13 @@
         <v>4030</v>
       </c>
       <c r="Q30" t="s">
-        <v>591</v>
+        <v>592</v>
       </c>
       <c r="U30">
         <v>5090</v>
       </c>
       <c r="V30" t="s">
-        <v>592</v>
+        <v>593</v>
       </c>
     </row>
     <row r="31" spans="16:22">
@@ -39191,13 +39200,13 @@
         <v>4040</v>
       </c>
       <c r="Q31" t="s">
-        <v>593</v>
+        <v>594</v>
       </c>
       <c r="U31">
         <v>5100</v>
       </c>
       <c r="V31" t="s">
-        <v>594</v>
+        <v>595</v>
       </c>
     </row>
     <row r="32" spans="16:22">
@@ -39205,13 +39214,13 @@
         <v>5010</v>
       </c>
       <c r="Q32" t="s">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="U32">
         <v>5110</v>
       </c>
       <c r="V32" t="s">
-        <v>596</v>
+        <v>597</v>
       </c>
     </row>
     <row r="33" spans="16:22">
@@ -39219,13 +39228,13 @@
         <v>5011</v>
       </c>
       <c r="Q33" t="s">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="U33">
         <v>5120</v>
       </c>
       <c r="V33" t="s">
-        <v>598</v>
+        <v>599</v>
       </c>
     </row>
     <row r="34" spans="16:22">
@@ -39233,13 +39242,13 @@
         <v>5012</v>
       </c>
       <c r="Q34" t="s">
-        <v>599</v>
+        <v>600</v>
       </c>
       <c r="U34">
         <v>5130</v>
       </c>
       <c r="V34" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
     </row>
     <row r="35" spans="16:22">
@@ -39247,13 +39256,13 @@
         <v>5020</v>
       </c>
       <c r="Q35" t="s">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="U35">
         <v>5140</v>
       </c>
       <c r="V35" t="s">
-        <v>602</v>
+        <v>603</v>
       </c>
     </row>
     <row r="36" spans="16:22">
@@ -39261,13 +39270,13 @@
         <v>5030</v>
       </c>
       <c r="Q36" t="s">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="U36">
         <v>6010</v>
       </c>
       <c r="V36" t="s">
-        <v>604</v>
+        <v>605</v>
       </c>
     </row>
     <row r="37" spans="16:22">
@@ -39275,13 +39284,13 @@
         <v>5040</v>
       </c>
       <c r="Q37" t="s">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="U37">
         <v>6020</v>
       </c>
       <c r="V37" t="s">
-        <v>606</v>
+        <v>607</v>
       </c>
     </row>
     <row r="38" spans="16:22">
@@ -39289,13 +39298,13 @@
         <v>5050</v>
       </c>
       <c r="Q38" t="s">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="U38">
         <v>6030</v>
       </c>
       <c r="V38" t="s">
-        <v>608</v>
+        <v>609</v>
       </c>
     </row>
     <row r="39" spans="16:22">
@@ -39303,13 +39312,13 @@
         <v>6010</v>
       </c>
       <c r="Q39" t="s">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="U39">
         <v>6040</v>
       </c>
       <c r="V39" t="s">
-        <v>610</v>
+        <v>611</v>
       </c>
     </row>
     <row r="40" spans="16:22">
@@ -39317,13 +39326,13 @@
         <v>6020</v>
       </c>
       <c r="Q40" t="s">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="U40">
         <v>6050</v>
       </c>
       <c r="V40" t="s">
-        <v>612</v>
+        <v>613</v>
       </c>
     </row>
     <row r="41" spans="16:22">
@@ -39331,13 +39340,13 @@
         <v>6030</v>
       </c>
       <c r="Q41" t="s">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="U41">
         <v>6060</v>
       </c>
       <c r="V41" t="s">
-        <v>614</v>
+        <v>615</v>
       </c>
     </row>
     <row r="42" spans="16:22">
@@ -39345,13 +39354,13 @@
         <v>6040</v>
       </c>
       <c r="Q42" t="s">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="U42">
         <v>6110</v>
       </c>
       <c r="V42" t="s">
-        <v>616</v>
+        <v>617</v>
       </c>
     </row>
     <row r="43" spans="16:22">
@@ -39359,13 +39368,13 @@
         <v>6050</v>
       </c>
       <c r="Q43" t="s">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="U43">
         <v>6120</v>
       </c>
       <c r="V43" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
     </row>
     <row r="44" spans="16:22">
@@ -39373,13 +39382,13 @@
         <v>6060</v>
       </c>
       <c r="Q44" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="U44">
         <v>6130</v>
       </c>
       <c r="V44" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
     </row>
     <row r="45" spans="16:22">
@@ -39387,13 +39396,13 @@
         <v>6070</v>
       </c>
       <c r="Q45" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="U45">
         <v>6140</v>
       </c>
       <c r="V45" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
     </row>
     <row r="46" spans="16:22">
@@ -39401,13 +39410,13 @@
         <v>6080</v>
       </c>
       <c r="Q46" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="U46">
         <v>6150</v>
       </c>
       <c r="V46" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
     </row>
     <row r="47" spans="16:22">
@@ -39415,13 +39424,13 @@
         <v>6100</v>
       </c>
       <c r="Q47" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="U47">
         <v>6210</v>
       </c>
       <c r="V47" t="s">
-        <v>626</v>
+        <v>627</v>
       </c>
     </row>
     <row r="48" spans="16:22">
@@ -39429,13 +39438,13 @@
         <v>6210</v>
       </c>
       <c r="Q48" t="s">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="U48">
         <v>6220</v>
       </c>
       <c r="V48" t="s">
-        <v>628</v>
+        <v>629</v>
       </c>
     </row>
     <row r="49" spans="16:22">
@@ -39443,13 +39452,13 @@
         <v>6310</v>
       </c>
       <c r="Q49" t="s">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="U49">
         <v>6230</v>
       </c>
       <c r="V49" t="s">
-        <v>630</v>
+        <v>631</v>
       </c>
     </row>
     <row r="50" spans="16:22">
@@ -39457,13 +39466,13 @@
         <v>7010</v>
       </c>
       <c r="Q50" t="s">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="U50">
         <v>6240</v>
       </c>
       <c r="V50" t="s">
-        <v>632</v>
+        <v>633</v>
       </c>
     </row>
     <row r="51" spans="16:22">
@@ -39471,13 +39480,13 @@
         <v>7020</v>
       </c>
       <c r="Q51" t="s">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="U51">
         <v>6250</v>
       </c>
       <c r="V51" t="s">
-        <v>634</v>
+        <v>635</v>
       </c>
     </row>
     <row r="52" spans="16:22">
@@ -39485,13 +39494,13 @@
         <v>8010</v>
       </c>
       <c r="Q52" t="s">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="U52">
         <v>6310</v>
       </c>
       <c r="V52" t="s">
-        <v>636</v>
+        <v>637</v>
       </c>
     </row>
     <row r="53" spans="16:22">
@@ -39499,13 +39508,13 @@
         <v>8020</v>
       </c>
       <c r="Q53" t="s">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="U53">
         <v>6320</v>
       </c>
       <c r="V53" t="s">
-        <v>638</v>
+        <v>639</v>
       </c>
     </row>
     <row r="54" spans="16:22">
@@ -39513,13 +39522,13 @@
         <v>9010</v>
       </c>
       <c r="Q54" t="s">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="U54">
         <v>6330</v>
       </c>
       <c r="V54" t="s">
-        <v>640</v>
+        <v>641</v>
       </c>
     </row>
     <row r="55" spans="16:22">
@@ -39527,13 +39536,13 @@
         <v>10010</v>
       </c>
       <c r="Q55" t="s">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="U55">
         <v>6340</v>
       </c>
       <c r="V55" t="s">
-        <v>642</v>
+        <v>643</v>
       </c>
     </row>
     <row r="56" spans="16:22">
@@ -39541,13 +39550,13 @@
         <v>11010</v>
       </c>
       <c r="Q56" t="s">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="U56">
         <v>6350</v>
       </c>
       <c r="V56" t="s">
-        <v>644</v>
+        <v>645</v>
       </c>
     </row>
     <row r="57" spans="16:22">
@@ -39555,13 +39564,13 @@
         <v>12010</v>
       </c>
       <c r="Q57" t="s">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="U57">
         <v>7010</v>
       </c>
       <c r="V57" t="s">
-        <v>646</v>
+        <v>647</v>
       </c>
     </row>
     <row r="58" spans="16:22">
@@ -39569,13 +39578,13 @@
         <v>13010</v>
       </c>
       <c r="Q58" t="s">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="U58">
         <v>7020</v>
       </c>
       <c r="V58" t="s">
-        <v>648</v>
+        <v>649</v>
       </c>
     </row>
     <row r="59" spans="21:22">
@@ -39583,7 +39592,7 @@
         <v>7030</v>
       </c>
       <c r="V59" t="s">
-        <v>649</v>
+        <v>650</v>
       </c>
     </row>
     <row r="60" spans="21:22">
@@ -39591,7 +39600,7 @@
         <v>7040</v>
       </c>
       <c r="V60" t="s">
-        <v>650</v>
+        <v>651</v>
       </c>
     </row>
     <row r="61" spans="21:22">
@@ -39599,7 +39608,7 @@
         <v>7050</v>
       </c>
       <c r="V61" t="s">
-        <v>651</v>
+        <v>652</v>
       </c>
     </row>
     <row r="62" spans="21:22">
@@ -39607,7 +39616,7 @@
         <v>7060</v>
       </c>
       <c r="V62" t="s">
-        <v>652</v>
+        <v>653</v>
       </c>
     </row>
     <row r="63" spans="21:22">
@@ -39615,7 +39624,7 @@
         <v>7070</v>
       </c>
       <c r="V63" t="s">
-        <v>653</v>
+        <v>654</v>
       </c>
     </row>
     <row r="64" spans="21:22">
@@ -39623,7 +39632,7 @@
         <v>8010</v>
       </c>
       <c r="V64" t="s">
-        <v>654</v>
+        <v>655</v>
       </c>
     </row>
     <row r="65" spans="21:22">
@@ -39631,7 +39640,7 @@
         <v>8020</v>
       </c>
       <c r="V65" t="s">
-        <v>655</v>
+        <v>656</v>
       </c>
     </row>
     <row r="66" spans="21:22">
@@ -39639,7 +39648,7 @@
         <v>8030</v>
       </c>
       <c r="V66" t="s">
-        <v>656</v>
+        <v>657</v>
       </c>
     </row>
     <row r="67" spans="21:22">
@@ -39647,7 +39656,7 @@
         <v>8040</v>
       </c>
       <c r="V67" t="s">
-        <v>657</v>
+        <v>658</v>
       </c>
     </row>
     <row r="68" spans="21:22">
@@ -39655,7 +39664,7 @@
         <v>8050</v>
       </c>
       <c r="V68" t="s">
-        <v>658</v>
+        <v>659</v>
       </c>
     </row>
     <row r="69" spans="21:22">
@@ -39663,7 +39672,7 @@
         <v>8060</v>
       </c>
       <c r="V69" t="s">
-        <v>659</v>
+        <v>660</v>
       </c>
     </row>
     <row r="70" spans="21:22">
@@ -39671,7 +39680,7 @@
         <v>9010</v>
       </c>
       <c r="V70" t="s">
-        <v>660</v>
+        <v>661</v>
       </c>
     </row>
     <row r="71" spans="21:22">
@@ -39679,7 +39688,7 @@
         <v>9020</v>
       </c>
       <c r="V71" t="s">
-        <v>661</v>
+        <v>662</v>
       </c>
     </row>
     <row r="72" spans="21:22">
@@ -39687,7 +39696,7 @@
         <v>9030</v>
       </c>
       <c r="V72" t="s">
-        <v>662</v>
+        <v>663</v>
       </c>
     </row>
     <row r="73" spans="21:22">
@@ -39695,7 +39704,7 @@
         <v>9031</v>
       </c>
       <c r="V73" t="s">
-        <v>663</v>
+        <v>664</v>
       </c>
     </row>
     <row r="74" spans="21:22">
@@ -39703,7 +39712,7 @@
         <v>9040</v>
       </c>
       <c r="V74" t="s">
-        <v>664</v>
+        <v>665</v>
       </c>
     </row>
     <row r="75" spans="21:22">
@@ -39711,7 +39720,7 @@
         <v>9110</v>
       </c>
       <c r="V75" t="s">
-        <v>665</v>
+        <v>666</v>
       </c>
     </row>
     <row r="76" spans="21:22">
@@ -39719,7 +39728,7 @@
         <v>9120</v>
       </c>
       <c r="V76" t="s">
-        <v>666</v>
+        <v>667</v>
       </c>
     </row>
     <row r="77" spans="21:22">
@@ -39727,7 +39736,7 @@
         <v>10010</v>
       </c>
       <c r="V77" t="s">
-        <v>667</v>
+        <v>668</v>
       </c>
     </row>
     <row r="78" spans="21:22">
@@ -39735,7 +39744,7 @@
         <v>10020</v>
       </c>
       <c r="V78" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
     </row>
     <row r="79" spans="21:22">
@@ -39743,7 +39752,7 @@
         <v>10110</v>
       </c>
       <c r="V79" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
     </row>
     <row r="80" spans="21:22">
@@ -39751,7 +39760,7 @@
         <v>11010</v>
       </c>
       <c r="V80" t="s">
-        <v>670</v>
+        <v>671</v>
       </c>
     </row>
     <row r="81" spans="21:22">
@@ -39759,7 +39768,7 @@
         <v>11020</v>
       </c>
       <c r="V81" t="s">
-        <v>671</v>
+        <v>672</v>
       </c>
     </row>
     <row r="82" spans="21:22">
@@ -39767,7 +39776,7 @@
         <v>12030</v>
       </c>
       <c r="V82" t="s">
-        <v>672</v>
+        <v>673</v>
       </c>
     </row>
     <row r="83" spans="21:22">
@@ -39775,7 +39784,7 @@
         <v>12040</v>
       </c>
       <c r="V83" t="s">
-        <v>673</v>
+        <v>674</v>
       </c>
     </row>
     <row r="84" spans="21:22">
@@ -39783,7 +39792,7 @@
         <v>12041</v>
       </c>
       <c r="V84" t="s">
-        <v>674</v>
+        <v>675</v>
       </c>
     </row>
     <row r="85" spans="21:22">
@@ -39791,7 +39800,7 @@
         <v>12042</v>
       </c>
       <c r="V85" t="s">
-        <v>675</v>
+        <v>676</v>
       </c>
     </row>
     <row r="86" spans="21:22">
@@ -39799,7 +39808,7 @@
         <v>12043</v>
       </c>
       <c r="V86" t="s">
-        <v>676</v>
+        <v>677</v>
       </c>
     </row>
     <row r="87" spans="21:22">
@@ -39807,7 +39816,7 @@
         <v>12050</v>
       </c>
       <c r="V87" t="s">
-        <v>677</v>
+        <v>678</v>
       </c>
     </row>
     <row r="88" spans="21:22">
@@ -39815,7 +39824,7 @@
         <v>12060</v>
       </c>
       <c r="V88" t="s">
-        <v>678</v>
+        <v>679</v>
       </c>
     </row>
     <row r="89" spans="21:22">
@@ -39823,7 +39832,7 @@
         <v>12063</v>
       </c>
       <c r="V89" t="s">
-        <v>679</v>
+        <v>680</v>
       </c>
     </row>
     <row r="90" spans="21:22">
@@ -39831,7 +39840,7 @@
         <v>12066</v>
       </c>
       <c r="V90" t="s">
-        <v>680</v>
+        <v>681</v>
       </c>
     </row>
     <row r="91" spans="21:22">
@@ -39839,7 +39848,7 @@
         <v>12070</v>
       </c>
       <c r="V91" t="s">
-        <v>681</v>
+        <v>682</v>
       </c>
     </row>
     <row r="92" spans="21:22">
@@ -39847,7 +39856,7 @@
         <v>12071</v>
       </c>
       <c r="V92" t="s">
-        <v>682</v>
+        <v>683</v>
       </c>
     </row>
     <row r="93" spans="21:22">
@@ -39855,7 +39864,7 @@
         <v>12082</v>
       </c>
       <c r="V93" t="s">
-        <v>683</v>
+        <v>684</v>
       </c>
     </row>
     <row r="94" spans="21:22">
@@ -39863,7 +39872,7 @@
         <v>12092</v>
       </c>
       <c r="V94" t="s">
-        <v>684</v>
+        <v>685</v>
       </c>
     </row>
     <row r="95" spans="21:22">
@@ -39871,7 +39880,7 @@
         <v>13010</v>
       </c>
       <c r="V95" t="s">
-        <v>685</v>
+        <v>686</v>
       </c>
     </row>
     <row r="96" spans="21:22">
@@ -39879,7 +39888,7 @@
         <v>13020</v>
       </c>
       <c r="V96" t="s">
-        <v>686</v>
+        <v>687</v>
       </c>
     </row>
     <row r="97" spans="21:22">
@@ -39887,7 +39896,7 @@
         <v>14010</v>
       </c>
       <c r="V97" t="s">
-        <v>687</v>
+        <v>688</v>
       </c>
     </row>
     <row r="98" spans="21:22">
@@ -39895,7 +39904,7 @@
         <v>14110</v>
       </c>
       <c r="V98" t="s">
-        <v>688</v>
+        <v>689</v>
       </c>
     </row>
     <row r="99" spans="21:22">
@@ -39903,7 +39912,7 @@
         <v>14210</v>
       </c>
       <c r="V99" t="s">
-        <v>689</v>
+        <v>690</v>
       </c>
     </row>
     <row r="100" spans="21:22">
@@ -39911,7 +39920,7 @@
         <v>14310</v>
       </c>
       <c r="V100" t="s">
-        <v>690</v>
+        <v>691</v>
       </c>
     </row>
     <row r="101" spans="21:22">
@@ -39919,7 +39928,7 @@
         <v>14410</v>
       </c>
       <c r="V101" t="s">
-        <v>691</v>
+        <v>692</v>
       </c>
     </row>
     <row r="102" spans="21:22">
@@ -39927,7 +39936,7 @@
         <v>15010</v>
       </c>
       <c r="V102" t="s">
-        <v>692</v>
+        <v>693</v>
       </c>
     </row>
     <row r="103" spans="21:22">
@@ -39935,7 +39944,7 @@
         <v>15011</v>
       </c>
       <c r="V103" t="s">
-        <v>693</v>
+        <v>694</v>
       </c>
     </row>
     <row r="104" spans="21:22">
@@ -39943,7 +39952,7 @@
         <v>15022</v>
       </c>
       <c r="V104" t="s">
-        <v>694</v>
+        <v>695</v>
       </c>
     </row>
     <row r="105" spans="21:22">
@@ -39951,7 +39960,7 @@
         <v>16010</v>
       </c>
       <c r="V105" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
     </row>
     <row r="106" spans="21:22">
@@ -39959,7 +39968,7 @@
         <v>17010</v>
       </c>
       <c r="V106" t="s">
-        <v>696</v>
+        <v>697</v>
       </c>
     </row>
     <row r="107" spans="21:22">
@@ -39967,7 +39976,7 @@
         <v>17020</v>
       </c>
       <c r="V107" t="s">
-        <v>697</v>
+        <v>698</v>
       </c>
     </row>
     <row r="108" spans="21:22">
@@ -39975,7 +39984,7 @@
         <v>17030</v>
       </c>
       <c r="V108" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
     </row>
     <row r="109" spans="21:22">
@@ -39983,7 +39992,7 @@
         <v>17040</v>
       </c>
       <c r="V109" t="s">
-        <v>699</v>
+        <v>700</v>
       </c>
     </row>
     <row r="110" spans="21:22">
@@ -39991,7 +40000,7 @@
         <v>17050</v>
       </c>
       <c r="V110" t="s">
-        <v>700</v>
+        <v>701</v>
       </c>
     </row>
     <row r="111" spans="21:22">
@@ -39999,7 +40008,7 @@
         <v>17060</v>
       </c>
       <c r="V111" t="s">
-        <v>701</v>
+        <v>702</v>
       </c>
     </row>
     <row r="112" spans="21:22">
@@ -40007,7 +40016,7 @@
         <v>18010</v>
       </c>
       <c r="V112" t="s">
-        <v>702</v>
+        <v>703</v>
       </c>
     </row>
     <row r="113" spans="21:22">
@@ -40015,7 +40024,7 @@
         <v>18020</v>
       </c>
       <c r="V113" t="s">
-        <v>703</v>
+        <v>704</v>
       </c>
     </row>
     <row r="114" spans="21:22">
@@ -40023,7 +40032,7 @@
         <v>19010</v>
       </c>
       <c r="V114" t="s">
-        <v>704</v>
+        <v>705</v>
       </c>
     </row>
     <row r="115" spans="21:22">
@@ -40031,7 +40040,7 @@
         <v>19020</v>
       </c>
       <c r="V115" t="s">
-        <v>705</v>
+        <v>706</v>
       </c>
     </row>
     <row r="116" spans="21:22">
@@ -40039,7 +40048,7 @@
         <v>20030</v>
       </c>
       <c r="V116" t="s">
-        <v>706</v>
+        <v>707</v>
       </c>
     </row>
     <row r="117" spans="21:22">
@@ -40047,7 +40056,7 @@
         <v>20040</v>
       </c>
       <c r="V117" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
     </row>
     <row r="118" spans="21:22">
@@ -40055,7 +40064,7 @@
         <v>20050</v>
       </c>
       <c r="V118" t="s">
-        <v>708</v>
+        <v>709</v>
       </c>
     </row>
     <row r="119" spans="21:22">
@@ -40063,7 +40072,7 @@
         <v>20070</v>
       </c>
       <c r="V119" t="s">
-        <v>709</v>
+        <v>710</v>
       </c>
     </row>
     <row r="120" spans="21:22">
@@ -40071,7 +40080,7 @@
         <v>20071</v>
       </c>
       <c r="V120" t="s">
-        <v>710</v>
+        <v>711</v>
       </c>
     </row>
     <row r="121" spans="21:22">
@@ -40079,7 +40088,7 @@
         <v>20110</v>
       </c>
       <c r="V121" t="s">
-        <v>711</v>
+        <v>712</v>
       </c>
     </row>
     <row r="122" spans="21:22">
@@ -40087,7 +40096,7 @@
         <v>20120</v>
       </c>
       <c r="V122" t="s">
-        <v>712</v>
+        <v>713</v>
       </c>
     </row>
     <row r="123" spans="21:22">
@@ -40095,7 +40104,7 @@
         <v>20130</v>
       </c>
       <c r="V123" t="s">
-        <v>713</v>
+        <v>714</v>
       </c>
     </row>
     <row r="124" spans="21:22">
@@ -40103,7 +40112,7 @@
         <v>20140</v>
       </c>
       <c r="V124" t="s">
-        <v>714</v>
+        <v>715</v>
       </c>
     </row>
     <row r="125" spans="21:22">
@@ -40111,7 +40120,7 @@
         <v>20150</v>
       </c>
       <c r="V125" t="s">
-        <v>715</v>
+        <v>716</v>
       </c>
     </row>
     <row r="126" spans="21:22">
@@ -40119,7 +40128,7 @@
         <v>20160</v>
       </c>
       <c r="V126" t="s">
-        <v>716</v>
+        <v>717</v>
       </c>
     </row>
     <row r="127" spans="21:22">
@@ -40127,7 +40136,7 @@
         <v>23010</v>
       </c>
       <c r="V127" t="s">
-        <v>717</v>
+        <v>718</v>
       </c>
     </row>
     <row r="128" spans="21:22">
@@ -40135,7 +40144,7 @@
         <v>30010</v>
       </c>
       <c r="V128" t="s">
-        <v>718</v>
+        <v>719</v>
       </c>
     </row>
     <row r="129" spans="21:22">
@@ -40143,7 +40152,7 @@
         <v>30020</v>
       </c>
       <c r="V129" t="s">
-        <v>719</v>
+        <v>720</v>
       </c>
     </row>
   </sheetData>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6620"/>
+    <workbookView windowWidth="19200" windowHeight="6620" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2376,10 +2376,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2398,6 +2398,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -2411,22 +2418,25 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
+      <color rgb="FF0000FF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2440,17 +2450,16 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2464,7 +2473,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFF0000"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2472,15 +2481,14 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2511,14 +2519,6 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2528,7 +2528,7 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFA7D00"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2556,7 +2556,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2568,19 +2574,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2592,13 +2604,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2622,25 +2652,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2652,13 +2670,61 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2670,73 +2736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2765,6 +2765,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FFB2B2B2"/>
       </left>
@@ -2782,15 +2791,6 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -2800,17 +2800,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
+      <left/>
+      <right/>
+      <top/>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2834,16 +2828,22 @@
       <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4"/>
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2855,145 +2855,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="19" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -30544,11 +30544,11 @@
         <v>アクティブギフト+</v>
       </c>
       <c r="C275">
-        <v>6010</v>
+        <v>6080</v>
       </c>
       <c r="D275" t="str">
         <f>INDEX(Define!Q:Q,MATCH(C275,Define!P:P))</f>
-        <v>指定のFeatureのParam1を増やす</v>
+        <v>指定魔法のCTリセット値を変更する</v>
       </c>
       <c r="E275">
         <v>11040</v>
@@ -30557,7 +30557,7 @@
         <v>0</v>
       </c>
       <c r="G275">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H275">
         <v>100</v>
@@ -37737,7 +37737,7 @@
         <v>399</v>
       </c>
       <c r="C204" s="4" t="s">
-        <v>377</v>
+        <v>340</v>
       </c>
     </row>
     <row r="205" customFormat="1" spans="1:3">

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6620" activeTab="2"/>
+    <workbookView windowWidth="19200" windowHeight="6620" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2376,10 +2376,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2397,15 +2397,55 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <sz val="11"/>
-      <color theme="0"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2426,14 +2466,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
@@ -2445,21 +2477,6 @@
       <u/>
       <sz val="11"/>
       <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2479,26 +2496,10 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2510,25 +2511,24 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
-      <sz val="13"/>
-      <color theme="3"/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color theme="1"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2556,13 +2556,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2574,19 +2592,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2598,37 +2610,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2646,25 +2652,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2676,7 +2670,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2688,7 +2682,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2700,7 +2724,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2712,31 +2736,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2747,6 +2747,15 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -2761,50 +2770,6 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2833,6 +2798,30 @@
       <diagonal/>
     </border>
     <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -2847,6 +2836,17 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2855,145 +2855,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="11" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6620" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6620"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2376,10 +2376,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2397,55 +2397,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
+      <u/>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2459,7 +2413,66 @@
     </font>
     <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="134"/>
@@ -2474,45 +2487,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2527,15 +2503,39 @@
     </font>
     <font>
       <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2556,31 +2556,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2592,13 +2568,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2610,73 +2580,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="8" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2694,7 +2604,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2706,31 +2682,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2750,11 +2750,17 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2774,41 +2780,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color theme="4"/>
       </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+      <bottom style="double">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2839,11 +2817,33 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
       <top style="thin">
-        <color theme="4"/>
+        <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2855,16 +2855,16 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -2873,127 +2873,127 @@
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="18" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="28" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -11779,7 +11779,7 @@
         <v>覚醒</v>
       </c>
       <c r="F105">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="G105">
         <v>1</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -114,7 +114,7 @@
     <t>""</t>
   </si>
   <si>
-    <t>攻撃</t>
+    <t>はずす</t>
   </si>
   <si>
     <t>覚醒</t>
@@ -2376,10 +2376,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2399,6 +2399,57 @@
     <font>
       <u/>
       <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
       <color rgb="FF800080"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
@@ -2406,7 +2457,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2429,74 +2480,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2511,10 +2495,10 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -2528,14 +2512,30 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
       <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FFFFFFFF"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2556,6 +2556,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -2568,7 +2574,121 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2580,79 +2700,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2664,49 +2712,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2724,19 +2730,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2782,11 +2782,9 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2800,26 +2798,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
       </top>
       <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2847,6 +2832,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2855,145 +2855,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="22" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="21" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -4120,24 +4120,24 @@
       </c>
       <c r="C3" t="str">
         <f>INDEX(TextData!B:B,MATCH(B3,TextData!A:A))</f>
-        <v>攻撃</v>
+        <v>はずす</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3" t="str">
         <f>INDEX(Define!X:X,MATCH(D3,Define!W:W))</f>
-        <v>元素</v>
+        <v>なし</v>
       </c>
       <c r="F3">
         <v>0</v>
       </c>
       <c r="G3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H3" t="str">
         <f>INDEX(Define!B:B,MATCH(G3,Define!A:A))</f>
-        <v>単体</v>
+        <v>なし</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -4153,25 +4153,25 @@
         <v>なし</v>
       </c>
       <c r="M3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N3" t="str">
         <f>INDEX(Define!H:H,MATCH(M3,Define!G:G))</f>
-        <v>魔法</v>
+        <v>なし</v>
       </c>
       <c r="O3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P3" t="str">
         <f>INDEX(Define!K:K,MATCH(O3,Define!J:J))</f>
-        <v>相手</v>
+        <v>なし</v>
       </c>
       <c r="Q3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R3" t="str">
         <f>INDEX(Define!N:N,MATCH(Q3,Define!M:M))</f>
-        <v>単体</v>
+        <v>なし</v>
       </c>
       <c r="S3">
         <v>1</v>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="C4" t="str">
         <f>INDEX(TextData!B:B,MATCH(B4,TextData!A:A))</f>
-        <v>攻撃</v>
+        <v>はずす</v>
       </c>
       <c r="D4">
         <v>1</v>
@@ -22477,7 +22477,7 @@
       </c>
       <c r="B2" t="str">
         <f>INDEX(TextData!B:B,MATCH(A2,TextData!A:A))</f>
-        <v>攻撃</v>
+        <v>はずす</v>
       </c>
       <c r="C2">
         <v>1010</v>
@@ -22505,7 +22505,7 @@
       </c>
       <c r="B3" t="str">
         <f>INDEX(TextData!B:B,MATCH(A3,TextData!A:A))</f>
-        <v>攻撃</v>
+        <v>はずす</v>
       </c>
       <c r="C3">
         <v>1010</v>

--- a/Assets/Data/Skills.xlsx
+++ b/Assets/Data/Skills.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19200" windowHeight="6620" activeTab="1"/>
+    <workbookView windowWidth="19200" windowHeight="6620"/>
   </bookViews>
   <sheets>
     <sheet name="Skills" sheetId="1" r:id="rId1"/>
@@ -2389,9 +2389,9 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
   </numFmts>
   <fonts count="21">
     <font>
@@ -2410,6 +2410,119 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="ＭＳ Ｐゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="13"/>
       <color theme="3"/>
       <name val="ＭＳ Ｐゴシック"/>
@@ -2417,9 +2530,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FFFA7D00"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2434,120 +2547,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color theme="0"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C6500"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="ＭＳ Ｐゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="ＭＳ Ｐゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -2568,13 +2568,103 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7"/>
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2592,25 +2682,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2622,7 +2730,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2634,121 +2748,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -2764,24 +2764,26 @@
     <border>
       <left/>
       <right/>
-      <top/>
-      <bottom style="medium">
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
         <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </left>
       <right style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </right>
       <top style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </top>
       <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2802,6 +2804,30 @@
     </border>
     <border>
       <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
       <right style="thin">
@@ -2816,17 +2842,11 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2839,26 +2859,6 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -2867,145 +2867,145 @@
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="18" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="18" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="9" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="9" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3968,7 +3968,7 @@
     <col min="9" max="10" width="6.63636363636364" customWidth="1"/>
     <col min="11" max="11" width="5.36363636363636" style="6" customWidth="1"/>
     <col min="12" max="12" width="4.90909090909091" style="6" customWidth="1"/>
-    <col min="13" max="13" width="4.72727272727273" customWidth="1"/>
+    <col min="13" max="13" width="4.45454545454545" customWidth="1"/>
     <col min="14" max="14" width="5.54545454545455" customWidth="1"/>
     <col min="15" max="15" width="5.18181818181818" customWidth="1"/>
     <col min="16" max="16" width="22.0909090909091" customWidth="1"/>
